--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,6 +904,9743 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125023406</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>753718</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7218042</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125023389</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>753729</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7218042</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125023327</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>753740</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7217891</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125023338</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8720</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100798</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Smal trollknäppare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Danosoma conspersum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Gyllenhal, 1808)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>753699</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7217618</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125023367</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>753786</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7217962</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125023395</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>753472</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7218031</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125023392</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>753718</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7218035</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125023316</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>753568</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7217733</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre bohål</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125023366</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>753778</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7217945</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125023446</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91221</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>753567</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7217721</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125023438</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>753612</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7217703</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125023380</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79927</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>753769</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7218019</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125023426</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>753597</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7217728</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125023339</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92285</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>753567</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7217957</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp. Brunorangt kött uppåt hatten, vitdassigt ner mot foten</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125023411</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>753557</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7217895</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125023354</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>753773</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7217842</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125023335</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>753790</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7217992</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125023445</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>753715</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7218026</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125023333</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>753781</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7217902</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125023375</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>753750</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7218028</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125023420</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>753559</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7217734</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125023398</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>753778</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7217858</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125023435</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>753562</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7217727</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färsk bohål</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125023401</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>753780</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7217865</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125023412</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>753568</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7217875</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125023323</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>753504</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7217889</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125023345</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>753790</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7217981</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125023374</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>753763</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7218015</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125023343</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>753760</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7218023</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125023320</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>753687</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7217999</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125023365</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>753784</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7217948</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125023442</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>753726</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7218039</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125023324</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>753480</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7218033</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125023417</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>753474</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7218026</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125023378</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>753722</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7218033</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125023414</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>753630</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7218006</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125023388</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>753742</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7217924</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125023349</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>753795</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7217800</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125023394</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>753596</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7217939</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125023325</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>753575</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7217959</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>125023416</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>753470</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7218024</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>125023360</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>753752</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7217944</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125023409</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>753562</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7217917</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125023421</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>753573</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7217745</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125023341</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79919</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>753654</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7218008</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125023372</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>753790</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7217992</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125023396</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>753626</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7218004</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>125023373</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>753768</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7218016</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125023418</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>753406</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7217999</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125023434</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>753797</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7217988</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125023336</v>
+      </c>
+      <c r="B54" t="n">
+        <v>90962</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>112</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>753566</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7217862</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>125023358</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>753758</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7217900</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>125023337</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79795</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>753523</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7218086</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125023319</v>
+      </c>
+      <c r="B57" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>753506</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7217904</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>125023441</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>753798</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7217948</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125023402</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>753752</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7217878</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>125023328</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>753742</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7217926</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>125023368</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>753808</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7217964</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>125023348</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>753817</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7217853</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>125023334</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>753752</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7217919</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>125023350</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>753789</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7217812</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>125023326</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>753598</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7217744</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>125023430</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79926</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>753789</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7217809</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>125023315</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>753491</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7217766</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>125023419</v>
+      </c>
+      <c r="B68" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>753550</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7217725</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>125023342</v>
+      </c>
+      <c r="B69" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>753722</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7217596</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>125023405</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>753748</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7218047</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>125023352</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>753763</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7217831</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>125023423</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>753610</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7217727</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>125023399</v>
+      </c>
+      <c r="B73" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>753751</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7217806</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>125023432</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79926</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>753769</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7218019</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>125023330</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>753730</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7217943</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>125023387</v>
+      </c>
+      <c r="B76" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>753816</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7217838</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>125023443</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>753575</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7217751</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>125023439</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>753568</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7217716</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>125023429</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79926</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>753792</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7217798</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>125023359</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>753753</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7217910</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>125023347</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>753850</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7217843</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>125023369</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>753797</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7218005</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>125023381</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79927</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>753722</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7218033</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>125023321</v>
+      </c>
+      <c r="B84" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>753679</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7218005</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>125023318</v>
+      </c>
+      <c r="B85" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>753680</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7218004</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>125023404</v>
+      </c>
+      <c r="B86" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>753743</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7218044</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>125023444</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>753746</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7217930</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>125023407</v>
+      </c>
+      <c r="B88" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>753671</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7218008</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>125023357</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>753793</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7217856</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>125023413</v>
+      </c>
+      <c r="B90" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>753517</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7217918</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>125023403</v>
+      </c>
+      <c r="B91" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>753762</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7218015</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>125023391</v>
+      </c>
+      <c r="B92" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>753706</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7218039</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>125023363</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>753782</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7217946</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>125023355</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>753792</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7217850</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>125023390</v>
+      </c>
+      <c r="B95" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>753701</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7218031</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>125023431</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79926</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>753774</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7217939</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>125023351</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>753758</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7217819</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125023406</v>
+        <v>125023375</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753718</v>
+        <v>753750</v>
       </c>
       <c r="R4" t="n">
-        <v>7218042</v>
+        <v>7218028</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125023389</v>
+        <v>125023398</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,38 +1021,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753729</v>
+        <v>753778</v>
       </c>
       <c r="R5" t="n">
-        <v>7218042</v>
+        <v>7217858</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,12 +1094,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1111,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125023327</v>
+        <v>125023423</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,21 +1140,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753740</v>
+        <v>753610</v>
       </c>
       <c r="R6" t="n">
-        <v>7217891</v>
+        <v>7217727</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125023338</v>
+        <v>125023343</v>
       </c>
       <c r="B7" t="n">
-        <v>8720</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,25 +1238,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100798</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smal trollknäppare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Danosoma conspersum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>753699</v>
+        <v>753760</v>
       </c>
       <c r="R7" t="n">
-        <v>7217618</v>
+        <v>7218023</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,6 +1302,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,7 +1334,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125023367</v>
+        <v>125023362</v>
       </c>
       <c r="B8" t="n">
         <v>79891</v>
@@ -1356,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>753786</v>
+        <v>753752</v>
       </c>
       <c r="R8" t="n">
-        <v>7217962</v>
+        <v>7217944</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125023395</v>
+        <v>125023396</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,34 +1452,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>753472</v>
+        <v>753626</v>
       </c>
       <c r="R9" t="n">
-        <v>7218031</v>
+        <v>7218004</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,12 +1521,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1520,7 +1551,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125023392</v>
+        <v>125023388</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1560,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>753718</v>
+        <v>753742</v>
       </c>
       <c r="R10" t="n">
-        <v>7218035</v>
+        <v>7217924</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125023316</v>
+        <v>125023341</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>79919</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,46 +1665,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>753568</v>
+        <v>753654</v>
       </c>
       <c r="R11" t="n">
-        <v>7217733</v>
+        <v>7218008</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,11 +1729,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1737,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023366</v>
+        <v>125023435</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,34 +1771,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>753778</v>
+        <v>753562</v>
       </c>
       <c r="R12" t="n">
-        <v>7217945</v>
+        <v>7217727</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,6 +1839,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1839,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125023446</v>
+        <v>125023357</v>
       </c>
       <c r="B13" t="n">
-        <v>91221</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1851,25 +1882,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1106</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1879,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753567</v>
+        <v>753793</v>
       </c>
       <c r="R13" t="n">
-        <v>7217721</v>
+        <v>7217856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,7 +1954,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1942,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125023438</v>
+        <v>125023446</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>91221</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1954,25 +1984,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1106</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1982,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753612</v>
+        <v>753567</v>
       </c>
       <c r="R14" t="n">
-        <v>7217703</v>
+        <v>7217721</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,17 +2050,13 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2049,10 +2075,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125023380</v>
+        <v>125023372</v>
       </c>
       <c r="B15" t="n">
-        <v>79927</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2061,25 +2087,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2089,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>753769</v>
+        <v>753790</v>
       </c>
       <c r="R15" t="n">
-        <v>7218019</v>
+        <v>7217992</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,10 +2177,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125023426</v>
+        <v>125023443</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2167,21 +2193,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2191,10 +2217,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753597</v>
+        <v>753575</v>
       </c>
       <c r="R16" t="n">
-        <v>7217728</v>
+        <v>7217751</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2227,6 +2253,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2253,10 +2284,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125023339</v>
+        <v>125023349</v>
       </c>
       <c r="B17" t="n">
-        <v>92285</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2269,37 +2300,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753567</v>
+        <v>753795</v>
       </c>
       <c r="R17" t="n">
-        <v>7217957</v>
+        <v>7217800</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2334,18 +2362,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp. Brunorangt kött uppåt hatten, vitdassigt ner mot foten</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2364,10 +2386,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125023411</v>
+        <v>125023351</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2380,21 +2402,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2404,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753557</v>
+        <v>753758</v>
       </c>
       <c r="R18" t="n">
-        <v>7217895</v>
+        <v>7217819</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,10 +2488,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125023354</v>
+        <v>125023442</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2482,21 +2504,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2506,10 +2528,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753773</v>
+        <v>753726</v>
       </c>
       <c r="R19" t="n">
-        <v>7217842</v>
+        <v>7218039</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2542,6 +2564,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2568,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125023335</v>
+        <v>125023326</v>
       </c>
       <c r="B20" t="n">
-        <v>79920</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2580,38 +2607,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753790</v>
+        <v>753598</v>
       </c>
       <c r="R20" t="n">
-        <v>7217992</v>
+        <v>7217744</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2644,6 +2679,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2670,10 +2710,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125023445</v>
+        <v>125023336</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>90962</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2686,21 +2726,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2710,10 +2750,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753715</v>
+        <v>753566</v>
       </c>
       <c r="R21" t="n">
-        <v>7218026</v>
+        <v>7217862</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2746,11 +2786,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2777,10 +2812,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125023333</v>
+        <v>125023431</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>79926</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2789,25 +2824,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2817,10 +2852,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753781</v>
+        <v>753774</v>
       </c>
       <c r="R22" t="n">
-        <v>7217902</v>
+        <v>7217939</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2879,10 +2914,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125023375</v>
+        <v>125023405</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2895,21 +2930,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2919,10 +2954,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753750</v>
+        <v>753748</v>
       </c>
       <c r="R23" t="n">
-        <v>7218028</v>
+        <v>7218047</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2981,10 +3016,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125023420</v>
+        <v>125023328</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2997,21 +3032,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3021,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753559</v>
+        <v>753742</v>
       </c>
       <c r="R24" t="n">
-        <v>7217734</v>
+        <v>7217926</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3083,10 +3118,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125023398</v>
+        <v>125023441</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3099,41 +3134,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753778</v>
+        <v>753798</v>
       </c>
       <c r="R25" t="n">
-        <v>7217858</v>
+        <v>7217948</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3170,7 +3198,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3179,7 +3207,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3198,10 +3225,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125023435</v>
+        <v>125023419</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3214,42 +3241,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753562</v>
+        <v>753550</v>
       </c>
       <c r="R26" t="n">
-        <v>7217727</v>
+        <v>7217725</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3282,11 +3301,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3313,10 +3327,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125023401</v>
+        <v>125023333</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3329,21 +3343,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3353,10 +3367,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753780</v>
+        <v>753781</v>
       </c>
       <c r="R27" t="n">
-        <v>7217865</v>
+        <v>7217902</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3415,10 +3429,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125023412</v>
+        <v>125023368</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3431,21 +3445,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3455,10 +3469,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753568</v>
+        <v>753808</v>
       </c>
       <c r="R28" t="n">
-        <v>7217875</v>
+        <v>7217964</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3517,10 +3531,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125023323</v>
+        <v>125023354</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3533,21 +3547,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3557,10 +3571,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753504</v>
+        <v>753773</v>
       </c>
       <c r="R29" t="n">
-        <v>7217889</v>
+        <v>7217842</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3619,10 +3633,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125023345</v>
+        <v>125023444</v>
       </c>
       <c r="B30" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3635,21 +3649,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3659,10 +3673,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753790</v>
+        <v>753746</v>
       </c>
       <c r="R30" t="n">
-        <v>7217981</v>
+        <v>7217930</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3695,6 +3709,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3721,10 +3740,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125023374</v>
+        <v>125023321</v>
       </c>
       <c r="B31" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3737,21 +3756,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3761,10 +3780,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753763</v>
+        <v>753679</v>
       </c>
       <c r="R31" t="n">
-        <v>7218015</v>
+        <v>7218005</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3823,7 +3842,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125023343</v>
+        <v>125023378</v>
       </c>
       <c r="B32" t="n">
         <v>79891</v>
@@ -3863,10 +3882,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753760</v>
+        <v>753722</v>
       </c>
       <c r="R32" t="n">
-        <v>7218023</v>
+        <v>7218033</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3901,18 +3920,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3931,10 +3944,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125023320</v>
+        <v>125023429</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>79926</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3943,25 +3956,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3971,10 +3984,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753687</v>
+        <v>753792</v>
       </c>
       <c r="R33" t="n">
-        <v>7217999</v>
+        <v>7217798</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4033,7 +4046,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125023365</v>
+        <v>125023374</v>
       </c>
       <c r="B34" t="n">
         <v>79891</v>
@@ -4073,10 +4086,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753784</v>
+        <v>753763</v>
       </c>
       <c r="R34" t="n">
-        <v>7217948</v>
+        <v>7218015</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4135,10 +4148,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125023442</v>
+        <v>125023330</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4151,21 +4164,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4175,10 +4188,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753726</v>
+        <v>753730</v>
       </c>
       <c r="R35" t="n">
-        <v>7218039</v>
+        <v>7217943</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4211,11 +4224,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4242,10 +4250,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125023324</v>
+        <v>125023394</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4258,21 +4266,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4282,10 +4290,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753480</v>
+        <v>753596</v>
       </c>
       <c r="R36" t="n">
-        <v>7218033</v>
+        <v>7217939</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4344,7 +4352,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125023417</v>
+        <v>125023403</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4384,10 +4392,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753474</v>
+        <v>753762</v>
       </c>
       <c r="R37" t="n">
-        <v>7218026</v>
+        <v>7218015</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4446,7 +4454,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125023378</v>
+        <v>125023373</v>
       </c>
       <c r="B38" t="n">
         <v>79891</v>
@@ -4486,10 +4494,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753722</v>
+        <v>753768</v>
       </c>
       <c r="R38" t="n">
-        <v>7218033</v>
+        <v>7218016</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4650,10 +4658,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125023388</v>
+        <v>125023339</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>92285</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4662,38 +4670,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753742</v>
+        <v>753567</v>
       </c>
       <c r="R40" t="n">
-        <v>7217924</v>
+        <v>7217957</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4728,12 +4739,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp. Brunorangt kött uppåt hatten, vitdassigt ner mot foten</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4752,10 +4769,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125023349</v>
+        <v>125023327</v>
       </c>
       <c r="B41" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4768,21 +4785,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4792,10 +4809,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753795</v>
+        <v>753740</v>
       </c>
       <c r="R41" t="n">
-        <v>7217800</v>
+        <v>7217891</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4854,10 +4871,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125023394</v>
+        <v>125023338</v>
       </c>
       <c r="B42" t="n">
-        <v>91030</v>
+        <v>8720</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4866,25 +4883,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smal trollknäppare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Danosoma conspersum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyllenhal, 1808)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4894,10 +4911,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753596</v>
+        <v>753699</v>
       </c>
       <c r="R42" t="n">
-        <v>7217939</v>
+        <v>7217618</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4938,6 +4955,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4956,10 +4974,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125023325</v>
+        <v>125023381</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>79927</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4968,46 +4986,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753575</v>
+        <v>753722</v>
       </c>
       <c r="R43" t="n">
-        <v>7217959</v>
+        <v>7218033</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5040,11 +5050,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5071,7 +5076,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125023416</v>
+        <v>125023411</v>
       </c>
       <c r="B44" t="n">
         <v>78810</v>
@@ -5111,10 +5116,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753470</v>
+        <v>753557</v>
       </c>
       <c r="R44" t="n">
-        <v>7218024</v>
+        <v>7217895</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5173,10 +5178,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125023360</v>
+        <v>125023434</v>
       </c>
       <c r="B45" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5189,34 +5194,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753752</v>
+        <v>753797</v>
       </c>
       <c r="R45" t="n">
-        <v>7217944</v>
+        <v>7217988</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5249,6 +5262,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5275,10 +5293,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125023409</v>
+        <v>125023438</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5291,21 +5309,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5315,10 +5333,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753562</v>
+        <v>753612</v>
       </c>
       <c r="R46" t="n">
-        <v>7217917</v>
+        <v>7217703</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5351,6 +5369,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5377,7 +5400,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125023421</v>
+        <v>125023420</v>
       </c>
       <c r="B47" t="n">
         <v>78810</v>
@@ -5417,10 +5440,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753573</v>
+        <v>753559</v>
       </c>
       <c r="R47" t="n">
-        <v>7217745</v>
+        <v>7217734</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5479,10 +5502,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125023341</v>
+        <v>125023421</v>
       </c>
       <c r="B48" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5491,25 +5514,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5519,10 +5542,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753654</v>
+        <v>753573</v>
       </c>
       <c r="R48" t="n">
-        <v>7218008</v>
+        <v>7217745</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5581,10 +5604,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125023372</v>
+        <v>125023320</v>
       </c>
       <c r="B49" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5597,21 +5620,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5621,10 +5644,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753790</v>
+        <v>753687</v>
       </c>
       <c r="R49" t="n">
-        <v>7217992</v>
+        <v>7217999</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5683,10 +5706,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125023396</v>
+        <v>125023445</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5699,41 +5722,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753626</v>
+        <v>753715</v>
       </c>
       <c r="R50" t="n">
-        <v>7218004</v>
+        <v>7218026</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5770,7 +5786,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5779,7 +5795,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5798,10 +5813,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125023373</v>
+        <v>125023337</v>
       </c>
       <c r="B51" t="n">
-        <v>79891</v>
+        <v>79795</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5810,25 +5825,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5838,10 +5853,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753768</v>
+        <v>753523</v>
       </c>
       <c r="R51" t="n">
-        <v>7218016</v>
+        <v>7218086</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5900,10 +5915,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125023418</v>
+        <v>125023324</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5916,21 +5931,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5940,10 +5955,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>753406</v>
+        <v>753480</v>
       </c>
       <c r="R52" t="n">
-        <v>7217999</v>
+        <v>7218033</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6002,10 +6017,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125023434</v>
+        <v>125023369</v>
       </c>
       <c r="B53" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6018,32 +6033,24 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
@@ -6053,7 +6060,7 @@
         <v>753797</v>
       </c>
       <c r="R53" t="n">
-        <v>7217988</v>
+        <v>7218005</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6086,11 +6093,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6117,10 +6119,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125023336</v>
+        <v>125023358</v>
       </c>
       <c r="B54" t="n">
-        <v>90962</v>
+        <v>79891</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6133,21 +6135,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6157,10 +6159,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753566</v>
+        <v>753758</v>
       </c>
       <c r="R54" t="n">
-        <v>7217862</v>
+        <v>7217900</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6219,10 +6221,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125023358</v>
+        <v>125023315</v>
       </c>
       <c r="B55" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6235,21 +6237,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6259,10 +6261,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753758</v>
+        <v>753491</v>
       </c>
       <c r="R55" t="n">
-        <v>7217900</v>
+        <v>7217766</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6295,6 +6297,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6321,10 +6328,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125023337</v>
+        <v>125023387</v>
       </c>
       <c r="B56" t="n">
-        <v>79795</v>
+        <v>78546</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6333,25 +6340,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6361,10 +6368,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753523</v>
+        <v>753816</v>
       </c>
       <c r="R56" t="n">
-        <v>7218086</v>
+        <v>7217838</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6423,10 +6430,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125023319</v>
+        <v>125023365</v>
       </c>
       <c r="B57" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6435,25 +6442,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6463,10 +6470,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753506</v>
+        <v>753784</v>
       </c>
       <c r="R57" t="n">
-        <v>7217904</v>
+        <v>7217948</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6525,7 +6532,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125023441</v>
+        <v>125023316</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -6559,16 +6566,24 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753798</v>
+        <v>753568</v>
       </c>
       <c r="R58" t="n">
-        <v>7217948</v>
+        <v>7217733</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6605,7 +6620,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Barksprätt</t>
+          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6632,10 +6647,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125023402</v>
+        <v>125023350</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6648,21 +6663,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6672,10 +6687,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753752</v>
+        <v>753789</v>
       </c>
       <c r="R59" t="n">
-        <v>7217878</v>
+        <v>7217812</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6734,10 +6749,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125023328</v>
+        <v>125023439</v>
       </c>
       <c r="B60" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6750,21 +6765,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6774,10 +6789,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753742</v>
+        <v>753568</v>
       </c>
       <c r="R60" t="n">
-        <v>7217926</v>
+        <v>7217716</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6810,6 +6825,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6836,7 +6856,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125023368</v>
+        <v>125023363</v>
       </c>
       <c r="B61" t="n">
         <v>79891</v>
@@ -6876,10 +6896,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753808</v>
+        <v>753782</v>
       </c>
       <c r="R61" t="n">
-        <v>7217964</v>
+        <v>7217946</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6938,10 +6958,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125023348</v>
+        <v>125023413</v>
       </c>
       <c r="B62" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6954,21 +6974,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6978,10 +6998,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753817</v>
+        <v>753517</v>
       </c>
       <c r="R62" t="n">
-        <v>7217853</v>
+        <v>7217918</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7040,10 +7060,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125023334</v>
+        <v>125023391</v>
       </c>
       <c r="B63" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7052,25 +7072,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7080,10 +7100,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753752</v>
+        <v>753706</v>
       </c>
       <c r="R63" t="n">
-        <v>7217919</v>
+        <v>7218039</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7142,10 +7162,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125023350</v>
+        <v>125023412</v>
       </c>
       <c r="B64" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7158,21 +7178,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7182,10 +7202,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753789</v>
+        <v>753568</v>
       </c>
       <c r="R64" t="n">
-        <v>7217812</v>
+        <v>7217875</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7244,10 +7264,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125023326</v>
+        <v>125023432</v>
       </c>
       <c r="B65" t="n">
-        <v>57513</v>
+        <v>79926</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7256,46 +7276,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753598</v>
+        <v>753769</v>
       </c>
       <c r="R65" t="n">
-        <v>7217744</v>
+        <v>7218019</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7328,11 +7340,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7359,10 +7366,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125023430</v>
+        <v>125023319</v>
       </c>
       <c r="B66" t="n">
-        <v>79926</v>
+        <v>90977</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7375,21 +7382,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7399,10 +7406,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753789</v>
+        <v>753506</v>
       </c>
       <c r="R66" t="n">
-        <v>7217809</v>
+        <v>7217904</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7461,10 +7468,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125023315</v>
+        <v>125023366</v>
       </c>
       <c r="B67" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7477,21 +7484,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7501,10 +7508,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753491</v>
+        <v>753778</v>
       </c>
       <c r="R67" t="n">
-        <v>7217766</v>
+        <v>7217945</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7537,11 +7544,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7568,7 +7570,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125023419</v>
+        <v>125023404</v>
       </c>
       <c r="B68" t="n">
         <v>78810</v>
@@ -7608,10 +7610,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753550</v>
+        <v>753743</v>
       </c>
       <c r="R68" t="n">
-        <v>7217725</v>
+        <v>7218044</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7670,10 +7672,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125023342</v>
+        <v>125023355</v>
       </c>
       <c r="B69" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7686,21 +7688,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7710,10 +7712,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753722</v>
+        <v>753792</v>
       </c>
       <c r="R69" t="n">
-        <v>7217596</v>
+        <v>7217850</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7754,7 +7756,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7773,7 +7774,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125023405</v>
+        <v>125023416</v>
       </c>
       <c r="B70" t="n">
         <v>78810</v>
@@ -7813,10 +7814,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753748</v>
+        <v>753470</v>
       </c>
       <c r="R70" t="n">
-        <v>7218047</v>
+        <v>7218024</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7875,10 +7876,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125023352</v>
+        <v>125023390</v>
       </c>
       <c r="B71" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7887,25 +7888,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7915,10 +7916,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753763</v>
+        <v>753701</v>
       </c>
       <c r="R71" t="n">
-        <v>7217831</v>
+        <v>7218031</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7977,7 +7978,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125023423</v>
+        <v>125023402</v>
       </c>
       <c r="B72" t="n">
         <v>78810</v>
@@ -8017,10 +8018,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753610</v>
+        <v>753752</v>
       </c>
       <c r="R72" t="n">
-        <v>7217727</v>
+        <v>7217878</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8079,10 +8080,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125023399</v>
+        <v>125023367</v>
       </c>
       <c r="B73" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8095,21 +8096,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8119,10 +8120,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>753751</v>
+        <v>753786</v>
       </c>
       <c r="R73" t="n">
-        <v>7217806</v>
+        <v>7217962</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8181,10 +8182,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125023432</v>
+        <v>125023401</v>
       </c>
       <c r="B74" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8193,20 +8194,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8221,10 +8222,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>753769</v>
+        <v>753780</v>
       </c>
       <c r="R74" t="n">
-        <v>7218019</v>
+        <v>7217865</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8283,10 +8284,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125023330</v>
+        <v>125023389</v>
       </c>
       <c r="B75" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8295,25 +8296,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8323,10 +8324,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>753730</v>
+        <v>753729</v>
       </c>
       <c r="R75" t="n">
-        <v>7217943</v>
+        <v>7218042</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8385,10 +8386,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125023387</v>
+        <v>125023348</v>
       </c>
       <c r="B76" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8401,21 +8402,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8425,10 +8426,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>753816</v>
+        <v>753817</v>
       </c>
       <c r="R76" t="n">
-        <v>7217838</v>
+        <v>7217853</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8487,10 +8488,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125023443</v>
+        <v>125023347</v>
       </c>
       <c r="B77" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8503,21 +8504,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8527,10 +8528,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>753575</v>
+        <v>753850</v>
       </c>
       <c r="R77" t="n">
-        <v>7217751</v>
+        <v>7217843</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8563,11 +8564,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8594,10 +8590,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125023439</v>
+        <v>125023417</v>
       </c>
       <c r="B78" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8610,21 +8606,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8634,10 +8630,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>753568</v>
+        <v>753474</v>
       </c>
       <c r="R78" t="n">
-        <v>7217716</v>
+        <v>7218026</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8670,11 +8666,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8701,10 +8692,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125023429</v>
+        <v>125023335</v>
       </c>
       <c r="B79" t="n">
-        <v>79926</v>
+        <v>79920</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8717,21 +8708,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8741,10 +8732,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>753792</v>
+        <v>753790</v>
       </c>
       <c r="R79" t="n">
-        <v>7217798</v>
+        <v>7217992</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8803,7 +8794,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125023359</v>
+        <v>125023345</v>
       </c>
       <c r="B80" t="n">
         <v>79891</v>
@@ -8843,10 +8834,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>753753</v>
+        <v>753790</v>
       </c>
       <c r="R80" t="n">
-        <v>7217910</v>
+        <v>7217981</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8905,10 +8896,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125023347</v>
+        <v>125023406</v>
       </c>
       <c r="B81" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8921,21 +8912,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8945,10 +8936,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>753850</v>
+        <v>753718</v>
       </c>
       <c r="R81" t="n">
-        <v>7217843</v>
+        <v>7218042</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9007,10 +8998,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125023369</v>
+        <v>125023380</v>
       </c>
       <c r="B82" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9019,25 +9010,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9047,10 +9038,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>753797</v>
+        <v>753769</v>
       </c>
       <c r="R82" t="n">
-        <v>7218005</v>
+        <v>7218019</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9109,10 +9100,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125023381</v>
+        <v>125023407</v>
       </c>
       <c r="B83" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9121,25 +9112,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9149,10 +9140,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>753722</v>
+        <v>753671</v>
       </c>
       <c r="R83" t="n">
-        <v>7218033</v>
+        <v>7218008</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9211,10 +9202,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125023321</v>
+        <v>125023399</v>
       </c>
       <c r="B84" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9227,21 +9218,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9251,10 +9242,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>753679</v>
+        <v>753751</v>
       </c>
       <c r="R84" t="n">
-        <v>7218005</v>
+        <v>7217806</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9313,10 +9304,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125023318</v>
+        <v>125023325</v>
       </c>
       <c r="B85" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9325,38 +9316,46 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>753680</v>
+        <v>753575</v>
       </c>
       <c r="R85" t="n">
-        <v>7218004</v>
+        <v>7217959</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9389,6 +9388,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9415,10 +9419,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125023404</v>
+        <v>125023395</v>
       </c>
       <c r="B86" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9431,21 +9435,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9455,10 +9459,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>753743</v>
+        <v>753472</v>
       </c>
       <c r="R86" t="n">
-        <v>7218044</v>
+        <v>7218031</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9517,10 +9521,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125023444</v>
+        <v>125023426</v>
       </c>
       <c r="B87" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9533,21 +9537,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9557,10 +9561,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>753746</v>
+        <v>753597</v>
       </c>
       <c r="R87" t="n">
-        <v>7217930</v>
+        <v>7217728</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9593,11 +9597,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9624,10 +9623,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125023407</v>
+        <v>125023342</v>
       </c>
       <c r="B88" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9640,21 +9639,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9664,10 +9663,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>753671</v>
+        <v>753722</v>
       </c>
       <c r="R88" t="n">
-        <v>7218008</v>
+        <v>7217596</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9708,6 +9707,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9726,10 +9726,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125023357</v>
+        <v>125023392</v>
       </c>
       <c r="B89" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9738,25 +9738,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>753793</v>
+        <v>753718</v>
       </c>
       <c r="R89" t="n">
-        <v>7217856</v>
+        <v>7218035</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9828,10 +9828,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125023413</v>
+        <v>125023318</v>
       </c>
       <c r="B90" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9840,25 +9840,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9868,10 +9868,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>753517</v>
+        <v>753680</v>
       </c>
       <c r="R90" t="n">
-        <v>7217918</v>
+        <v>7218004</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9930,10 +9930,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125023403</v>
+        <v>125023323</v>
       </c>
       <c r="B91" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9946,21 +9946,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>753762</v>
+        <v>753504</v>
       </c>
       <c r="R91" t="n">
-        <v>7218015</v>
+        <v>7217889</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10032,10 +10032,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125023391</v>
+        <v>125023359</v>
       </c>
       <c r="B92" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10044,25 +10044,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10072,10 +10072,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>753706</v>
+        <v>753753</v>
       </c>
       <c r="R92" t="n">
-        <v>7218039</v>
+        <v>7217910</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10134,10 +10134,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125023363</v>
+        <v>125023418</v>
       </c>
       <c r="B93" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10150,21 +10150,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10174,10 +10174,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>753782</v>
+        <v>753406</v>
       </c>
       <c r="R93" t="n">
-        <v>7217946</v>
+        <v>7217999</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10236,10 +10236,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125023355</v>
+        <v>125023334</v>
       </c>
       <c r="B94" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10248,25 +10248,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10276,10 +10276,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>753792</v>
+        <v>753752</v>
       </c>
       <c r="R94" t="n">
-        <v>7217850</v>
+        <v>7217919</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10338,10 +10338,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125023390</v>
+        <v>125023409</v>
       </c>
       <c r="B95" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10350,25 +10350,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10378,10 +10378,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>753701</v>
+        <v>753562</v>
       </c>
       <c r="R95" t="n">
-        <v>7218031</v>
+        <v>7217917</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10440,10 +10440,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125023431</v>
+        <v>125023352</v>
       </c>
       <c r="B96" t="n">
-        <v>79926</v>
+        <v>79891</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10452,25 +10452,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10480,10 +10480,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>753774</v>
+        <v>753763</v>
       </c>
       <c r="R96" t="n">
-        <v>7217939</v>
+        <v>7217831</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10542,10 +10542,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125023351</v>
+        <v>125023430</v>
       </c>
       <c r="B97" t="n">
-        <v>79891</v>
+        <v>79926</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10554,25 +10554,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10582,10 +10582,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>753758</v>
+        <v>753789</v>
       </c>
       <c r="R97" t="n">
-        <v>7217819</v>
+        <v>7217809</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY97"/>
+  <dimension ref="A1:AY99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10642,6 +10642,213 @@
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>125023383</v>
+      </c>
+      <c r="B98" t="n">
+        <v>91410</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>753603</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7217932</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>125023317</v>
+      </c>
+      <c r="B99" t="n">
+        <v>78842</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>185</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Fjällboslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>753719</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7217616</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125023375</v>
+        <v>125023389</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753750</v>
+        <v>753729</v>
       </c>
       <c r="R4" t="n">
-        <v>7218028</v>
+        <v>7218042</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125023398</v>
+        <v>125023357</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,41 +1025,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753778</v>
+        <v>753793</v>
       </c>
       <c r="R5" t="n">
-        <v>7217858</v>
+        <v>7217856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,18 +1087,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125023423</v>
+        <v>125023373</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,21 +1127,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1164,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753610</v>
+        <v>753768</v>
       </c>
       <c r="R6" t="n">
-        <v>7217727</v>
+        <v>7218016</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125023343</v>
+        <v>125023409</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1266,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>753760</v>
+        <v>753562</v>
       </c>
       <c r="R7" t="n">
-        <v>7218023</v>
+        <v>7217917</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,18 +1291,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1334,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125023362</v>
+        <v>125023402</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,21 +1331,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,7 +1358,7 @@
         <v>753752</v>
       </c>
       <c r="R8" t="n">
-        <v>7217944</v>
+        <v>7217878</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125023396</v>
+        <v>125023336</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>90962</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,41 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>753626</v>
+        <v>753566</v>
       </c>
       <c r="R9" t="n">
-        <v>7218004</v>
+        <v>7217862</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,18 +1495,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1551,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125023388</v>
+        <v>125023319</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,25 +1531,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1559,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>753742</v>
+        <v>753506</v>
       </c>
       <c r="R10" t="n">
-        <v>7217924</v>
+        <v>7217904</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125023341</v>
+        <v>125023349</v>
       </c>
       <c r="B11" t="n">
-        <v>79919</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,25 +1633,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1661,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>753654</v>
+        <v>753795</v>
       </c>
       <c r="R11" t="n">
-        <v>7218008</v>
+        <v>7217800</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1755,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023435</v>
+        <v>125023378</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,42 +1739,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>753562</v>
+        <v>753722</v>
       </c>
       <c r="R12" t="n">
-        <v>7217727</v>
+        <v>7218033</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,11 +1799,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125023357</v>
+        <v>125023399</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1886,21 +1841,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1910,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753793</v>
+        <v>753751</v>
       </c>
       <c r="R13" t="n">
-        <v>7217856</v>
+        <v>7217806</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1972,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125023446</v>
+        <v>125023435</v>
       </c>
       <c r="B14" t="n">
-        <v>91221</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,38 +1939,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1106</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753567</v>
+        <v>753562</v>
       </c>
       <c r="R14" t="n">
-        <v>7217721</v>
+        <v>7217727</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,13 +2013,17 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färsk bohål</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2075,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125023372</v>
+        <v>125023328</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2091,21 +2058,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2115,10 +2082,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>753790</v>
+        <v>753742</v>
       </c>
       <c r="R15" t="n">
-        <v>7217992</v>
+        <v>7217926</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2177,10 +2144,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125023443</v>
+        <v>125023342</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>78547</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2193,21 +2160,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2217,10 +2184,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753575</v>
+        <v>753722</v>
       </c>
       <c r="R16" t="n">
-        <v>7217751</v>
+        <v>7217596</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,17 +2222,13 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2284,10 +2247,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125023349</v>
+        <v>125023337</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>79795</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2296,25 +2259,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2324,10 +2287,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753795</v>
+        <v>753523</v>
       </c>
       <c r="R17" t="n">
-        <v>7217800</v>
+        <v>7218086</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,7 +2349,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125023351</v>
+        <v>125023366</v>
       </c>
       <c r="B18" t="n">
         <v>79891</v>
@@ -2426,10 +2389,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753758</v>
+        <v>753778</v>
       </c>
       <c r="R18" t="n">
-        <v>7217819</v>
+        <v>7217945</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,7 +2451,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125023442</v>
+        <v>125023445</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2528,10 +2491,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753726</v>
+        <v>753715</v>
       </c>
       <c r="R19" t="n">
-        <v>7218039</v>
+        <v>7218026</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2568,7 +2531,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Barksprätt</t>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2595,10 +2558,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125023326</v>
+        <v>125023381</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>79927</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2607,46 +2570,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753598</v>
+        <v>753722</v>
       </c>
       <c r="R20" t="n">
-        <v>7217744</v>
+        <v>7218033</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2679,11 +2634,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2710,10 +2660,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125023336</v>
+        <v>125023367</v>
       </c>
       <c r="B21" t="n">
-        <v>90962</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2726,21 +2676,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2750,10 +2700,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753566</v>
+        <v>753786</v>
       </c>
       <c r="R21" t="n">
-        <v>7217862</v>
+        <v>7217962</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2914,10 +2864,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125023405</v>
+        <v>125023351</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2930,21 +2880,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2954,10 +2904,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753748</v>
+        <v>753758</v>
       </c>
       <c r="R23" t="n">
-        <v>7218047</v>
+        <v>7217819</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3016,10 +2966,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125023328</v>
+        <v>125023369</v>
       </c>
       <c r="B24" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3032,21 +2982,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3056,10 +3006,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753742</v>
+        <v>753797</v>
       </c>
       <c r="R24" t="n">
-        <v>7217926</v>
+        <v>7218005</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3118,10 +3068,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125023441</v>
+        <v>125023405</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3134,21 +3084,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3158,10 +3108,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753798</v>
+        <v>753748</v>
       </c>
       <c r="R25" t="n">
-        <v>7217948</v>
+        <v>7218047</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3194,11 +3144,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3225,7 +3170,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125023419</v>
+        <v>125023421</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3265,10 +3210,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753550</v>
+        <v>753573</v>
       </c>
       <c r="R26" t="n">
-        <v>7217725</v>
+        <v>7217745</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3327,10 +3272,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125023333</v>
+        <v>125023412</v>
       </c>
       <c r="B27" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3343,21 +3288,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3367,10 +3312,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753781</v>
+        <v>753568</v>
       </c>
       <c r="R27" t="n">
-        <v>7217902</v>
+        <v>7217875</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,10 +3374,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125023368</v>
+        <v>125023426</v>
       </c>
       <c r="B28" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3445,21 +3390,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3469,10 +3414,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753808</v>
+        <v>753597</v>
       </c>
       <c r="R28" t="n">
-        <v>7217964</v>
+        <v>7217728</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,10 +3476,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125023354</v>
+        <v>125023325</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3547,34 +3492,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753773</v>
+        <v>753575</v>
       </c>
       <c r="R29" t="n">
-        <v>7217842</v>
+        <v>7217959</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3607,6 +3560,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3633,7 +3591,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125023444</v>
+        <v>125023439</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -3673,10 +3631,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753746</v>
+        <v>753568</v>
       </c>
       <c r="R30" t="n">
-        <v>7217930</v>
+        <v>7217716</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3713,7 +3671,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Avskalad gran</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3740,10 +3698,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125023321</v>
+        <v>125023444</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3756,21 +3714,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3780,10 +3738,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753679</v>
+        <v>753746</v>
       </c>
       <c r="R31" t="n">
-        <v>7218005</v>
+        <v>7217930</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3816,6 +3774,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3842,10 +3805,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125023378</v>
+        <v>125023330</v>
       </c>
       <c r="B32" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3858,21 +3821,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3882,10 +3845,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753722</v>
+        <v>753730</v>
       </c>
       <c r="R32" t="n">
-        <v>7218033</v>
+        <v>7217943</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3944,10 +3907,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125023429</v>
+        <v>125023333</v>
       </c>
       <c r="B33" t="n">
-        <v>79926</v>
+        <v>57666</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3956,25 +3919,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3984,10 +3947,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753792</v>
+        <v>753781</v>
       </c>
       <c r="R33" t="n">
-        <v>7217798</v>
+        <v>7217902</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4046,7 +4009,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125023374</v>
+        <v>125023368</v>
       </c>
       <c r="B34" t="n">
         <v>79891</v>
@@ -4086,10 +4049,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753763</v>
+        <v>753808</v>
       </c>
       <c r="R34" t="n">
-        <v>7218015</v>
+        <v>7217964</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4148,10 +4111,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125023330</v>
+        <v>125023343</v>
       </c>
       <c r="B35" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4164,21 +4127,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4188,10 +4151,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753730</v>
+        <v>753760</v>
       </c>
       <c r="R35" t="n">
-        <v>7217943</v>
+        <v>7218023</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4226,12 +4189,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4250,10 +4219,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125023394</v>
+        <v>125023362</v>
       </c>
       <c r="B36" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4266,21 +4235,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4290,10 +4259,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753596</v>
+        <v>753752</v>
       </c>
       <c r="R36" t="n">
-        <v>7217939</v>
+        <v>7217944</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4352,7 +4321,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125023403</v>
+        <v>125023418</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4392,10 +4361,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753762</v>
+        <v>753406</v>
       </c>
       <c r="R37" t="n">
-        <v>7218015</v>
+        <v>7217999</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4454,10 +4423,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125023373</v>
+        <v>125023338</v>
       </c>
       <c r="B38" t="n">
-        <v>79891</v>
+        <v>8720</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4466,25 +4435,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100798</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smal trollknäppare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Danosoma conspersum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyllenhal, 1808)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4494,10 +4463,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753768</v>
+        <v>753699</v>
       </c>
       <c r="R38" t="n">
-        <v>7218016</v>
+        <v>7217618</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4538,6 +4507,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4556,10 +4526,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125023414</v>
+        <v>125023318</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4568,25 +4538,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4596,10 +4566,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753630</v>
+        <v>753680</v>
       </c>
       <c r="R39" t="n">
-        <v>7218006</v>
+        <v>7218004</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4658,10 +4628,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125023339</v>
+        <v>125023320</v>
       </c>
       <c r="B40" t="n">
-        <v>92285</v>
+        <v>91012</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4674,37 +4644,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753567</v>
+        <v>753687</v>
       </c>
       <c r="R40" t="n">
-        <v>7217957</v>
+        <v>7217999</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4739,18 +4706,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp. Brunorangt kött uppåt hatten, vitdassigt ner mot foten</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4769,10 +4730,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125023327</v>
+        <v>125023321</v>
       </c>
       <c r="B41" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4785,21 +4746,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4809,10 +4770,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753740</v>
+        <v>753679</v>
       </c>
       <c r="R41" t="n">
-        <v>7217891</v>
+        <v>7218005</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4871,10 +4832,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125023338</v>
+        <v>125023363</v>
       </c>
       <c r="B42" t="n">
-        <v>8720</v>
+        <v>79891</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4883,25 +4844,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100798</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smal trollknäppare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Danosoma conspersum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4911,10 +4872,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753699</v>
+        <v>753782</v>
       </c>
       <c r="R42" t="n">
-        <v>7217618</v>
+        <v>7217946</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4955,7 +4916,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4974,10 +4934,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125023381</v>
+        <v>125023350</v>
       </c>
       <c r="B43" t="n">
-        <v>79927</v>
+        <v>79891</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4986,25 +4946,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5014,10 +4974,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753722</v>
+        <v>753789</v>
       </c>
       <c r="R43" t="n">
-        <v>7218033</v>
+        <v>7217812</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5076,10 +5036,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125023411</v>
+        <v>125023395</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5092,21 +5052,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5116,10 +5076,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753557</v>
+        <v>753472</v>
       </c>
       <c r="R44" t="n">
-        <v>7217895</v>
+        <v>7218031</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5178,10 +5138,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125023434</v>
+        <v>125023323</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5194,42 +5154,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753797</v>
+        <v>753504</v>
       </c>
       <c r="R45" t="n">
-        <v>7217988</v>
+        <v>7217889</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5262,11 +5214,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5293,10 +5240,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125023438</v>
+        <v>125023345</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5309,21 +5256,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5333,10 +5280,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753612</v>
+        <v>753790</v>
       </c>
       <c r="R46" t="n">
-        <v>7217703</v>
+        <v>7217981</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5369,11 +5316,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5400,10 +5342,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125023420</v>
+        <v>125023341</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5412,25 +5354,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5440,10 +5382,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753559</v>
+        <v>753654</v>
       </c>
       <c r="R47" t="n">
-        <v>7217734</v>
+        <v>7218008</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5502,7 +5444,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125023421</v>
+        <v>125023407</v>
       </c>
       <c r="B48" t="n">
         <v>78810</v>
@@ -5542,10 +5484,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753573</v>
+        <v>753671</v>
       </c>
       <c r="R48" t="n">
-        <v>7217745</v>
+        <v>7218008</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5604,10 +5546,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125023320</v>
+        <v>125023441</v>
       </c>
       <c r="B49" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5620,21 +5562,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5644,10 +5586,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753687</v>
+        <v>753798</v>
       </c>
       <c r="R49" t="n">
-        <v>7217999</v>
+        <v>7217948</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5680,6 +5622,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5706,10 +5653,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125023445</v>
+        <v>125023401</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5722,21 +5669,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5746,10 +5693,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753715</v>
+        <v>753780</v>
       </c>
       <c r="R50" t="n">
-        <v>7218026</v>
+        <v>7217865</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5782,11 +5729,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5813,10 +5755,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125023337</v>
+        <v>125023398</v>
       </c>
       <c r="B51" t="n">
-        <v>79795</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5825,38 +5767,45 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753523</v>
+        <v>753778</v>
       </c>
       <c r="R51" t="n">
-        <v>7218086</v>
+        <v>7217858</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5891,12 +5840,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5915,10 +5870,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125023324</v>
+        <v>125023423</v>
       </c>
       <c r="B52" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5931,21 +5886,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5955,10 +5910,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>753480</v>
+        <v>753610</v>
       </c>
       <c r="R52" t="n">
-        <v>7218033</v>
+        <v>7217727</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6017,10 +5972,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125023369</v>
+        <v>125023387</v>
       </c>
       <c r="B53" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6033,21 +5988,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6057,10 +6012,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>753797</v>
+        <v>753816</v>
       </c>
       <c r="R53" t="n">
-        <v>7218005</v>
+        <v>7217838</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6119,10 +6074,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125023358</v>
+        <v>125023391</v>
       </c>
       <c r="B54" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6131,25 +6086,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6159,10 +6114,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753758</v>
+        <v>753706</v>
       </c>
       <c r="R54" t="n">
-        <v>7217900</v>
+        <v>7218039</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6221,10 +6176,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125023315</v>
+        <v>125023358</v>
       </c>
       <c r="B55" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6237,21 +6192,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6261,10 +6216,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753491</v>
+        <v>753758</v>
       </c>
       <c r="R55" t="n">
-        <v>7217766</v>
+        <v>7217900</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6297,11 +6252,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6328,10 +6278,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125023387</v>
+        <v>125023388</v>
       </c>
       <c r="B56" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6340,25 +6290,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6368,10 +6318,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753816</v>
+        <v>753742</v>
       </c>
       <c r="R56" t="n">
-        <v>7217838</v>
+        <v>7217924</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6430,10 +6380,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125023365</v>
+        <v>125023430</v>
       </c>
       <c r="B57" t="n">
-        <v>79891</v>
+        <v>79926</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6442,25 +6392,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6470,10 +6420,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753784</v>
+        <v>753789</v>
       </c>
       <c r="R57" t="n">
-        <v>7217948</v>
+        <v>7217809</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6532,10 +6482,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125023316</v>
+        <v>125023365</v>
       </c>
       <c r="B58" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6548,42 +6498,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753568</v>
+        <v>753784</v>
       </c>
       <c r="R58" t="n">
-        <v>7217733</v>
+        <v>7217948</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6616,11 +6558,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6647,7 +6584,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125023350</v>
+        <v>125023359</v>
       </c>
       <c r="B59" t="n">
         <v>79891</v>
@@ -6687,10 +6624,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753789</v>
+        <v>753753</v>
       </c>
       <c r="R59" t="n">
-        <v>7217812</v>
+        <v>7217910</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6749,10 +6686,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125023439</v>
+        <v>125023347</v>
       </c>
       <c r="B60" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6765,21 +6702,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6789,10 +6726,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753568</v>
+        <v>753850</v>
       </c>
       <c r="R60" t="n">
-        <v>7217716</v>
+        <v>7217843</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6825,11 +6762,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6856,10 +6788,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125023363</v>
+        <v>125023334</v>
       </c>
       <c r="B61" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6868,25 +6800,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6896,10 +6828,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753782</v>
+        <v>753752</v>
       </c>
       <c r="R61" t="n">
-        <v>7217946</v>
+        <v>7217919</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6958,7 +6890,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125023413</v>
+        <v>125023416</v>
       </c>
       <c r="B62" t="n">
         <v>78810</v>
@@ -6998,10 +6930,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753517</v>
+        <v>753470</v>
       </c>
       <c r="R62" t="n">
-        <v>7217918</v>
+        <v>7218024</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7060,10 +6992,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125023391</v>
+        <v>125023326</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7072,38 +7004,46 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753706</v>
+        <v>753598</v>
       </c>
       <c r="R63" t="n">
-        <v>7218039</v>
+        <v>7217744</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7136,6 +7076,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7162,10 +7107,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125023412</v>
+        <v>125023324</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7178,21 +7123,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7202,10 +7147,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753568</v>
+        <v>753480</v>
       </c>
       <c r="R64" t="n">
-        <v>7217875</v>
+        <v>7218033</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7264,10 +7209,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125023432</v>
+        <v>125023354</v>
       </c>
       <c r="B65" t="n">
-        <v>79926</v>
+        <v>79891</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7276,25 +7221,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7304,10 +7249,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753769</v>
+        <v>753773</v>
       </c>
       <c r="R65" t="n">
-        <v>7218019</v>
+        <v>7217842</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7366,10 +7311,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125023319</v>
+        <v>125023404</v>
       </c>
       <c r="B66" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7378,25 +7323,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7406,10 +7351,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753506</v>
+        <v>753743</v>
       </c>
       <c r="R66" t="n">
-        <v>7217904</v>
+        <v>7218044</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7468,10 +7413,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125023366</v>
+        <v>125023432</v>
       </c>
       <c r="B67" t="n">
-        <v>79891</v>
+        <v>79926</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7480,25 +7425,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7508,10 +7453,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753778</v>
+        <v>753769</v>
       </c>
       <c r="R67" t="n">
-        <v>7217945</v>
+        <v>7218019</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7570,10 +7515,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125023404</v>
+        <v>125023375</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7586,21 +7531,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7610,10 +7555,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753743</v>
+        <v>753750</v>
       </c>
       <c r="R68" t="n">
-        <v>7218044</v>
+        <v>7218028</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7672,10 +7617,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125023355</v>
+        <v>125023429</v>
       </c>
       <c r="B69" t="n">
-        <v>79891</v>
+        <v>79926</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7684,25 +7629,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7715,7 +7660,7 @@
         <v>753792</v>
       </c>
       <c r="R69" t="n">
-        <v>7217850</v>
+        <v>7217798</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7774,10 +7719,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125023416</v>
+        <v>125023348</v>
       </c>
       <c r="B70" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7790,21 +7735,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7814,10 +7759,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753470</v>
+        <v>753817</v>
       </c>
       <c r="R70" t="n">
-        <v>7218024</v>
+        <v>7217853</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7876,10 +7821,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125023390</v>
+        <v>125023335</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7888,25 +7833,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7916,10 +7861,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753701</v>
+        <v>753790</v>
       </c>
       <c r="R71" t="n">
-        <v>7218031</v>
+        <v>7217992</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7978,7 +7923,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125023402</v>
+        <v>125023411</v>
       </c>
       <c r="B72" t="n">
         <v>78810</v>
@@ -8018,10 +7963,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753752</v>
+        <v>753557</v>
       </c>
       <c r="R72" t="n">
-        <v>7217878</v>
+        <v>7217895</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8080,10 +8025,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125023367</v>
+        <v>125023327</v>
       </c>
       <c r="B73" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8096,21 +8041,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8120,10 +8065,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>753786</v>
+        <v>753740</v>
       </c>
       <c r="R73" t="n">
-        <v>7217962</v>
+        <v>7217891</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8182,10 +8127,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125023401</v>
+        <v>125023442</v>
       </c>
       <c r="B74" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8198,21 +8143,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8222,10 +8167,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>753780</v>
+        <v>753726</v>
       </c>
       <c r="R74" t="n">
-        <v>7217865</v>
+        <v>7218039</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8258,6 +8203,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8284,10 +8234,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125023389</v>
+        <v>125023420</v>
       </c>
       <c r="B75" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8296,25 +8246,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8324,10 +8274,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>753729</v>
+        <v>753559</v>
       </c>
       <c r="R75" t="n">
-        <v>7218042</v>
+        <v>7217734</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8386,10 +8336,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125023348</v>
+        <v>125023417</v>
       </c>
       <c r="B76" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8402,21 +8352,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8426,10 +8376,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>753817</v>
+        <v>753474</v>
       </c>
       <c r="R76" t="n">
-        <v>7217853</v>
+        <v>7218026</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8488,10 +8438,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125023347</v>
+        <v>125023380</v>
       </c>
       <c r="B77" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8500,25 +8450,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8528,10 +8478,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>753850</v>
+        <v>753769</v>
       </c>
       <c r="R77" t="n">
-        <v>7217843</v>
+        <v>7218019</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8590,10 +8540,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125023417</v>
+        <v>125023446</v>
       </c>
       <c r="B78" t="n">
-        <v>78810</v>
+        <v>91221</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8602,25 +8552,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>1106</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8630,10 +8580,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>753474</v>
+        <v>753567</v>
       </c>
       <c r="R78" t="n">
-        <v>7218026</v>
+        <v>7217721</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8674,6 +8624,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8692,10 +8643,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125023335</v>
+        <v>125023394</v>
       </c>
       <c r="B79" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8704,25 +8655,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8732,10 +8683,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>753790</v>
+        <v>753596</v>
       </c>
       <c r="R79" t="n">
-        <v>7217992</v>
+        <v>7217939</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8794,7 +8745,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125023345</v>
+        <v>125023352</v>
       </c>
       <c r="B80" t="n">
         <v>79891</v>
@@ -8834,10 +8785,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>753790</v>
+        <v>753763</v>
       </c>
       <c r="R80" t="n">
-        <v>7217981</v>
+        <v>7217831</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8896,7 +8847,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125023406</v>
+        <v>125023419</v>
       </c>
       <c r="B81" t="n">
         <v>78810</v>
@@ -8936,10 +8887,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>753718</v>
+        <v>753550</v>
       </c>
       <c r="R81" t="n">
-        <v>7218042</v>
+        <v>7217725</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8998,10 +8949,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125023380</v>
+        <v>125023403</v>
       </c>
       <c r="B82" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9010,25 +8961,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9038,10 +8989,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>753769</v>
+        <v>753762</v>
       </c>
       <c r="R82" t="n">
-        <v>7218019</v>
+        <v>7218015</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9100,7 +9051,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125023407</v>
+        <v>125023414</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -9140,10 +9091,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>753671</v>
+        <v>753630</v>
       </c>
       <c r="R83" t="n">
-        <v>7218008</v>
+        <v>7218006</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9202,7 +9153,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125023399</v>
+        <v>125023396</v>
       </c>
       <c r="B84" t="n">
         <v>78810</v>
@@ -9236,16 +9187,23 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>753751</v>
+        <v>753626</v>
       </c>
       <c r="R84" t="n">
-        <v>7217806</v>
+        <v>7218004</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9280,12 +9238,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9304,7 +9268,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125023325</v>
+        <v>125023443</v>
       </c>
       <c r="B85" t="n">
         <v>57513</v>
@@ -9338,14 +9302,6 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
@@ -9355,7 +9311,7 @@
         <v>753575</v>
       </c>
       <c r="R85" t="n">
-        <v>7217959</v>
+        <v>7217751</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9392,7 +9348,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9419,10 +9375,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125023395</v>
+        <v>125023372</v>
       </c>
       <c r="B86" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9435,21 +9391,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9459,10 +9415,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>753472</v>
+        <v>753790</v>
       </c>
       <c r="R86" t="n">
-        <v>7218031</v>
+        <v>7217992</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9521,10 +9477,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125023426</v>
+        <v>125023374</v>
       </c>
       <c r="B87" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9537,21 +9493,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9561,10 +9517,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>753597</v>
+        <v>753763</v>
       </c>
       <c r="R87" t="n">
-        <v>7217728</v>
+        <v>7218015</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9623,10 +9579,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125023342</v>
+        <v>125023315</v>
       </c>
       <c r="B88" t="n">
-        <v>78547</v>
+        <v>57513</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9639,21 +9595,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9663,10 +9619,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>753722</v>
+        <v>753491</v>
       </c>
       <c r="R88" t="n">
-        <v>7217596</v>
+        <v>7217766</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9701,13 +9657,17 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9828,10 +9788,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125023318</v>
+        <v>125023406</v>
       </c>
       <c r="B90" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9840,25 +9800,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9868,10 +9828,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>753680</v>
+        <v>753718</v>
       </c>
       <c r="R90" t="n">
-        <v>7218004</v>
+        <v>7218042</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9930,10 +9890,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125023323</v>
+        <v>125023339</v>
       </c>
       <c r="B91" t="n">
-        <v>91012</v>
+        <v>92285</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9946,34 +9906,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>753504</v>
+        <v>753567</v>
       </c>
       <c r="R91" t="n">
-        <v>7217889</v>
+        <v>7217957</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10008,12 +9971,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp. Brunorangt kött uppåt hatten, vitdassigt ner mot foten</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10032,10 +10001,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125023359</v>
+        <v>125023434</v>
       </c>
       <c r="B92" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10048,34 +10017,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>753753</v>
+        <v>753797</v>
       </c>
       <c r="R92" t="n">
-        <v>7217910</v>
+        <v>7217988</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10108,6 +10085,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10134,10 +10116,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125023418</v>
+        <v>125023390</v>
       </c>
       <c r="B93" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10146,25 +10128,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10174,10 +10156,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>753406</v>
+        <v>753701</v>
       </c>
       <c r="R93" t="n">
-        <v>7217999</v>
+        <v>7218031</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10236,10 +10218,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125023334</v>
+        <v>125023355</v>
       </c>
       <c r="B94" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10248,25 +10230,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10276,10 +10258,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>753752</v>
+        <v>753792</v>
       </c>
       <c r="R94" t="n">
-        <v>7217919</v>
+        <v>7217850</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10338,7 +10320,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125023409</v>
+        <v>125023413</v>
       </c>
       <c r="B95" t="n">
         <v>78810</v>
@@ -10378,10 +10360,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>753562</v>
+        <v>753517</v>
       </c>
       <c r="R95" t="n">
-        <v>7217917</v>
+        <v>7217918</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10440,10 +10422,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125023352</v>
+        <v>125023438</v>
       </c>
       <c r="B96" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10456,21 +10438,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10480,10 +10462,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>753763</v>
+        <v>753612</v>
       </c>
       <c r="R96" t="n">
-        <v>7217831</v>
+        <v>7217703</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10516,6 +10498,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10542,10 +10529,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125023430</v>
+        <v>125023316</v>
       </c>
       <c r="B97" t="n">
-        <v>79926</v>
+        <v>57513</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10554,38 +10541,46 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>753789</v>
+        <v>753568</v>
       </c>
       <c r="R97" t="n">
-        <v>7217809</v>
+        <v>7217733</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10618,6 +10613,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10644,10 +10644,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125023383</v>
+        <v>125023317</v>
       </c>
       <c r="B98" t="n">
-        <v>91410</v>
+        <v>78842</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10660,16 +10660,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6040186</v>
+        <v>185</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10682,10 +10687,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>753603</v>
+        <v>753719</v>
       </c>
       <c r="R98" t="n">
-        <v>7217932</v>
+        <v>7217616</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10745,10 +10750,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125023317</v>
+        <v>125023383</v>
       </c>
       <c r="B99" t="n">
-        <v>78842</v>
+        <v>91410</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10761,21 +10766,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>185</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>753719</v>
+        <v>753603</v>
       </c>
       <c r="R99" t="n">
-        <v>7217616</v>
+        <v>7217932</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125023389</v>
+        <v>125023357</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753729</v>
+        <v>753793</v>
       </c>
       <c r="R4" t="n">
-        <v>7218042</v>
+        <v>7217856</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125023357</v>
+        <v>125023389</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,25 +1021,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753793</v>
+        <v>753729</v>
       </c>
       <c r="R5" t="n">
-        <v>7217856</v>
+        <v>7218042</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125023373</v>
+        <v>125023409</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,21 +1127,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753768</v>
+        <v>753562</v>
       </c>
       <c r="R6" t="n">
-        <v>7218016</v>
+        <v>7217917</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125023409</v>
+        <v>125023402</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>753562</v>
+        <v>753752</v>
       </c>
       <c r="R7" t="n">
-        <v>7217917</v>
+        <v>7217878</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125023402</v>
+        <v>125023373</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,21 +1331,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>753752</v>
+        <v>753768</v>
       </c>
       <c r="R8" t="n">
-        <v>7217878</v>
+        <v>7218016</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -4009,10 +4009,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125023368</v>
+        <v>125023418</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4025,21 +4025,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4049,10 +4049,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753808</v>
+        <v>753406</v>
       </c>
       <c r="R34" t="n">
-        <v>7217964</v>
+        <v>7217999</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4111,7 +4111,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125023343</v>
+        <v>125023368</v>
       </c>
       <c r="B35" t="n">
         <v>79891</v>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753760</v>
+        <v>753808</v>
       </c>
       <c r="R35" t="n">
-        <v>7218023</v>
+        <v>7217964</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4189,18 +4189,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4219,7 +4213,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125023362</v>
+        <v>125023343</v>
       </c>
       <c r="B36" t="n">
         <v>79891</v>
@@ -4259,10 +4253,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753752</v>
+        <v>753760</v>
       </c>
       <c r="R36" t="n">
-        <v>7217944</v>
+        <v>7218023</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4297,12 +4291,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4321,10 +4321,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125023418</v>
+        <v>125023362</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4337,21 +4337,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4361,10 +4361,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753406</v>
+        <v>753752</v>
       </c>
       <c r="R37" t="n">
-        <v>7217999</v>
+        <v>7217944</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4526,10 +4526,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125023318</v>
+        <v>125023320</v>
       </c>
       <c r="B39" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4538,25 +4538,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4566,10 +4566,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753680</v>
+        <v>753687</v>
       </c>
       <c r="R39" t="n">
-        <v>7218004</v>
+        <v>7217999</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4628,7 +4628,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125023320</v>
+        <v>125023321</v>
       </c>
       <c r="B40" t="n">
         <v>91012</v>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753687</v>
+        <v>753679</v>
       </c>
       <c r="R40" t="n">
-        <v>7217999</v>
+        <v>7218005</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4730,10 +4730,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125023321</v>
+        <v>125023318</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4742,25 +4742,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753679</v>
+        <v>753680</v>
       </c>
       <c r="R41" t="n">
-        <v>7218005</v>
+        <v>7218004</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -8025,10 +8025,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125023327</v>
+        <v>125023442</v>
       </c>
       <c r="B73" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8041,21 +8041,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8065,10 +8065,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>753740</v>
+        <v>753726</v>
       </c>
       <c r="R73" t="n">
-        <v>7217891</v>
+        <v>7218039</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8101,6 +8101,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8127,10 +8132,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125023442</v>
+        <v>125023327</v>
       </c>
       <c r="B74" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8143,21 +8148,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8167,10 +8172,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>753726</v>
+        <v>753740</v>
       </c>
       <c r="R74" t="n">
-        <v>7218039</v>
+        <v>7217891</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8203,11 +8208,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8234,10 +8234,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125023420</v>
+        <v>125023446</v>
       </c>
       <c r="B75" t="n">
-        <v>78810</v>
+        <v>91221</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8246,25 +8246,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1106</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>753559</v>
+        <v>753567</v>
       </c>
       <c r="R75" t="n">
-        <v>7217734</v>
+        <v>7217721</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8318,6 +8318,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8336,7 +8337,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125023417</v>
+        <v>125023420</v>
       </c>
       <c r="B76" t="n">
         <v>78810</v>
@@ -8376,10 +8377,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>753474</v>
+        <v>753559</v>
       </c>
       <c r="R76" t="n">
-        <v>7218026</v>
+        <v>7217734</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8438,10 +8439,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125023380</v>
+        <v>125023417</v>
       </c>
       <c r="B77" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8450,25 +8451,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8478,10 +8479,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>753769</v>
+        <v>753474</v>
       </c>
       <c r="R77" t="n">
-        <v>7218019</v>
+        <v>7218026</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8540,10 +8541,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125023446</v>
+        <v>125023380</v>
       </c>
       <c r="B78" t="n">
-        <v>91221</v>
+        <v>79927</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8552,25 +8553,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1106</v>
+        <v>6464</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8580,10 +8581,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>753567</v>
+        <v>753769</v>
       </c>
       <c r="R78" t="n">
-        <v>7217721</v>
+        <v>7218019</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8624,7 +8625,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125023357</v>
+        <v>125023341</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>79919</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753793</v>
+        <v>753654</v>
       </c>
       <c r="R4" t="n">
-        <v>7217856</v>
+        <v>7218008</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125023389</v>
+        <v>125023432</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,25 +1021,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753729</v>
+        <v>753769</v>
       </c>
       <c r="R5" t="n">
-        <v>7218042</v>
+        <v>7218019</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125023409</v>
+        <v>125023441</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,21 +1127,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753562</v>
+        <v>753798</v>
       </c>
       <c r="R6" t="n">
-        <v>7217917</v>
+        <v>7217948</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,6 +1187,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125023402</v>
+        <v>125023442</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,21 +1234,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>753752</v>
+        <v>753726</v>
       </c>
       <c r="R7" t="n">
-        <v>7217878</v>
+        <v>7218039</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,6 +1294,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125023373</v>
+        <v>125023412</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,21 +1341,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>753768</v>
+        <v>753568</v>
       </c>
       <c r="R8" t="n">
-        <v>7218016</v>
+        <v>7217875</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125023336</v>
+        <v>125023325</v>
       </c>
       <c r="B9" t="n">
-        <v>90962</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,34 +1443,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>753566</v>
+        <v>753575</v>
       </c>
       <c r="R9" t="n">
-        <v>7217862</v>
+        <v>7217959</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,6 +1511,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,10 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125023319</v>
+        <v>125023355</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,25 +1554,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1559,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>753506</v>
+        <v>753792</v>
       </c>
       <c r="R10" t="n">
-        <v>7217904</v>
+        <v>7217850</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125023349</v>
+        <v>125023337</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>79795</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,25 +1656,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1661,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>753795</v>
+        <v>753523</v>
       </c>
       <c r="R11" t="n">
-        <v>7217800</v>
+        <v>7218086</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1746,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023378</v>
+        <v>125023347</v>
       </c>
       <c r="B12" t="n">
         <v>79891</v>
@@ -1763,10 +1786,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>753722</v>
+        <v>753850</v>
       </c>
       <c r="R12" t="n">
-        <v>7218033</v>
+        <v>7217843</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125023399</v>
+        <v>125023349</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1841,21 +1864,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1865,10 +1888,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753751</v>
+        <v>753795</v>
       </c>
       <c r="R13" t="n">
-        <v>7217806</v>
+        <v>7217800</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,10 +1950,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125023435</v>
+        <v>125023333</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1943,42 +1966,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753562</v>
+        <v>753781</v>
       </c>
       <c r="R14" t="n">
-        <v>7217727</v>
+        <v>7217902</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,11 +2026,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,10 +2052,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125023328</v>
+        <v>125023399</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2058,21 +2068,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2082,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>753742</v>
+        <v>753751</v>
       </c>
       <c r="R15" t="n">
-        <v>7217926</v>
+        <v>7217806</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2144,10 +2154,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125023342</v>
+        <v>125023327</v>
       </c>
       <c r="B16" t="n">
-        <v>78547</v>
+        <v>57666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2160,21 +2170,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2184,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753722</v>
+        <v>753740</v>
       </c>
       <c r="R16" t="n">
-        <v>7217596</v>
+        <v>7217891</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,7 +2238,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2247,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125023337</v>
+        <v>125023336</v>
       </c>
       <c r="B17" t="n">
-        <v>79795</v>
+        <v>90962</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2259,25 +2268,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>112</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2287,10 +2296,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753523</v>
+        <v>753566</v>
       </c>
       <c r="R17" t="n">
-        <v>7218086</v>
+        <v>7217862</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,10 +2358,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125023366</v>
+        <v>125023388</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2361,25 +2370,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2389,10 +2398,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753778</v>
+        <v>753742</v>
       </c>
       <c r="R18" t="n">
-        <v>7217945</v>
+        <v>7217924</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2451,10 +2460,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125023445</v>
+        <v>125023359</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2467,21 +2476,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2491,10 +2500,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753715</v>
+        <v>753753</v>
       </c>
       <c r="R19" t="n">
-        <v>7218026</v>
+        <v>7217910</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2527,11 +2536,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2558,10 +2562,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125023381</v>
+        <v>125023352</v>
       </c>
       <c r="B20" t="n">
-        <v>79927</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2570,25 +2574,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2598,10 +2602,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753722</v>
+        <v>753763</v>
       </c>
       <c r="R20" t="n">
-        <v>7218033</v>
+        <v>7217831</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2660,10 +2664,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125023367</v>
+        <v>125023315</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2676,21 +2680,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,10 +2704,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753786</v>
+        <v>753491</v>
       </c>
       <c r="R21" t="n">
-        <v>7217962</v>
+        <v>7217766</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2736,6 +2740,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2762,10 +2771,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125023431</v>
+        <v>125023405</v>
       </c>
       <c r="B22" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2774,20 +2783,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2802,10 +2811,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753774</v>
+        <v>753748</v>
       </c>
       <c r="R22" t="n">
-        <v>7217939</v>
+        <v>7218047</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2864,10 +2873,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125023351</v>
+        <v>125023417</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2880,21 +2889,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2904,10 +2913,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753758</v>
+        <v>753474</v>
       </c>
       <c r="R23" t="n">
-        <v>7217819</v>
+        <v>7218026</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2966,10 +2975,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125023369</v>
+        <v>125023394</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2982,21 +2991,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3006,10 +3015,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753797</v>
+        <v>753596</v>
       </c>
       <c r="R24" t="n">
-        <v>7218005</v>
+        <v>7217939</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3068,10 +3077,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125023405</v>
+        <v>125023381</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3080,25 +3089,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3108,10 +3117,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753748</v>
+        <v>753722</v>
       </c>
       <c r="R25" t="n">
-        <v>7218047</v>
+        <v>7218033</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3170,7 +3179,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125023421</v>
+        <v>125023398</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3204,16 +3213,23 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753573</v>
+        <v>753778</v>
       </c>
       <c r="R26" t="n">
-        <v>7217745</v>
+        <v>7217858</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3248,12 +3264,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3272,10 +3294,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125023412</v>
+        <v>125023326</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3288,34 +3310,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753568</v>
+        <v>753598</v>
       </c>
       <c r="R27" t="n">
-        <v>7217875</v>
+        <v>7217744</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3348,6 +3378,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3374,10 +3409,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125023426</v>
+        <v>125023342</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3390,21 +3425,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3414,10 +3449,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753597</v>
+        <v>753722</v>
       </c>
       <c r="R28" t="n">
-        <v>7217728</v>
+        <v>7217596</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3458,6 +3493,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3476,10 +3512,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125023325</v>
+        <v>125023330</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3492,42 +3528,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753575</v>
+        <v>753730</v>
       </c>
       <c r="R29" t="n">
-        <v>7217959</v>
+        <v>7217943</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3560,11 +3588,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3698,10 +3721,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125023444</v>
+        <v>125023446</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>91221</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3710,25 +3733,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1106</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3738,10 +3761,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753746</v>
+        <v>753567</v>
       </c>
       <c r="R31" t="n">
-        <v>7217930</v>
+        <v>7217721</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3776,17 +3799,13 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3805,10 +3824,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125023330</v>
+        <v>125023429</v>
       </c>
       <c r="B32" t="n">
-        <v>57666</v>
+        <v>79926</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3817,25 +3836,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3845,10 +3864,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753730</v>
+        <v>753792</v>
       </c>
       <c r="R32" t="n">
-        <v>7217943</v>
+        <v>7217798</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3907,10 +3926,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125023333</v>
+        <v>125023380</v>
       </c>
       <c r="B33" t="n">
-        <v>57666</v>
+        <v>79927</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3919,25 +3938,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3947,10 +3966,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753781</v>
+        <v>753769</v>
       </c>
       <c r="R33" t="n">
-        <v>7217902</v>
+        <v>7218019</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4009,7 +4028,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125023418</v>
+        <v>125023413</v>
       </c>
       <c r="B34" t="n">
         <v>78810</v>
@@ -4049,10 +4068,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753406</v>
+        <v>753517</v>
       </c>
       <c r="R34" t="n">
-        <v>7217999</v>
+        <v>7217918</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4111,10 +4130,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125023368</v>
+        <v>125023404</v>
       </c>
       <c r="B35" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4127,21 +4146,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4151,10 +4170,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753808</v>
+        <v>753743</v>
       </c>
       <c r="R35" t="n">
-        <v>7217964</v>
+        <v>7218044</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4213,10 +4232,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125023343</v>
+        <v>125023338</v>
       </c>
       <c r="B36" t="n">
-        <v>79891</v>
+        <v>8720</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4225,25 +4244,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100798</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smal trollknäppare</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Danosoma conspersum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyllenhal, 1808)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4253,10 +4272,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753760</v>
+        <v>753699</v>
       </c>
       <c r="R36" t="n">
-        <v>7218023</v>
+        <v>7217618</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4289,11 +4308,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4321,7 +4335,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125023362</v>
+        <v>125023351</v>
       </c>
       <c r="B37" t="n">
         <v>79891</v>
@@ -4361,10 +4375,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753752</v>
+        <v>753758</v>
       </c>
       <c r="R37" t="n">
-        <v>7217944</v>
+        <v>7217819</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4423,10 +4437,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125023338</v>
+        <v>125023350</v>
       </c>
       <c r="B38" t="n">
-        <v>8720</v>
+        <v>79891</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4435,25 +4449,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100798</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Smal trollknäppare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Danosoma conspersum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4463,10 +4477,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753699</v>
+        <v>753789</v>
       </c>
       <c r="R38" t="n">
-        <v>7217618</v>
+        <v>7217812</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4507,7 +4521,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4526,10 +4539,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125023320</v>
+        <v>125023366</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4542,21 +4555,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4566,10 +4579,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753687</v>
+        <v>753778</v>
       </c>
       <c r="R39" t="n">
-        <v>7217999</v>
+        <v>7217945</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4628,10 +4641,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125023321</v>
+        <v>125023414</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4644,21 +4657,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4668,10 +4681,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753679</v>
+        <v>753630</v>
       </c>
       <c r="R40" t="n">
-        <v>7218005</v>
+        <v>7218006</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4730,10 +4743,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125023318</v>
+        <v>125023389</v>
       </c>
       <c r="B41" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4742,25 +4755,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4770,10 +4783,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753680</v>
+        <v>753729</v>
       </c>
       <c r="R41" t="n">
-        <v>7218004</v>
+        <v>7218042</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4832,10 +4845,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125023363</v>
+        <v>125023392</v>
       </c>
       <c r="B42" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4844,25 +4857,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4872,10 +4885,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753782</v>
+        <v>753718</v>
       </c>
       <c r="R42" t="n">
-        <v>7217946</v>
+        <v>7218035</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4934,10 +4947,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125023350</v>
+        <v>125023426</v>
       </c>
       <c r="B43" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4950,21 +4963,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4974,10 +4987,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753789</v>
+        <v>753597</v>
       </c>
       <c r="R43" t="n">
-        <v>7217812</v>
+        <v>7217728</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5036,10 +5049,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125023395</v>
+        <v>125023324</v>
       </c>
       <c r="B44" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5052,21 +5065,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5076,10 +5089,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753472</v>
+        <v>753480</v>
       </c>
       <c r="R44" t="n">
-        <v>7218031</v>
+        <v>7218033</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5138,10 +5151,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125023323</v>
+        <v>125023365</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5154,21 +5167,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5178,10 +5191,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753504</v>
+        <v>753784</v>
       </c>
       <c r="R45" t="n">
-        <v>7217889</v>
+        <v>7217948</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5240,7 +5253,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125023345</v>
+        <v>125023357</v>
       </c>
       <c r="B46" t="n">
         <v>79891</v>
@@ -5280,10 +5293,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753790</v>
+        <v>753793</v>
       </c>
       <c r="R46" t="n">
-        <v>7217981</v>
+        <v>7217856</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5342,10 +5355,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125023341</v>
+        <v>125023420</v>
       </c>
       <c r="B47" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5354,25 +5367,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5382,10 +5395,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753654</v>
+        <v>753559</v>
       </c>
       <c r="R47" t="n">
-        <v>7218008</v>
+        <v>7217734</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5444,7 +5457,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125023407</v>
+        <v>125023423</v>
       </c>
       <c r="B48" t="n">
         <v>78810</v>
@@ -5484,10 +5497,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753671</v>
+        <v>753610</v>
       </c>
       <c r="R48" t="n">
-        <v>7218008</v>
+        <v>7217727</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5546,10 +5559,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125023441</v>
+        <v>125023374</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5562,21 +5575,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5586,10 +5599,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753798</v>
+        <v>753763</v>
       </c>
       <c r="R49" t="n">
-        <v>7217948</v>
+        <v>7218015</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5622,11 +5635,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5653,10 +5661,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125023401</v>
+        <v>125023354</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5669,21 +5677,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5693,10 +5701,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753780</v>
+        <v>753773</v>
       </c>
       <c r="R50" t="n">
-        <v>7217865</v>
+        <v>7217842</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5755,7 +5763,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125023398</v>
+        <v>125023402</v>
       </c>
       <c r="B51" t="n">
         <v>78810</v>
@@ -5789,23 +5797,16 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753778</v>
+        <v>753752</v>
       </c>
       <c r="R51" t="n">
-        <v>7217858</v>
+        <v>7217878</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5840,18 +5841,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5870,7 +5865,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125023423</v>
+        <v>125023396</v>
       </c>
       <c r="B52" t="n">
         <v>78810</v>
@@ -5904,16 +5899,23 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>753610</v>
+        <v>753626</v>
       </c>
       <c r="R52" t="n">
-        <v>7217727</v>
+        <v>7218004</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5948,12 +5950,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5972,10 +5980,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125023387</v>
+        <v>125023323</v>
       </c>
       <c r="B53" t="n">
-        <v>78546</v>
+        <v>91012</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5988,21 +5996,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6012,10 +6020,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>753816</v>
+        <v>753504</v>
       </c>
       <c r="R53" t="n">
-        <v>7217838</v>
+        <v>7217889</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6074,10 +6082,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125023391</v>
+        <v>125023345</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6086,25 +6094,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6114,10 +6122,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753706</v>
+        <v>753790</v>
       </c>
       <c r="R54" t="n">
-        <v>7218039</v>
+        <v>7217981</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6176,10 +6184,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125023358</v>
+        <v>125023334</v>
       </c>
       <c r="B55" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6188,25 +6196,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6216,10 +6224,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753758</v>
+        <v>753752</v>
       </c>
       <c r="R55" t="n">
-        <v>7217900</v>
+        <v>7217919</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6278,10 +6286,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125023388</v>
+        <v>125023367</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6290,25 +6298,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6318,10 +6326,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753742</v>
+        <v>753786</v>
       </c>
       <c r="R56" t="n">
-        <v>7217924</v>
+        <v>7217962</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6380,10 +6388,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125023430</v>
+        <v>125023343</v>
       </c>
       <c r="B57" t="n">
-        <v>79926</v>
+        <v>79891</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6392,25 +6400,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6420,10 +6428,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753789</v>
+        <v>753760</v>
       </c>
       <c r="R57" t="n">
-        <v>7217809</v>
+        <v>7218023</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6458,12 +6466,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6482,10 +6496,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125023365</v>
+        <v>125023390</v>
       </c>
       <c r="B58" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6494,25 +6508,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6522,10 +6536,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753784</v>
+        <v>753701</v>
       </c>
       <c r="R58" t="n">
-        <v>7217948</v>
+        <v>7218031</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6584,10 +6598,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125023359</v>
+        <v>125023418</v>
       </c>
       <c r="B59" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6600,21 +6614,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6624,10 +6638,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753753</v>
+        <v>753406</v>
       </c>
       <c r="R59" t="n">
-        <v>7217910</v>
+        <v>7217999</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6686,10 +6700,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125023347</v>
+        <v>125023318</v>
       </c>
       <c r="B60" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6698,25 +6712,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6726,10 +6740,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753850</v>
+        <v>753680</v>
       </c>
       <c r="R60" t="n">
-        <v>7217843</v>
+        <v>7218004</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6788,10 +6802,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125023334</v>
+        <v>125023419</v>
       </c>
       <c r="B61" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6800,25 +6814,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6828,10 +6842,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753752</v>
+        <v>753550</v>
       </c>
       <c r="R61" t="n">
-        <v>7217919</v>
+        <v>7217725</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6890,10 +6904,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125023416</v>
+        <v>125023443</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6906,21 +6920,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6930,10 +6944,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753470</v>
+        <v>753575</v>
       </c>
       <c r="R62" t="n">
-        <v>7218024</v>
+        <v>7217751</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6966,6 +6980,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6992,10 +7011,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125023326</v>
+        <v>125023320</v>
       </c>
       <c r="B63" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7008,42 +7027,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753598</v>
+        <v>753687</v>
       </c>
       <c r="R63" t="n">
-        <v>7217744</v>
+        <v>7217999</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7076,11 +7087,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7107,10 +7113,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125023324</v>
+        <v>125023348</v>
       </c>
       <c r="B64" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7123,21 +7129,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7147,10 +7153,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753480</v>
+        <v>753817</v>
       </c>
       <c r="R64" t="n">
-        <v>7218033</v>
+        <v>7217853</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7209,7 +7215,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125023354</v>
+        <v>125023368</v>
       </c>
       <c r="B65" t="n">
         <v>79891</v>
@@ -7249,10 +7255,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753773</v>
+        <v>753808</v>
       </c>
       <c r="R65" t="n">
-        <v>7217842</v>
+        <v>7217964</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7311,10 +7317,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125023404</v>
+        <v>125023373</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7327,21 +7333,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7351,10 +7357,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753743</v>
+        <v>753768</v>
       </c>
       <c r="R66" t="n">
-        <v>7218044</v>
+        <v>7218016</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7413,10 +7419,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125023432</v>
+        <v>125023411</v>
       </c>
       <c r="B67" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7425,20 +7431,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7453,10 +7459,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753769</v>
+        <v>753557</v>
       </c>
       <c r="R67" t="n">
-        <v>7218019</v>
+        <v>7217895</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7515,10 +7521,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125023375</v>
+        <v>125023416</v>
       </c>
       <c r="B68" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7531,21 +7537,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7555,10 +7561,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753750</v>
+        <v>753470</v>
       </c>
       <c r="R68" t="n">
-        <v>7218028</v>
+        <v>7218024</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7617,10 +7623,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125023429</v>
+        <v>125023403</v>
       </c>
       <c r="B69" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7629,20 +7635,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7657,10 +7663,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753792</v>
+        <v>753762</v>
       </c>
       <c r="R69" t="n">
-        <v>7217798</v>
+        <v>7218015</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7719,10 +7725,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125023348</v>
+        <v>125023434</v>
       </c>
       <c r="B70" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7735,34 +7741,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753817</v>
+        <v>753797</v>
       </c>
       <c r="R70" t="n">
-        <v>7217853</v>
+        <v>7217988</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7795,6 +7809,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7821,10 +7840,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125023335</v>
+        <v>125023445</v>
       </c>
       <c r="B71" t="n">
-        <v>79920</v>
+        <v>57513</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7833,25 +7852,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7861,10 +7880,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753790</v>
+        <v>753715</v>
       </c>
       <c r="R71" t="n">
-        <v>7217992</v>
+        <v>7218026</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7897,6 +7916,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7923,10 +7947,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125023411</v>
+        <v>125023435</v>
       </c>
       <c r="B72" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7939,34 +7963,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753557</v>
+        <v>753562</v>
       </c>
       <c r="R72" t="n">
-        <v>7217895</v>
+        <v>7217727</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7999,6 +8031,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8025,10 +8062,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125023442</v>
+        <v>125023358</v>
       </c>
       <c r="B73" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8041,21 +8078,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8065,10 +8102,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>753726</v>
+        <v>753758</v>
       </c>
       <c r="R73" t="n">
-        <v>7218039</v>
+        <v>7217900</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8101,11 +8138,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8132,10 +8164,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125023327</v>
+        <v>125023378</v>
       </c>
       <c r="B74" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8148,21 +8180,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8172,10 +8204,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>753740</v>
+        <v>753722</v>
       </c>
       <c r="R74" t="n">
-        <v>7217891</v>
+        <v>7218033</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8234,10 +8266,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125023446</v>
+        <v>125023360</v>
       </c>
       <c r="B75" t="n">
-        <v>91221</v>
+        <v>79891</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8246,25 +8278,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1106</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8274,10 +8306,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>753567</v>
+        <v>753752</v>
       </c>
       <c r="R75" t="n">
-        <v>7217721</v>
+        <v>7217944</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8318,7 +8350,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8337,10 +8368,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125023420</v>
+        <v>125023391</v>
       </c>
       <c r="B76" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8349,25 +8380,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8377,10 +8408,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>753559</v>
+        <v>753706</v>
       </c>
       <c r="R76" t="n">
-        <v>7217734</v>
+        <v>7218039</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8439,10 +8470,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125023417</v>
+        <v>125023321</v>
       </c>
       <c r="B77" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8455,21 +8486,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8479,10 +8510,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>753474</v>
+        <v>753679</v>
       </c>
       <c r="R77" t="n">
-        <v>7218026</v>
+        <v>7218005</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8541,10 +8572,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125023380</v>
+        <v>125023372</v>
       </c>
       <c r="B78" t="n">
-        <v>79927</v>
+        <v>79891</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8553,25 +8584,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8581,10 +8612,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>753769</v>
+        <v>753790</v>
       </c>
       <c r="R78" t="n">
-        <v>7218019</v>
+        <v>7217992</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8643,7 +8674,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125023394</v>
+        <v>125023395</v>
       </c>
       <c r="B79" t="n">
         <v>91030</v>
@@ -8683,10 +8714,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>753596</v>
+        <v>753472</v>
       </c>
       <c r="R79" t="n">
-        <v>7217939</v>
+        <v>7218031</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8745,10 +8776,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125023352</v>
+        <v>125023409</v>
       </c>
       <c r="B80" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8761,21 +8792,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8785,10 +8816,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>753763</v>
+        <v>753562</v>
       </c>
       <c r="R80" t="n">
-        <v>7217831</v>
+        <v>7217917</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8847,7 +8878,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125023419</v>
+        <v>125023407</v>
       </c>
       <c r="B81" t="n">
         <v>78810</v>
@@ -8887,10 +8918,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>753550</v>
+        <v>753671</v>
       </c>
       <c r="R81" t="n">
-        <v>7217725</v>
+        <v>7218008</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8949,10 +8980,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125023403</v>
+        <v>125023438</v>
       </c>
       <c r="B82" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8965,21 +8996,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8989,10 +9020,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>753762</v>
+        <v>753612</v>
       </c>
       <c r="R82" t="n">
-        <v>7218015</v>
+        <v>7217703</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9025,6 +9056,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9051,7 +9087,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125023414</v>
+        <v>125023401</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -9091,10 +9127,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>753630</v>
+        <v>753780</v>
       </c>
       <c r="R83" t="n">
-        <v>7218006</v>
+        <v>7217865</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9153,10 +9189,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125023396</v>
+        <v>125023335</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9165,45 +9201,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>753626</v>
+        <v>753790</v>
       </c>
       <c r="R84" t="n">
-        <v>7218004</v>
+        <v>7217992</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9238,18 +9267,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9268,10 +9291,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125023443</v>
+        <v>125023375</v>
       </c>
       <c r="B85" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9284,21 +9307,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9308,10 +9331,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>753575</v>
+        <v>753750</v>
       </c>
       <c r="R85" t="n">
-        <v>7217751</v>
+        <v>7218028</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9344,11 +9367,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9375,7 +9393,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125023372</v>
+        <v>125023369</v>
       </c>
       <c r="B86" t="n">
         <v>79891</v>
@@ -9415,10 +9433,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>753790</v>
+        <v>753797</v>
       </c>
       <c r="R86" t="n">
-        <v>7217992</v>
+        <v>7218005</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9477,10 +9495,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125023374</v>
+        <v>125023316</v>
       </c>
       <c r="B87" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9493,34 +9511,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>753763</v>
+        <v>753568</v>
       </c>
       <c r="R87" t="n">
-        <v>7218015</v>
+        <v>7217733</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9553,6 +9579,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9579,7 +9610,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125023315</v>
+        <v>125023444</v>
       </c>
       <c r="B88" t="n">
         <v>57513</v>
@@ -9619,10 +9650,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>753491</v>
+        <v>753746</v>
       </c>
       <c r="R88" t="n">
-        <v>7217766</v>
+        <v>7217930</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9659,7 +9690,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9686,10 +9717,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125023392</v>
+        <v>125023421</v>
       </c>
       <c r="B89" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9698,25 +9729,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9726,10 +9757,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>753718</v>
+        <v>753573</v>
       </c>
       <c r="R89" t="n">
-        <v>7218035</v>
+        <v>7217745</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9890,10 +9921,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125023339</v>
+        <v>125023387</v>
       </c>
       <c r="B91" t="n">
-        <v>92285</v>
+        <v>78546</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9906,37 +9937,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>753567</v>
+        <v>753816</v>
       </c>
       <c r="R91" t="n">
-        <v>7217957</v>
+        <v>7217838</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9971,18 +9999,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp. Brunorangt kött uppåt hatten, vitdassigt ner mot foten</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10001,10 +10023,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125023434</v>
+        <v>125023328</v>
       </c>
       <c r="B92" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10017,42 +10039,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>753797</v>
+        <v>753742</v>
       </c>
       <c r="R92" t="n">
-        <v>7217988</v>
+        <v>7217926</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10085,11 +10099,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10116,10 +10125,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125023390</v>
+        <v>125023431</v>
       </c>
       <c r="B93" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10128,25 +10137,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10156,10 +10165,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>753701</v>
+        <v>753774</v>
       </c>
       <c r="R93" t="n">
-        <v>7218031</v>
+        <v>7217939</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10218,10 +10227,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125023355</v>
+        <v>125023339</v>
       </c>
       <c r="B94" t="n">
-        <v>79891</v>
+        <v>92285</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10234,34 +10243,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>4361</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>753792</v>
+        <v>753567</v>
       </c>
       <c r="R94" t="n">
-        <v>7217850</v>
+        <v>7217957</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10296,12 +10308,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp. Brunorangt kött uppåt hatten, vitdassigt ner mot foten</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10320,10 +10338,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125023413</v>
+        <v>125023363</v>
       </c>
       <c r="B95" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10336,21 +10354,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10360,10 +10378,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>753517</v>
+        <v>753782</v>
       </c>
       <c r="R95" t="n">
-        <v>7217918</v>
+        <v>7217946</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10422,10 +10440,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125023438</v>
+        <v>125023430</v>
       </c>
       <c r="B96" t="n">
-        <v>57513</v>
+        <v>79926</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10434,25 +10452,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10462,10 +10480,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>753612</v>
+        <v>753789</v>
       </c>
       <c r="R96" t="n">
-        <v>7217703</v>
+        <v>7217809</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10498,11 +10516,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10529,10 +10542,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125023316</v>
+        <v>125023319</v>
       </c>
       <c r="B97" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10541,46 +10554,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>753568</v>
+        <v>753506</v>
       </c>
       <c r="R97" t="n">
-        <v>7217733</v>
+        <v>7217904</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10613,11 +10618,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10644,10 +10644,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125023317</v>
+        <v>125023383</v>
       </c>
       <c r="B98" t="n">
-        <v>78842</v>
+        <v>91410</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10660,21 +10660,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>185</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10687,10 +10682,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>753719</v>
+        <v>753603</v>
       </c>
       <c r="R98" t="n">
-        <v>7217616</v>
+        <v>7217932</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10750,10 +10745,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125023383</v>
+        <v>125023317</v>
       </c>
       <c r="B99" t="n">
-        <v>91410</v>
+        <v>78842</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10766,16 +10761,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6040186</v>
+        <v>185</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>753603</v>
+        <v>753719</v>
       </c>
       <c r="R99" t="n">
-        <v>7217932</v>
+        <v>7217616</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125023341</v>
+        <v>125023355</v>
       </c>
       <c r="B4" t="n">
-        <v>79919</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753654</v>
+        <v>753792</v>
       </c>
       <c r="R4" t="n">
-        <v>7218008</v>
+        <v>7217850</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125023432</v>
+        <v>125023367</v>
       </c>
       <c r="B5" t="n">
-        <v>79926</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,25 +1021,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753769</v>
+        <v>753786</v>
       </c>
       <c r="R5" t="n">
-        <v>7218019</v>
+        <v>7217962</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125023441</v>
+        <v>125023420</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,21 +1127,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753798</v>
+        <v>753559</v>
       </c>
       <c r="R6" t="n">
-        <v>7217948</v>
+        <v>7217734</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,11 +1187,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125023442</v>
+        <v>125023327</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1258,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>753726</v>
+        <v>753740</v>
       </c>
       <c r="R7" t="n">
-        <v>7218039</v>
+        <v>7217891</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,11 +1289,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,7 +1315,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125023412</v>
+        <v>125023403</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1365,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>753568</v>
+        <v>753762</v>
       </c>
       <c r="R8" t="n">
-        <v>7217875</v>
+        <v>7218015</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125023355</v>
+        <v>125023445</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,21 +1548,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1582,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>753792</v>
+        <v>753715</v>
       </c>
       <c r="R10" t="n">
-        <v>7217850</v>
+        <v>7218026</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,6 +1608,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125023337</v>
+        <v>125023328</v>
       </c>
       <c r="B11" t="n">
-        <v>79795</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>753523</v>
+        <v>753742</v>
       </c>
       <c r="R11" t="n">
-        <v>7218086</v>
+        <v>7217926</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,7 +1741,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023347</v>
+        <v>125023362</v>
       </c>
       <c r="B12" t="n">
         <v>79891</v>
@@ -1786,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>753850</v>
+        <v>753752</v>
       </c>
       <c r="R12" t="n">
-        <v>7217843</v>
+        <v>7217944</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125023349</v>
+        <v>125023443</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1864,21 +1859,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1888,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753795</v>
+        <v>753575</v>
       </c>
       <c r="R13" t="n">
-        <v>7217800</v>
+        <v>7217751</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,6 +1919,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1950,10 +1950,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125023333</v>
+        <v>125023363</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1966,21 +1966,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753781</v>
+        <v>753782</v>
       </c>
       <c r="R14" t="n">
-        <v>7217902</v>
+        <v>7217946</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,10 +2052,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125023399</v>
+        <v>125023354</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2068,21 +2068,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>753751</v>
+        <v>753773</v>
       </c>
       <c r="R15" t="n">
-        <v>7217806</v>
+        <v>7217842</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2154,10 +2154,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125023327</v>
+        <v>125023359</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2170,21 +2170,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753740</v>
+        <v>753753</v>
       </c>
       <c r="R16" t="n">
-        <v>7217891</v>
+        <v>7217910</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125023336</v>
+        <v>125023335</v>
       </c>
       <c r="B17" t="n">
-        <v>90962</v>
+        <v>79920</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2268,25 +2268,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753566</v>
+        <v>753790</v>
       </c>
       <c r="R17" t="n">
-        <v>7217862</v>
+        <v>7217992</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2358,10 +2358,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125023388</v>
+        <v>125023351</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2370,25 +2370,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753742</v>
+        <v>753758</v>
       </c>
       <c r="R18" t="n">
-        <v>7217924</v>
+        <v>7217819</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125023359</v>
+        <v>125023343</v>
       </c>
       <c r="B19" t="n">
         <v>79891</v>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753753</v>
+        <v>753760</v>
       </c>
       <c r="R19" t="n">
-        <v>7217910</v>
+        <v>7218023</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2538,12 +2538,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2562,10 +2568,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125023352</v>
+        <v>125023399</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2578,21 +2584,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2602,10 +2608,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753763</v>
+        <v>753751</v>
       </c>
       <c r="R20" t="n">
-        <v>7217831</v>
+        <v>7217806</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,10 +2670,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125023315</v>
+        <v>125023342</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>78547</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2680,21 +2686,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2704,10 +2710,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753491</v>
+        <v>753722</v>
       </c>
       <c r="R21" t="n">
-        <v>7217766</v>
+        <v>7217596</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2742,17 +2748,13 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2771,10 +2773,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125023405</v>
+        <v>125023391</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2783,25 +2785,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2811,10 +2813,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753748</v>
+        <v>753706</v>
       </c>
       <c r="R22" t="n">
-        <v>7218047</v>
+        <v>7218039</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2873,10 +2875,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125023417</v>
+        <v>125023434</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2889,34 +2891,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753474</v>
+        <v>753797</v>
       </c>
       <c r="R23" t="n">
-        <v>7218026</v>
+        <v>7217988</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2949,6 +2959,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2975,10 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125023394</v>
+        <v>125023398</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2991,34 +3006,41 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753596</v>
+        <v>753778</v>
       </c>
       <c r="R24" t="n">
-        <v>7217939</v>
+        <v>7217858</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3053,12 +3075,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3077,10 +3105,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125023381</v>
+        <v>125023414</v>
       </c>
       <c r="B25" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3089,25 +3117,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3117,10 +3145,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753722</v>
+        <v>753630</v>
       </c>
       <c r="R25" t="n">
-        <v>7218033</v>
+        <v>7218006</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,10 +3207,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125023398</v>
+        <v>125023341</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3191,45 +3219,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753778</v>
+        <v>753654</v>
       </c>
       <c r="R26" t="n">
-        <v>7217858</v>
+        <v>7218008</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3264,18 +3285,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3294,10 +3309,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125023326</v>
+        <v>125023365</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3310,42 +3325,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753598</v>
+        <v>753784</v>
       </c>
       <c r="R27" t="n">
-        <v>7217744</v>
+        <v>7217948</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3378,11 +3385,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3409,10 +3411,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125023342</v>
+        <v>125023368</v>
       </c>
       <c r="B28" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3425,21 +3427,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,10 +3451,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753722</v>
+        <v>753808</v>
       </c>
       <c r="R28" t="n">
-        <v>7217596</v>
+        <v>7217964</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3493,7 +3495,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3512,10 +3513,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125023330</v>
+        <v>125023401</v>
       </c>
       <c r="B29" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3528,21 +3529,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3552,10 +3553,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753730</v>
+        <v>753780</v>
       </c>
       <c r="R29" t="n">
-        <v>7217943</v>
+        <v>7217865</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,10 +3615,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125023439</v>
+        <v>125023406</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3630,21 +3631,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3654,10 +3655,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753568</v>
+        <v>753718</v>
       </c>
       <c r="R30" t="n">
-        <v>7217716</v>
+        <v>7218042</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3690,11 +3691,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3721,10 +3717,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125023446</v>
+        <v>125023441</v>
       </c>
       <c r="B31" t="n">
-        <v>91221</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3733,25 +3729,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1106</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3761,10 +3757,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753567</v>
+        <v>753798</v>
       </c>
       <c r="R31" t="n">
-        <v>7217721</v>
+        <v>7217948</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3799,13 +3795,17 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3824,10 +3824,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125023429</v>
+        <v>125023442</v>
       </c>
       <c r="B32" t="n">
-        <v>79926</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3836,25 +3836,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3864,10 +3864,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753792</v>
+        <v>753726</v>
       </c>
       <c r="R32" t="n">
-        <v>7217798</v>
+        <v>7218039</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3900,6 +3900,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3926,10 +3931,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125023380</v>
+        <v>125023326</v>
       </c>
       <c r="B33" t="n">
-        <v>79927</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3938,38 +3943,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753769</v>
+        <v>753598</v>
       </c>
       <c r="R33" t="n">
-        <v>7218019</v>
+        <v>7217744</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4002,6 +4015,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4028,10 +4046,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125023413</v>
+        <v>125023358</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4044,21 +4062,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4068,10 +4086,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753517</v>
+        <v>753758</v>
       </c>
       <c r="R34" t="n">
-        <v>7217918</v>
+        <v>7217900</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4130,10 +4148,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125023404</v>
+        <v>125023373</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4146,21 +4164,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4170,10 +4188,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753743</v>
+        <v>753768</v>
       </c>
       <c r="R35" t="n">
-        <v>7218044</v>
+        <v>7218016</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4232,10 +4250,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125023338</v>
+        <v>125023430</v>
       </c>
       <c r="B36" t="n">
-        <v>8720</v>
+        <v>79926</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4244,25 +4262,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100798</v>
+        <v>6463</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Smal trollknäppare</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Danosoma conspersum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4272,10 +4290,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753699</v>
+        <v>753789</v>
       </c>
       <c r="R36" t="n">
-        <v>7217618</v>
+        <v>7217809</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4316,7 +4334,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4335,10 +4352,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125023351</v>
+        <v>125023324</v>
       </c>
       <c r="B37" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4351,21 +4368,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4375,10 +4392,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753758</v>
+        <v>753480</v>
       </c>
       <c r="R37" t="n">
-        <v>7217819</v>
+        <v>7218033</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4437,10 +4454,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125023350</v>
+        <v>125023419</v>
       </c>
       <c r="B38" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4453,21 +4470,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4477,10 +4494,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753789</v>
+        <v>753550</v>
       </c>
       <c r="R38" t="n">
-        <v>7217812</v>
+        <v>7217725</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4539,10 +4556,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125023366</v>
+        <v>125023405</v>
       </c>
       <c r="B39" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4555,21 +4572,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4579,10 +4596,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753778</v>
+        <v>753748</v>
       </c>
       <c r="R39" t="n">
-        <v>7217945</v>
+        <v>7218047</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4641,10 +4658,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125023414</v>
+        <v>125023338</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>8720</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4653,25 +4670,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100798</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smal trollknäppare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Danosoma conspersum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyllenhal, 1808)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4681,10 +4698,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753630</v>
+        <v>753699</v>
       </c>
       <c r="R40" t="n">
-        <v>7218006</v>
+        <v>7217618</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4725,6 +4742,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4743,10 +4761,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125023389</v>
+        <v>125023438</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4755,25 +4773,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4783,10 +4801,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753729</v>
+        <v>753612</v>
       </c>
       <c r="R41" t="n">
-        <v>7218042</v>
+        <v>7217703</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4819,6 +4837,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4845,10 +4868,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125023392</v>
+        <v>125023334</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4857,25 +4880,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4885,10 +4908,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753718</v>
+        <v>753752</v>
       </c>
       <c r="R42" t="n">
-        <v>7218035</v>
+        <v>7217919</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4947,10 +4970,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125023426</v>
+        <v>125023357</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4963,21 +4986,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4987,10 +5010,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753597</v>
+        <v>753793</v>
       </c>
       <c r="R43" t="n">
-        <v>7217728</v>
+        <v>7217856</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5049,10 +5072,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125023324</v>
+        <v>125023366</v>
       </c>
       <c r="B44" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5065,21 +5088,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5089,10 +5112,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753480</v>
+        <v>753778</v>
       </c>
       <c r="R44" t="n">
-        <v>7218033</v>
+        <v>7217945</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5151,7 +5174,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125023365</v>
+        <v>125023345</v>
       </c>
       <c r="B45" t="n">
         <v>79891</v>
@@ -5191,10 +5214,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753784</v>
+        <v>753790</v>
       </c>
       <c r="R45" t="n">
-        <v>7217948</v>
+        <v>7217981</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5253,7 +5276,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125023357</v>
+        <v>125023369</v>
       </c>
       <c r="B46" t="n">
         <v>79891</v>
@@ -5293,10 +5316,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753793</v>
+        <v>753797</v>
       </c>
       <c r="R46" t="n">
-        <v>7217856</v>
+        <v>7218005</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5355,10 +5378,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125023420</v>
+        <v>125023319</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5367,25 +5390,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5395,10 +5418,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753559</v>
+        <v>753506</v>
       </c>
       <c r="R47" t="n">
-        <v>7217734</v>
+        <v>7217904</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5457,10 +5480,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125023423</v>
+        <v>125023435</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5473,31 +5496,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753610</v>
+        <v>753562</v>
       </c>
       <c r="R48" t="n">
         <v>7217727</v>
@@ -5533,6 +5564,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5559,10 +5595,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125023374</v>
+        <v>125023390</v>
       </c>
       <c r="B49" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5571,25 +5607,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5599,10 +5635,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753763</v>
+        <v>753701</v>
       </c>
       <c r="R49" t="n">
-        <v>7218015</v>
+        <v>7218031</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5661,10 +5697,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125023354</v>
+        <v>125023411</v>
       </c>
       <c r="B50" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5677,21 +5713,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5701,10 +5737,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753773</v>
+        <v>753557</v>
       </c>
       <c r="R50" t="n">
-        <v>7217842</v>
+        <v>7217895</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5763,7 +5799,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125023402</v>
+        <v>125023426</v>
       </c>
       <c r="B51" t="n">
         <v>78810</v>
@@ -5803,10 +5839,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753752</v>
+        <v>753597</v>
       </c>
       <c r="R51" t="n">
-        <v>7217878</v>
+        <v>7217728</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5865,7 +5901,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125023396</v>
+        <v>125023413</v>
       </c>
       <c r="B52" t="n">
         <v>78810</v>
@@ -5899,23 +5935,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>753626</v>
+        <v>753517</v>
       </c>
       <c r="R52" t="n">
-        <v>7218004</v>
+        <v>7217918</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5950,18 +5979,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5980,10 +6003,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125023323</v>
+        <v>125023352</v>
       </c>
       <c r="B53" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5996,21 +6019,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6020,10 +6043,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>753504</v>
+        <v>753763</v>
       </c>
       <c r="R53" t="n">
-        <v>7217889</v>
+        <v>7217831</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6082,7 +6105,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125023345</v>
+        <v>125023372</v>
       </c>
       <c r="B54" t="n">
         <v>79891</v>
@@ -6125,7 +6148,7 @@
         <v>753790</v>
       </c>
       <c r="R54" t="n">
-        <v>7217981</v>
+        <v>7217992</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6184,10 +6207,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125023334</v>
+        <v>125023446</v>
       </c>
       <c r="B55" t="n">
-        <v>79920</v>
+        <v>91221</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6196,25 +6219,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>1106</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6224,10 +6247,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753752</v>
+        <v>753567</v>
       </c>
       <c r="R55" t="n">
-        <v>7217919</v>
+        <v>7217721</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6268,6 +6291,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6286,10 +6310,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125023367</v>
+        <v>125023416</v>
       </c>
       <c r="B56" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6302,21 +6326,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6326,10 +6350,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753786</v>
+        <v>753470</v>
       </c>
       <c r="R56" t="n">
-        <v>7217962</v>
+        <v>7218024</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6388,10 +6412,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125023343</v>
+        <v>125023387</v>
       </c>
       <c r="B57" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6404,21 +6428,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6428,10 +6452,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753760</v>
+        <v>753816</v>
       </c>
       <c r="R57" t="n">
-        <v>7218023</v>
+        <v>7217838</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6466,18 +6490,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6496,10 +6514,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125023390</v>
+        <v>125023404</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6508,25 +6526,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6536,10 +6554,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753701</v>
+        <v>753743</v>
       </c>
       <c r="R58" t="n">
-        <v>7218031</v>
+        <v>7218044</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6598,10 +6616,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125023418</v>
+        <v>125023330</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6614,21 +6632,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6638,10 +6656,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753406</v>
+        <v>753730</v>
       </c>
       <c r="R59" t="n">
-        <v>7217999</v>
+        <v>7217943</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6700,10 +6718,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125023318</v>
+        <v>125023439</v>
       </c>
       <c r="B60" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6712,25 +6730,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6740,10 +6758,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753680</v>
+        <v>753568</v>
       </c>
       <c r="R60" t="n">
-        <v>7218004</v>
+        <v>7217716</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6776,6 +6794,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6802,10 +6825,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125023419</v>
+        <v>125023316</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6818,34 +6841,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753550</v>
+        <v>753568</v>
       </c>
       <c r="R61" t="n">
-        <v>7217725</v>
+        <v>7217733</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6878,6 +6909,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6904,10 +6940,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125023443</v>
+        <v>125023321</v>
       </c>
       <c r="B62" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6920,21 +6956,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6944,10 +6980,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753575</v>
+        <v>753679</v>
       </c>
       <c r="R62" t="n">
-        <v>7217751</v>
+        <v>7218005</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6980,11 +7016,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7011,10 +7042,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125023320</v>
+        <v>125023396</v>
       </c>
       <c r="B63" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7027,34 +7058,41 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753687</v>
+        <v>753626</v>
       </c>
       <c r="R63" t="n">
-        <v>7217999</v>
+        <v>7218004</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7089,12 +7127,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7113,10 +7157,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125023348</v>
+        <v>125023429</v>
       </c>
       <c r="B64" t="n">
-        <v>79891</v>
+        <v>79926</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7125,25 +7169,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7153,10 +7197,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753817</v>
+        <v>753792</v>
       </c>
       <c r="R64" t="n">
-        <v>7217853</v>
+        <v>7217798</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7215,10 +7259,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125023368</v>
+        <v>125023432</v>
       </c>
       <c r="B65" t="n">
-        <v>79891</v>
+        <v>79926</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7227,25 +7271,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7255,10 +7299,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753808</v>
+        <v>753769</v>
       </c>
       <c r="R65" t="n">
-        <v>7217964</v>
+        <v>7218019</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7317,10 +7361,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125023373</v>
+        <v>125023380</v>
       </c>
       <c r="B66" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7329,25 +7373,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7357,10 +7401,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753768</v>
+        <v>753769</v>
       </c>
       <c r="R66" t="n">
-        <v>7218016</v>
+        <v>7218019</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7419,7 +7463,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125023411</v>
+        <v>125023407</v>
       </c>
       <c r="B67" t="n">
         <v>78810</v>
@@ -7459,10 +7503,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753557</v>
+        <v>753671</v>
       </c>
       <c r="R67" t="n">
-        <v>7217895</v>
+        <v>7218008</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7521,10 +7565,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125023416</v>
+        <v>125023315</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7537,21 +7581,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7561,10 +7605,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753470</v>
+        <v>753491</v>
       </c>
       <c r="R68" t="n">
-        <v>7218024</v>
+        <v>7217766</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7597,6 +7641,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7623,10 +7672,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125023403</v>
+        <v>125023323</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7639,21 +7688,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7663,10 +7712,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753762</v>
+        <v>753504</v>
       </c>
       <c r="R69" t="n">
-        <v>7218015</v>
+        <v>7217889</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7725,10 +7774,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125023434</v>
+        <v>125023389</v>
       </c>
       <c r="B70" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7737,46 +7786,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753797</v>
+        <v>753729</v>
       </c>
       <c r="R70" t="n">
-        <v>7217988</v>
+        <v>7218042</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7809,11 +7850,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7840,10 +7876,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125023445</v>
+        <v>125023350</v>
       </c>
       <c r="B71" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7856,21 +7892,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7880,10 +7916,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753715</v>
+        <v>753789</v>
       </c>
       <c r="R71" t="n">
-        <v>7218026</v>
+        <v>7217812</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7916,11 +7952,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7947,10 +7978,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125023435</v>
+        <v>125023394</v>
       </c>
       <c r="B72" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7963,42 +7994,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753562</v>
+        <v>753596</v>
       </c>
       <c r="R72" t="n">
-        <v>7217727</v>
+        <v>7217939</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8031,11 +8054,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8062,7 +8080,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125023358</v>
+        <v>125023348</v>
       </c>
       <c r="B73" t="n">
         <v>79891</v>
@@ -8102,10 +8120,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>753758</v>
+        <v>753817</v>
       </c>
       <c r="R73" t="n">
-        <v>7217900</v>
+        <v>7217853</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8164,7 +8182,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125023378</v>
+        <v>125023349</v>
       </c>
       <c r="B74" t="n">
         <v>79891</v>
@@ -8204,10 +8222,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>753722</v>
+        <v>753795</v>
       </c>
       <c r="R74" t="n">
-        <v>7218033</v>
+        <v>7217800</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8266,10 +8284,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125023360</v>
+        <v>125023336</v>
       </c>
       <c r="B75" t="n">
-        <v>79891</v>
+        <v>90962</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8282,21 +8300,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8306,10 +8324,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>753752</v>
+        <v>753566</v>
       </c>
       <c r="R75" t="n">
-        <v>7217944</v>
+        <v>7217862</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8368,10 +8386,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125023391</v>
+        <v>125023320</v>
       </c>
       <c r="B76" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8380,25 +8398,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8408,10 +8426,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>753706</v>
+        <v>753687</v>
       </c>
       <c r="R76" t="n">
-        <v>7218039</v>
+        <v>7217999</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8470,10 +8488,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125023321</v>
+        <v>125023318</v>
       </c>
       <c r="B77" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8482,25 +8500,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8510,10 +8528,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>753679</v>
+        <v>753680</v>
       </c>
       <c r="R77" t="n">
-        <v>7218005</v>
+        <v>7218004</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8572,10 +8590,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125023372</v>
+        <v>125023412</v>
       </c>
       <c r="B78" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8588,21 +8606,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8612,10 +8630,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>753790</v>
+        <v>753568</v>
       </c>
       <c r="R78" t="n">
-        <v>7217992</v>
+        <v>7217875</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8674,10 +8692,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125023395</v>
+        <v>125023409</v>
       </c>
       <c r="B79" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8690,21 +8708,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8714,10 +8732,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>753472</v>
+        <v>753562</v>
       </c>
       <c r="R79" t="n">
-        <v>7218031</v>
+        <v>7217917</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8776,7 +8794,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125023409</v>
+        <v>125023402</v>
       </c>
       <c r="B80" t="n">
         <v>78810</v>
@@ -8816,10 +8834,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>753562</v>
+        <v>753752</v>
       </c>
       <c r="R80" t="n">
-        <v>7217917</v>
+        <v>7217878</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8878,10 +8896,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125023407</v>
+        <v>125023337</v>
       </c>
       <c r="B81" t="n">
-        <v>78810</v>
+        <v>79795</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8890,25 +8908,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8918,10 +8936,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>753671</v>
+        <v>753523</v>
       </c>
       <c r="R81" t="n">
-        <v>7218008</v>
+        <v>7218086</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8980,10 +8998,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125023438</v>
+        <v>125023347</v>
       </c>
       <c r="B82" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8996,21 +9014,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9020,10 +9038,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>753612</v>
+        <v>753850</v>
       </c>
       <c r="R82" t="n">
-        <v>7217703</v>
+        <v>7217843</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9056,11 +9074,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9087,10 +9100,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125023401</v>
+        <v>125023431</v>
       </c>
       <c r="B83" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9099,20 +9112,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9127,10 +9140,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>753780</v>
+        <v>753774</v>
       </c>
       <c r="R83" t="n">
-        <v>7217865</v>
+        <v>7217939</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9189,10 +9202,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125023335</v>
+        <v>125023421</v>
       </c>
       <c r="B84" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9201,25 +9214,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9229,10 +9242,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>753790</v>
+        <v>753573</v>
       </c>
       <c r="R84" t="n">
-        <v>7217992</v>
+        <v>7217745</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9291,10 +9304,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125023375</v>
+        <v>125023423</v>
       </c>
       <c r="B85" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9307,21 +9320,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9331,10 +9344,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>753750</v>
+        <v>753610</v>
       </c>
       <c r="R85" t="n">
-        <v>7218028</v>
+        <v>7217727</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9393,10 +9406,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125023369</v>
+        <v>125023333</v>
       </c>
       <c r="B86" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9409,21 +9422,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9433,10 +9446,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>753797</v>
+        <v>753781</v>
       </c>
       <c r="R86" t="n">
-        <v>7218005</v>
+        <v>7217902</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9495,10 +9508,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125023316</v>
+        <v>125023418</v>
       </c>
       <c r="B87" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9511,42 +9524,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>753568</v>
+        <v>753406</v>
       </c>
       <c r="R87" t="n">
-        <v>7217733</v>
+        <v>7217999</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9579,11 +9584,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9610,10 +9610,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125023444</v>
+        <v>125023417</v>
       </c>
       <c r="B88" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9626,21 +9626,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9650,10 +9650,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>753746</v>
+        <v>753474</v>
       </c>
       <c r="R88" t="n">
-        <v>7217930</v>
+        <v>7218026</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9686,11 +9686,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9717,10 +9712,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125023421</v>
+        <v>125023444</v>
       </c>
       <c r="B89" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9733,21 +9728,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9757,10 +9752,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>753573</v>
+        <v>753746</v>
       </c>
       <c r="R89" t="n">
-        <v>7217745</v>
+        <v>7217930</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9793,6 +9788,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9819,10 +9819,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125023406</v>
+        <v>125023392</v>
       </c>
       <c r="B90" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9831,25 +9831,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9862,7 +9862,7 @@
         <v>753718</v>
       </c>
       <c r="R90" t="n">
-        <v>7218042</v>
+        <v>7218035</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9921,10 +9921,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125023387</v>
+        <v>125023388</v>
       </c>
       <c r="B91" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9933,25 +9933,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9961,10 +9961,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>753816</v>
+        <v>753742</v>
       </c>
       <c r="R91" t="n">
-        <v>7217838</v>
+        <v>7217924</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10023,10 +10023,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125023328</v>
+        <v>125023381</v>
       </c>
       <c r="B92" t="n">
-        <v>57666</v>
+        <v>79927</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10035,25 +10035,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10063,10 +10063,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>753742</v>
+        <v>753722</v>
       </c>
       <c r="R92" t="n">
-        <v>7217926</v>
+        <v>7218033</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10125,10 +10125,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125023431</v>
+        <v>125023378</v>
       </c>
       <c r="B93" t="n">
-        <v>79926</v>
+        <v>79891</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10137,25 +10137,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10165,10 +10165,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>753774</v>
+        <v>753722</v>
       </c>
       <c r="R93" t="n">
-        <v>7217939</v>
+        <v>7218033</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10227,10 +10227,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125023339</v>
+        <v>125023375</v>
       </c>
       <c r="B94" t="n">
-        <v>92285</v>
+        <v>79891</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10243,37 +10243,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4361</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>753567</v>
+        <v>753750</v>
       </c>
       <c r="R94" t="n">
-        <v>7217957</v>
+        <v>7218028</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10308,18 +10305,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp. Brunorangt kött uppåt hatten, vitdassigt ner mot foten</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10338,7 +10329,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125023363</v>
+        <v>125023374</v>
       </c>
       <c r="B95" t="n">
         <v>79891</v>
@@ -10378,10 +10369,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>753782</v>
+        <v>753763</v>
       </c>
       <c r="R95" t="n">
-        <v>7217946</v>
+        <v>7218015</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10440,10 +10431,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125023430</v>
+        <v>125023395</v>
       </c>
       <c r="B96" t="n">
-        <v>79926</v>
+        <v>91030</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10452,25 +10443,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10480,10 +10471,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>753789</v>
+        <v>753472</v>
       </c>
       <c r="R96" t="n">
-        <v>7217809</v>
+        <v>7218031</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10542,10 +10533,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125023319</v>
+        <v>125023383</v>
       </c>
       <c r="B97" t="n">
-        <v>90977</v>
+        <v>91410</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10554,38 +10545,36 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>753506</v>
+        <v>753603</v>
       </c>
       <c r="R97" t="n">
-        <v>7217904</v>
+        <v>7217932</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10626,6 +10615,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10644,10 +10634,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125023383</v>
+        <v>125023317</v>
       </c>
       <c r="B98" t="n">
-        <v>91410</v>
+        <v>78842</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10660,16 +10650,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6040186</v>
+        <v>185</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10682,10 +10677,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>753603</v>
+        <v>753719</v>
       </c>
       <c r="R98" t="n">
-        <v>7217932</v>
+        <v>7217616</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10745,10 +10740,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125023317</v>
+        <v>125023339</v>
       </c>
       <c r="B99" t="n">
-        <v>78842</v>
+        <v>92285</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10761,21 +10756,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>185</v>
+        <v>4361</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10788,10 +10783,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>753719</v>
+        <v>753567</v>
       </c>
       <c r="R99" t="n">
-        <v>7217616</v>
+        <v>7217957</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10824,6 +10819,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp. Vitdassigt kött uppåt hatten, brunorangt ner mot foten</t>
         </is>
       </c>
       <c r="AD99" t="b">

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125023403</v>
+        <v>125023328</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,21 +1331,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>753762</v>
+        <v>753742</v>
       </c>
       <c r="R8" t="n">
-        <v>7218015</v>
+        <v>7217926</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125023325</v>
+        <v>125023403</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,42 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>753575</v>
+        <v>753762</v>
       </c>
       <c r="R9" t="n">
-        <v>7217959</v>
+        <v>7218015</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,11 +1493,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,7 +1519,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125023445</v>
+        <v>125023325</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1566,16 +1553,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>753715</v>
+        <v>753575</v>
       </c>
       <c r="R10" t="n">
-        <v>7218026</v>
+        <v>7217959</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,7 +1607,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Avskalad gran</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125023328</v>
+        <v>125023445</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>753742</v>
+        <v>753715</v>
       </c>
       <c r="R11" t="n">
-        <v>7217926</v>
+        <v>7218026</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,6 +1710,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023362</v>
+        <v>125023443</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,21 +1757,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>753752</v>
+        <v>753575</v>
       </c>
       <c r="R12" t="n">
-        <v>7217944</v>
+        <v>7217751</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,6 +1817,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125023443</v>
+        <v>125023362</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,21 +1864,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1888,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753575</v>
+        <v>753752</v>
       </c>
       <c r="R13" t="n">
-        <v>7217751</v>
+        <v>7217944</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,11 +1924,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2670,10 +2670,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125023342</v>
+        <v>125023391</v>
       </c>
       <c r="B21" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2682,25 +2682,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753722</v>
+        <v>753706</v>
       </c>
       <c r="R21" t="n">
-        <v>7217596</v>
+        <v>7218039</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,7 +2754,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2773,10 +2772,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125023391</v>
+        <v>125023342</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2785,25 +2784,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2813,10 +2812,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753706</v>
+        <v>753722</v>
       </c>
       <c r="R22" t="n">
-        <v>7218039</v>
+        <v>7217596</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2857,6 +2856,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3411,10 +3411,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125023368</v>
+        <v>125023441</v>
       </c>
       <c r="B28" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3427,21 +3427,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753808</v>
+        <v>753798</v>
       </c>
       <c r="R28" t="n">
-        <v>7217964</v>
+        <v>7217948</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3487,6 +3487,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3513,10 +3518,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125023401</v>
+        <v>125023368</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3529,21 +3534,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3553,10 +3558,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753780</v>
+        <v>753808</v>
       </c>
       <c r="R29" t="n">
-        <v>7217865</v>
+        <v>7217964</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3615,7 +3620,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125023406</v>
+        <v>125023401</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3655,10 +3660,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753718</v>
+        <v>753780</v>
       </c>
       <c r="R30" t="n">
-        <v>7218042</v>
+        <v>7217865</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3717,10 +3722,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125023441</v>
+        <v>125023406</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3733,21 +3738,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3757,10 +3762,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753798</v>
+        <v>753718</v>
       </c>
       <c r="R31" t="n">
-        <v>7217948</v>
+        <v>7218042</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3793,11 +3798,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3824,10 +3824,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125023442</v>
+        <v>125023419</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3840,21 +3840,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3864,10 +3864,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753726</v>
+        <v>753550</v>
       </c>
       <c r="R32" t="n">
-        <v>7218039</v>
+        <v>7217725</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3900,11 +3900,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3931,7 +3926,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125023326</v>
+        <v>125023442</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -3965,24 +3960,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753598</v>
+        <v>753726</v>
       </c>
       <c r="R33" t="n">
-        <v>7217744</v>
+        <v>7218039</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4019,7 +4006,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4046,10 +4033,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125023358</v>
+        <v>125023326</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4062,34 +4049,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753758</v>
+        <v>753598</v>
       </c>
       <c r="R34" t="n">
-        <v>7217900</v>
+        <v>7217744</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4122,6 +4117,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4148,10 +4148,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125023373</v>
+        <v>125023324</v>
       </c>
       <c r="B35" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4164,21 +4164,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753768</v>
+        <v>753480</v>
       </c>
       <c r="R35" t="n">
-        <v>7218016</v>
+        <v>7218033</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125023430</v>
+        <v>125023358</v>
       </c>
       <c r="B36" t="n">
-        <v>79926</v>
+        <v>79891</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4262,25 +4262,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753789</v>
+        <v>753758</v>
       </c>
       <c r="R36" t="n">
-        <v>7217809</v>
+        <v>7217900</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125023324</v>
+        <v>125023373</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4368,21 +4368,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753480</v>
+        <v>753768</v>
       </c>
       <c r="R37" t="n">
-        <v>7218033</v>
+        <v>7218016</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4454,10 +4454,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125023419</v>
+        <v>125023430</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4466,20 +4466,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753550</v>
+        <v>753789</v>
       </c>
       <c r="R38" t="n">
-        <v>7217725</v>
+        <v>7217809</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5378,10 +5378,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125023319</v>
+        <v>125023411</v>
       </c>
       <c r="B47" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5390,25 +5390,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753506</v>
+        <v>753557</v>
       </c>
       <c r="R47" t="n">
-        <v>7217904</v>
+        <v>7217895</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5480,10 +5480,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125023435</v>
+        <v>125023426</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5496,42 +5496,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753562</v>
+        <v>753597</v>
       </c>
       <c r="R48" t="n">
-        <v>7217727</v>
+        <v>7217728</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5564,11 +5556,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5595,10 +5582,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125023390</v>
+        <v>125023413</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5607,25 +5594,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5635,10 +5622,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753701</v>
+        <v>753517</v>
       </c>
       <c r="R49" t="n">
-        <v>7218031</v>
+        <v>7217918</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5697,10 +5684,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125023411</v>
+        <v>125023435</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5713,34 +5700,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753557</v>
+        <v>753562</v>
       </c>
       <c r="R50" t="n">
-        <v>7217895</v>
+        <v>7217727</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5773,6 +5768,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5799,10 +5799,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125023426</v>
+        <v>125023390</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5811,25 +5811,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753597</v>
+        <v>753701</v>
       </c>
       <c r="R51" t="n">
-        <v>7217728</v>
+        <v>7218031</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125023413</v>
+        <v>125023319</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5913,25 +5913,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>753517</v>
+        <v>753506</v>
       </c>
       <c r="R52" t="n">
-        <v>7217918</v>
+        <v>7217904</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6003,10 +6003,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125023352</v>
+        <v>125023416</v>
       </c>
       <c r="B53" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6019,21 +6019,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>753763</v>
+        <v>753470</v>
       </c>
       <c r="R53" t="n">
-        <v>7217831</v>
+        <v>7218024</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6105,10 +6105,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125023372</v>
+        <v>125023387</v>
       </c>
       <c r="B54" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6121,21 +6121,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6145,10 +6145,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753790</v>
+        <v>753816</v>
       </c>
       <c r="R54" t="n">
-        <v>7217992</v>
+        <v>7217838</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125023446</v>
+        <v>125023404</v>
       </c>
       <c r="B55" t="n">
-        <v>91221</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6219,25 +6219,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1106</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753567</v>
+        <v>753743</v>
       </c>
       <c r="R55" t="n">
-        <v>7217721</v>
+        <v>7218044</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6291,7 +6291,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6310,10 +6309,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125023416</v>
+        <v>125023352</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6326,21 +6325,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6350,10 +6349,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753470</v>
+        <v>753763</v>
       </c>
       <c r="R56" t="n">
-        <v>7218024</v>
+        <v>7217831</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6412,10 +6411,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125023387</v>
+        <v>125023372</v>
       </c>
       <c r="B57" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6428,21 +6427,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6452,10 +6451,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753816</v>
+        <v>753790</v>
       </c>
       <c r="R57" t="n">
-        <v>7217838</v>
+        <v>7217992</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6514,10 +6513,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125023404</v>
+        <v>125023446</v>
       </c>
       <c r="B58" t="n">
-        <v>78810</v>
+        <v>91221</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6526,25 +6525,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1106</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6554,10 +6553,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753743</v>
+        <v>753567</v>
       </c>
       <c r="R58" t="n">
-        <v>7218044</v>
+        <v>7217721</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6598,6 +6597,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7042,10 +7042,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125023396</v>
+        <v>125023429</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7054,20 +7054,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7076,23 +7076,16 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753626</v>
+        <v>753792</v>
       </c>
       <c r="R63" t="n">
-        <v>7218004</v>
+        <v>7217798</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7127,18 +7120,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7157,10 +7144,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125023429</v>
+        <v>125023396</v>
       </c>
       <c r="B64" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7169,20 +7156,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7191,16 +7178,23 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753792</v>
+        <v>753626</v>
       </c>
       <c r="R64" t="n">
-        <v>7217798</v>
+        <v>7218004</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7235,12 +7229,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7672,10 +7672,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125023323</v>
+        <v>125023389</v>
       </c>
       <c r="B69" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7684,25 +7684,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7712,10 +7712,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753504</v>
+        <v>753729</v>
       </c>
       <c r="R69" t="n">
-        <v>7217889</v>
+        <v>7218042</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7774,10 +7774,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125023389</v>
+        <v>125023350</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7786,25 +7786,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753729</v>
+        <v>753789</v>
       </c>
       <c r="R70" t="n">
-        <v>7218042</v>
+        <v>7217812</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7876,10 +7876,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125023350</v>
+        <v>125023394</v>
       </c>
       <c r="B71" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7892,21 +7892,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7916,10 +7916,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753789</v>
+        <v>753596</v>
       </c>
       <c r="R71" t="n">
-        <v>7217812</v>
+        <v>7217939</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7978,10 +7978,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125023394</v>
+        <v>125023323</v>
       </c>
       <c r="B72" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7994,21 +7994,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8018,10 +8018,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753596</v>
+        <v>753504</v>
       </c>
       <c r="R72" t="n">
-        <v>7217939</v>
+        <v>7217889</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9202,10 +9202,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125023421</v>
+        <v>125023333</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9218,21 +9218,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>753573</v>
+        <v>753781</v>
       </c>
       <c r="R84" t="n">
-        <v>7217745</v>
+        <v>7217902</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9304,7 +9304,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125023423</v>
+        <v>125023421</v>
       </c>
       <c r="B85" t="n">
         <v>78810</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>753610</v>
+        <v>753573</v>
       </c>
       <c r="R85" t="n">
-        <v>7217727</v>
+        <v>7217745</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9406,10 +9406,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125023333</v>
+        <v>125023423</v>
       </c>
       <c r="B86" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9422,21 +9422,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9446,10 +9446,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>753781</v>
+        <v>753610</v>
       </c>
       <c r="R86" t="n">
-        <v>7217902</v>
+        <v>7217727</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9921,10 +9921,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125023388</v>
+        <v>125023381</v>
       </c>
       <c r="B91" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9933,25 +9933,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9961,10 +9961,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>753742</v>
+        <v>753722</v>
       </c>
       <c r="R91" t="n">
-        <v>7217924</v>
+        <v>7218033</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10023,10 +10023,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125023381</v>
+        <v>125023378</v>
       </c>
       <c r="B92" t="n">
-        <v>79927</v>
+        <v>79891</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10035,25 +10035,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10125,7 +10125,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125023378</v>
+        <v>125023375</v>
       </c>
       <c r="B93" t="n">
         <v>79891</v>
@@ -10165,10 +10165,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>753722</v>
+        <v>753750</v>
       </c>
       <c r="R93" t="n">
-        <v>7218033</v>
+        <v>7218028</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10227,7 +10227,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125023375</v>
+        <v>125023374</v>
       </c>
       <c r="B94" t="n">
         <v>79891</v>
@@ -10267,10 +10267,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>753750</v>
+        <v>753763</v>
       </c>
       <c r="R94" t="n">
-        <v>7218028</v>
+        <v>7218015</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10329,10 +10329,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125023374</v>
+        <v>125023395</v>
       </c>
       <c r="B95" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10345,21 +10345,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10369,10 +10369,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>753763</v>
+        <v>753472</v>
       </c>
       <c r="R95" t="n">
-        <v>7218015</v>
+        <v>7218031</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10431,10 +10431,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125023395</v>
+        <v>125023388</v>
       </c>
       <c r="B96" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10443,25 +10443,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10471,10 +10471,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>753472</v>
+        <v>753742</v>
       </c>
       <c r="R96" t="n">
-        <v>7218031</v>
+        <v>7217924</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125023328</v>
+        <v>125023325</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,34 +1331,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>753742</v>
+        <v>753575</v>
       </c>
       <c r="R8" t="n">
-        <v>7217926</v>
+        <v>7217959</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,6 +1399,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125023403</v>
+        <v>125023445</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1446,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>753762</v>
+        <v>753715</v>
       </c>
       <c r="R9" t="n">
-        <v>7218015</v>
+        <v>7218026</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,6 +1506,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125023325</v>
+        <v>125023403</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,42 +1553,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>753575</v>
+        <v>753762</v>
       </c>
       <c r="R10" t="n">
-        <v>7217959</v>
+        <v>7218015</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,11 +1613,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125023445</v>
+        <v>125023328</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>753715</v>
+        <v>753742</v>
       </c>
       <c r="R11" t="n">
-        <v>7218026</v>
+        <v>7217926</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,11 +1715,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -4556,10 +4556,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125023405</v>
+        <v>125023334</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4568,25 +4568,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753748</v>
+        <v>753752</v>
       </c>
       <c r="R39" t="n">
-        <v>7218047</v>
+        <v>7217919</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125023338</v>
+        <v>125023357</v>
       </c>
       <c r="B40" t="n">
-        <v>8720</v>
+        <v>79891</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4670,25 +4670,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100798</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Smal trollknäppare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Danosoma conspersum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753699</v>
+        <v>753793</v>
       </c>
       <c r="R40" t="n">
-        <v>7217618</v>
+        <v>7217856</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4742,7 +4742,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4761,10 +4760,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125023438</v>
+        <v>125023366</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4777,21 +4776,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4801,10 +4800,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753612</v>
+        <v>753778</v>
       </c>
       <c r="R41" t="n">
-        <v>7217703</v>
+        <v>7217945</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4837,11 +4836,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4868,10 +4862,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125023334</v>
+        <v>125023405</v>
       </c>
       <c r="B42" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4880,25 +4874,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4908,10 +4902,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753752</v>
+        <v>753748</v>
       </c>
       <c r="R42" t="n">
-        <v>7217919</v>
+        <v>7218047</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4970,10 +4964,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125023357</v>
+        <v>125023338</v>
       </c>
       <c r="B43" t="n">
-        <v>79891</v>
+        <v>8720</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4982,25 +4976,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smal trollknäppare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Danosoma conspersum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyllenhal, 1808)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5010,10 +5004,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753793</v>
+        <v>753699</v>
       </c>
       <c r="R43" t="n">
-        <v>7217856</v>
+        <v>7217618</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5054,6 +5048,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5072,10 +5067,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125023366</v>
+        <v>125023438</v>
       </c>
       <c r="B44" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5088,21 +5083,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5112,10 +5107,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753778</v>
+        <v>753612</v>
       </c>
       <c r="R44" t="n">
-        <v>7217945</v>
+        <v>7217703</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5148,6 +5143,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6616,10 +6616,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125023330</v>
+        <v>125023439</v>
       </c>
       <c r="B59" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6632,21 +6632,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753730</v>
+        <v>753568</v>
       </c>
       <c r="R59" t="n">
-        <v>7217943</v>
+        <v>7217716</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6692,6 +6692,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6718,7 +6723,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125023439</v>
+        <v>125023316</v>
       </c>
       <c r="B60" t="n">
         <v>57513</v>
@@ -6752,6 +6757,14 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
@@ -6761,7 +6774,7 @@
         <v>753568</v>
       </c>
       <c r="R60" t="n">
-        <v>7217716</v>
+        <v>7217733</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6798,7 +6811,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Barksprätt</t>
+          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6825,10 +6838,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125023316</v>
+        <v>125023330</v>
       </c>
       <c r="B61" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6841,42 +6854,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753568</v>
+        <v>753730</v>
       </c>
       <c r="R61" t="n">
-        <v>7217733</v>
+        <v>7217943</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6909,11 +6914,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7042,10 +7042,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125023429</v>
+        <v>125023396</v>
       </c>
       <c r="B63" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7054,20 +7054,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7076,16 +7076,23 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753792</v>
+        <v>753626</v>
       </c>
       <c r="R63" t="n">
-        <v>7217798</v>
+        <v>7218004</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7120,12 +7127,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7144,10 +7157,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125023396</v>
+        <v>125023429</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7156,20 +7169,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7178,23 +7191,16 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753626</v>
+        <v>753792</v>
       </c>
       <c r="R64" t="n">
-        <v>7218004</v>
+        <v>7217798</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7229,18 +7235,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7259,10 +7259,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125023432</v>
+        <v>125023315</v>
       </c>
       <c r="B65" t="n">
-        <v>79926</v>
+        <v>57513</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7271,25 +7271,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753769</v>
+        <v>753491</v>
       </c>
       <c r="R65" t="n">
-        <v>7218019</v>
+        <v>7217766</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7335,6 +7335,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7361,10 +7366,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125023380</v>
+        <v>125023432</v>
       </c>
       <c r="B66" t="n">
-        <v>79927</v>
+        <v>79926</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7377,21 +7382,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7463,10 +7468,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125023407</v>
+        <v>125023380</v>
       </c>
       <c r="B67" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7475,25 +7480,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7503,10 +7508,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753671</v>
+        <v>753769</v>
       </c>
       <c r="R67" t="n">
-        <v>7218008</v>
+        <v>7218019</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7565,10 +7570,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125023315</v>
+        <v>125023407</v>
       </c>
       <c r="B68" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7581,21 +7586,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7605,10 +7610,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753491</v>
+        <v>753671</v>
       </c>
       <c r="R68" t="n">
-        <v>7217766</v>
+        <v>7218008</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7641,11 +7646,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7672,10 +7672,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125023389</v>
+        <v>125023323</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7684,25 +7684,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7712,10 +7712,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753729</v>
+        <v>753504</v>
       </c>
       <c r="R69" t="n">
-        <v>7218042</v>
+        <v>7217889</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7774,10 +7774,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125023350</v>
+        <v>125023389</v>
       </c>
       <c r="B70" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7786,25 +7786,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753789</v>
+        <v>753729</v>
       </c>
       <c r="R70" t="n">
-        <v>7217812</v>
+        <v>7218042</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7876,10 +7876,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125023394</v>
+        <v>125023350</v>
       </c>
       <c r="B71" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7892,21 +7892,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7916,10 +7916,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753596</v>
+        <v>753789</v>
       </c>
       <c r="R71" t="n">
-        <v>7217939</v>
+        <v>7217812</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7978,10 +7978,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125023323</v>
+        <v>125023394</v>
       </c>
       <c r="B72" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7994,21 +7994,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8018,10 +8018,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753504</v>
+        <v>753596</v>
       </c>
       <c r="R72" t="n">
-        <v>7217889</v>
+        <v>7217939</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9202,10 +9202,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125023333</v>
+        <v>125023421</v>
       </c>
       <c r="B84" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9218,21 +9218,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>753781</v>
+        <v>753573</v>
       </c>
       <c r="R84" t="n">
-        <v>7217902</v>
+        <v>7217745</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9304,7 +9304,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125023421</v>
+        <v>125023423</v>
       </c>
       <c r="B85" t="n">
         <v>78810</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>753573</v>
+        <v>753610</v>
       </c>
       <c r="R85" t="n">
-        <v>7217745</v>
+        <v>7217727</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9406,10 +9406,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125023423</v>
+        <v>125023333</v>
       </c>
       <c r="B86" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9422,21 +9422,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9446,10 +9446,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>753610</v>
+        <v>753781</v>
       </c>
       <c r="R86" t="n">
-        <v>7217727</v>
+        <v>7217902</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125023355</v>
+        <v>125023406</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753792</v>
+        <v>753718</v>
       </c>
       <c r="R4" t="n">
-        <v>7217850</v>
+        <v>7218042</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125023367</v>
+        <v>125023320</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,21 +1025,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753786</v>
+        <v>753687</v>
       </c>
       <c r="R5" t="n">
-        <v>7217962</v>
+        <v>7217999</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125023420</v>
+        <v>125023403</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753559</v>
+        <v>753762</v>
       </c>
       <c r="R6" t="n">
-        <v>7217734</v>
+        <v>7218015</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125023327</v>
+        <v>125023372</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>753740</v>
+        <v>753790</v>
       </c>
       <c r="R7" t="n">
-        <v>7217891</v>
+        <v>7217992</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125023445</v>
+        <v>125023327</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,21 +1446,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>753715</v>
+        <v>753740</v>
       </c>
       <c r="R9" t="n">
-        <v>7218026</v>
+        <v>7217891</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,11 +1506,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,7 +1532,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125023403</v>
+        <v>125023399</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1577,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>753762</v>
+        <v>753751</v>
       </c>
       <c r="R10" t="n">
-        <v>7218015</v>
+        <v>7217806</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125023328</v>
+        <v>125023417</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>753742</v>
+        <v>753474</v>
       </c>
       <c r="R11" t="n">
-        <v>7217926</v>
+        <v>7218026</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023443</v>
+        <v>125023396</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,34 +1752,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>753575</v>
+        <v>753626</v>
       </c>
       <c r="R12" t="n">
-        <v>7217751</v>
+        <v>7218004</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,7 +1823,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Barksprätt</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1830,6 +1832,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1848,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125023362</v>
+        <v>125023315</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1864,21 +1867,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1888,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753752</v>
+        <v>753491</v>
       </c>
       <c r="R13" t="n">
-        <v>7217944</v>
+        <v>7217766</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,6 +1927,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1950,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125023363</v>
+        <v>125023381</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1962,25 +1970,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1990,10 +1998,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753782</v>
+        <v>753722</v>
       </c>
       <c r="R14" t="n">
-        <v>7217946</v>
+        <v>7218033</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,7 +2060,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125023354</v>
+        <v>125023360</v>
       </c>
       <c r="B15" t="n">
         <v>79891</v>
@@ -2092,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>753773</v>
+        <v>753752</v>
       </c>
       <c r="R15" t="n">
-        <v>7217842</v>
+        <v>7217944</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2154,7 +2162,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125023359</v>
+        <v>125023374</v>
       </c>
       <c r="B16" t="n">
         <v>79891</v>
@@ -2194,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753753</v>
+        <v>753763</v>
       </c>
       <c r="R16" t="n">
-        <v>7217910</v>
+        <v>7218015</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125023335</v>
+        <v>125023343</v>
       </c>
       <c r="B17" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2268,25 +2276,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2296,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753790</v>
+        <v>753760</v>
       </c>
       <c r="R17" t="n">
-        <v>7217992</v>
+        <v>7218023</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2334,12 +2342,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2358,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125023351</v>
+        <v>125023333</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2374,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2398,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753758</v>
+        <v>753781</v>
       </c>
       <c r="R18" t="n">
-        <v>7217819</v>
+        <v>7217902</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2460,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125023343</v>
+        <v>125023441</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2476,21 +2490,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2500,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753760</v>
+        <v>753798</v>
       </c>
       <c r="R19" t="n">
-        <v>7218023</v>
+        <v>7217948</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,7 +2554,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2549,7 +2563,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2568,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125023399</v>
+        <v>125023338</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>8720</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2580,25 +2593,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smal trollknäppare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Danosoma conspersum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyllenhal, 1808)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2608,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753751</v>
+        <v>753699</v>
       </c>
       <c r="R20" t="n">
-        <v>7217806</v>
+        <v>7217618</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2652,6 +2665,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2670,7 +2684,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125023391</v>
+        <v>125023388</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2710,10 +2724,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753706</v>
+        <v>753742</v>
       </c>
       <c r="R21" t="n">
-        <v>7218039</v>
+        <v>7217924</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2772,10 +2786,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125023342</v>
+        <v>125023358</v>
       </c>
       <c r="B22" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2788,21 +2802,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2812,10 +2826,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753722</v>
+        <v>753758</v>
       </c>
       <c r="R22" t="n">
-        <v>7217596</v>
+        <v>7217900</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2856,7 +2870,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2875,10 +2888,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125023434</v>
+        <v>125023363</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2891,42 +2904,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753797</v>
+        <v>753782</v>
       </c>
       <c r="R23" t="n">
-        <v>7217988</v>
+        <v>7217946</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2959,11 +2964,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2990,10 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125023398</v>
+        <v>125023357</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3006,41 +3006,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753778</v>
+        <v>753793</v>
       </c>
       <c r="R24" t="n">
-        <v>7217858</v>
+        <v>7217856</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,18 +3068,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3105,10 +3092,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125023414</v>
+        <v>125023349</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3121,21 +3108,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3145,10 +3132,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753630</v>
+        <v>753795</v>
       </c>
       <c r="R25" t="n">
-        <v>7218006</v>
+        <v>7217800</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3207,10 +3194,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125023341</v>
+        <v>125023404</v>
       </c>
       <c r="B26" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,25 +3206,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3247,10 +3234,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753654</v>
+        <v>753743</v>
       </c>
       <c r="R26" t="n">
-        <v>7218008</v>
+        <v>7218044</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3309,10 +3296,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125023365</v>
+        <v>125023430</v>
       </c>
       <c r="B27" t="n">
-        <v>79891</v>
+        <v>79926</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3321,25 +3308,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3349,10 +3336,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753784</v>
+        <v>753789</v>
       </c>
       <c r="R27" t="n">
-        <v>7217948</v>
+        <v>7217809</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3411,10 +3398,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125023441</v>
+        <v>125023389</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3423,25 +3410,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3451,10 +3438,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753798</v>
+        <v>753729</v>
       </c>
       <c r="R28" t="n">
-        <v>7217948</v>
+        <v>7218042</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3487,11 +3474,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3518,7 +3500,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125023368</v>
+        <v>125023359</v>
       </c>
       <c r="B29" t="n">
         <v>79891</v>
@@ -3558,10 +3540,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753808</v>
+        <v>753753</v>
       </c>
       <c r="R29" t="n">
-        <v>7217964</v>
+        <v>7217910</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3620,10 +3602,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125023401</v>
+        <v>125023429</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3632,20 +3614,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3660,10 +3642,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753780</v>
+        <v>753792</v>
       </c>
       <c r="R30" t="n">
-        <v>7217865</v>
+        <v>7217798</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3722,10 +3704,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125023406</v>
+        <v>125023365</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3738,21 +3720,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3762,10 +3744,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753718</v>
+        <v>753784</v>
       </c>
       <c r="R31" t="n">
-        <v>7218042</v>
+        <v>7217948</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3824,10 +3806,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125023419</v>
+        <v>125023323</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3840,21 +3822,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3864,10 +3846,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753550</v>
+        <v>753504</v>
       </c>
       <c r="R32" t="n">
-        <v>7217725</v>
+        <v>7217889</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3926,10 +3908,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125023442</v>
+        <v>125023423</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3942,21 +3924,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3966,10 +3948,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753726</v>
+        <v>753610</v>
       </c>
       <c r="R33" t="n">
-        <v>7218039</v>
+        <v>7217727</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4002,11 +3984,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4033,10 +4010,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125023326</v>
+        <v>125023390</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4045,46 +4022,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753598</v>
+        <v>753701</v>
       </c>
       <c r="R34" t="n">
-        <v>7217744</v>
+        <v>7218031</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4117,11 +4086,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4148,10 +4112,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125023324</v>
+        <v>125023337</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>79795</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4160,25 +4124,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4188,10 +4152,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753480</v>
+        <v>753523</v>
       </c>
       <c r="R35" t="n">
-        <v>7218033</v>
+        <v>7218086</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4250,10 +4214,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125023358</v>
+        <v>125023435</v>
       </c>
       <c r="B36" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4266,34 +4230,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753758</v>
+        <v>753562</v>
       </c>
       <c r="R36" t="n">
-        <v>7217900</v>
+        <v>7217727</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4326,6 +4298,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4352,10 +4329,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125023373</v>
+        <v>125023321</v>
       </c>
       <c r="B37" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4368,21 +4345,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4392,10 +4369,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753768</v>
+        <v>753679</v>
       </c>
       <c r="R37" t="n">
-        <v>7218016</v>
+        <v>7218005</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4454,10 +4431,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125023430</v>
+        <v>125023426</v>
       </c>
       <c r="B38" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4466,20 +4443,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4494,10 +4471,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753789</v>
+        <v>753597</v>
       </c>
       <c r="R38" t="n">
-        <v>7217809</v>
+        <v>7217728</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4556,10 +4533,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125023334</v>
+        <v>125023418</v>
       </c>
       <c r="B39" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4568,25 +4545,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4596,10 +4573,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753752</v>
+        <v>753406</v>
       </c>
       <c r="R39" t="n">
-        <v>7217919</v>
+        <v>7217999</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4658,10 +4635,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125023357</v>
+        <v>125023416</v>
       </c>
       <c r="B40" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4674,21 +4651,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4698,10 +4675,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753793</v>
+        <v>753470</v>
       </c>
       <c r="R40" t="n">
-        <v>7217856</v>
+        <v>7218024</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4760,7 +4737,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125023366</v>
+        <v>125023351</v>
       </c>
       <c r="B41" t="n">
         <v>79891</v>
@@ -4800,10 +4777,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753778</v>
+        <v>753758</v>
       </c>
       <c r="R41" t="n">
-        <v>7217945</v>
+        <v>7217819</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4862,10 +4839,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125023405</v>
+        <v>125023373</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4878,21 +4855,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4902,10 +4879,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753748</v>
+        <v>753768</v>
       </c>
       <c r="R42" t="n">
-        <v>7218047</v>
+        <v>7218016</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4964,10 +4941,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125023338</v>
+        <v>125023347</v>
       </c>
       <c r="B43" t="n">
-        <v>8720</v>
+        <v>79891</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4976,25 +4953,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100798</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Smal trollknäppare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Danosoma conspersum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5004,10 +4981,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753699</v>
+        <v>753850</v>
       </c>
       <c r="R43" t="n">
-        <v>7217618</v>
+        <v>7217843</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5048,7 +5025,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5067,10 +5043,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125023438</v>
+        <v>125023330</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5083,21 +5059,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5107,10 +5083,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753612</v>
+        <v>753730</v>
       </c>
       <c r="R44" t="n">
-        <v>7217703</v>
+        <v>7217943</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5143,11 +5119,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5174,10 +5145,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125023345</v>
+        <v>125023387</v>
       </c>
       <c r="B45" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5190,21 +5161,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5214,10 +5185,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753790</v>
+        <v>753816</v>
       </c>
       <c r="R45" t="n">
-        <v>7217981</v>
+        <v>7217838</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5276,10 +5247,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125023369</v>
+        <v>125023414</v>
       </c>
       <c r="B46" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5292,21 +5263,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5316,10 +5287,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753797</v>
+        <v>753630</v>
       </c>
       <c r="R46" t="n">
-        <v>7218005</v>
+        <v>7218006</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5378,10 +5349,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125023411</v>
+        <v>125023431</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5390,20 +5361,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5418,10 +5389,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753557</v>
+        <v>753774</v>
       </c>
       <c r="R47" t="n">
-        <v>7217895</v>
+        <v>7217939</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5480,10 +5451,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125023426</v>
+        <v>125023378</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5496,21 +5467,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5520,10 +5491,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753597</v>
+        <v>753722</v>
       </c>
       <c r="R48" t="n">
-        <v>7217728</v>
+        <v>7218033</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5582,10 +5553,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125023413</v>
+        <v>125023444</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5598,21 +5569,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5622,10 +5593,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753517</v>
+        <v>753746</v>
       </c>
       <c r="R49" t="n">
-        <v>7217918</v>
+        <v>7217930</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5658,6 +5629,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5684,10 +5660,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125023435</v>
+        <v>125023409</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5700,32 +5676,24 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
@@ -5735,7 +5703,7 @@
         <v>753562</v>
       </c>
       <c r="R50" t="n">
-        <v>7217727</v>
+        <v>7217917</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5768,11 +5736,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5799,10 +5762,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125023390</v>
+        <v>125023366</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5811,25 +5774,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5839,10 +5802,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753701</v>
+        <v>753778</v>
       </c>
       <c r="R51" t="n">
-        <v>7218031</v>
+        <v>7217945</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5901,7 +5864,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125023319</v>
+        <v>125023318</v>
       </c>
       <c r="B52" t="n">
         <v>90977</v>
@@ -5941,10 +5904,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>753506</v>
+        <v>753680</v>
       </c>
       <c r="R52" t="n">
-        <v>7217904</v>
+        <v>7218004</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6003,7 +5966,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125023416</v>
+        <v>125023413</v>
       </c>
       <c r="B53" t="n">
         <v>78810</v>
@@ -6043,10 +6006,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>753470</v>
+        <v>753517</v>
       </c>
       <c r="R53" t="n">
-        <v>7218024</v>
+        <v>7217918</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6105,10 +6068,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125023387</v>
+        <v>125023432</v>
       </c>
       <c r="B54" t="n">
-        <v>78546</v>
+        <v>79926</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6117,25 +6080,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6145,10 +6108,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753816</v>
+        <v>753769</v>
       </c>
       <c r="R54" t="n">
-        <v>7217838</v>
+        <v>7218019</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6207,10 +6170,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125023404</v>
+        <v>125023380</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6219,25 +6182,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6247,10 +6210,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753743</v>
+        <v>753769</v>
       </c>
       <c r="R55" t="n">
-        <v>7218044</v>
+        <v>7218019</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6309,10 +6272,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125023352</v>
+        <v>125023411</v>
       </c>
       <c r="B56" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6325,21 +6288,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6349,10 +6312,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753763</v>
+        <v>753557</v>
       </c>
       <c r="R56" t="n">
-        <v>7217831</v>
+        <v>7217895</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6411,7 +6374,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125023372</v>
+        <v>125023355</v>
       </c>
       <c r="B57" t="n">
         <v>79891</v>
@@ -6451,10 +6414,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753790</v>
+        <v>753792</v>
       </c>
       <c r="R57" t="n">
-        <v>7217992</v>
+        <v>7217850</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6513,10 +6476,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125023446</v>
+        <v>125023368</v>
       </c>
       <c r="B58" t="n">
-        <v>91221</v>
+        <v>79891</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6525,25 +6488,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1106</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6553,10 +6516,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753567</v>
+        <v>753808</v>
       </c>
       <c r="R58" t="n">
-        <v>7217721</v>
+        <v>7217964</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6597,7 +6560,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6616,7 +6578,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125023439</v>
+        <v>125023434</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -6650,16 +6612,24 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753568</v>
+        <v>753797</v>
       </c>
       <c r="R59" t="n">
-        <v>7217716</v>
+        <v>7217988</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6696,7 +6666,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Barksprätt</t>
+          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6723,7 +6693,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125023316</v>
+        <v>125023438</v>
       </c>
       <c r="B60" t="n">
         <v>57513</v>
@@ -6757,24 +6727,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753568</v>
+        <v>753612</v>
       </c>
       <c r="R60" t="n">
-        <v>7217733</v>
+        <v>7217703</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6811,7 +6773,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Äldre bohål</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6838,10 +6800,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125023330</v>
+        <v>125023443</v>
       </c>
       <c r="B61" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6854,21 +6816,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6878,10 +6840,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753730</v>
+        <v>753575</v>
       </c>
       <c r="R61" t="n">
-        <v>7217943</v>
+        <v>7217751</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6914,6 +6876,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6940,10 +6907,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125023321</v>
+        <v>125023342</v>
       </c>
       <c r="B62" t="n">
-        <v>91012</v>
+        <v>78547</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6956,21 +6923,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6980,10 +6947,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753679</v>
+        <v>753722</v>
       </c>
       <c r="R62" t="n">
-        <v>7218005</v>
+        <v>7217596</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7024,6 +6991,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7042,7 +7010,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125023396</v>
+        <v>125023420</v>
       </c>
       <c r="B63" t="n">
         <v>78810</v>
@@ -7076,23 +7044,16 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753626</v>
+        <v>753559</v>
       </c>
       <c r="R63" t="n">
-        <v>7218004</v>
+        <v>7217734</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7127,18 +7088,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7157,10 +7112,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125023429</v>
+        <v>125023392</v>
       </c>
       <c r="B64" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7169,25 +7124,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7197,10 +7152,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753792</v>
+        <v>753718</v>
       </c>
       <c r="R64" t="n">
-        <v>7217798</v>
+        <v>7218035</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7259,10 +7214,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125023315</v>
+        <v>125023394</v>
       </c>
       <c r="B65" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7275,21 +7230,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7299,10 +7254,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753491</v>
+        <v>753596</v>
       </c>
       <c r="R65" t="n">
-        <v>7217766</v>
+        <v>7217939</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7335,11 +7290,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7366,10 +7316,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125023432</v>
+        <v>125023419</v>
       </c>
       <c r="B66" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7378,20 +7328,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7406,10 +7356,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753769</v>
+        <v>753550</v>
       </c>
       <c r="R66" t="n">
-        <v>7218019</v>
+        <v>7217725</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7468,10 +7418,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125023380</v>
+        <v>125023341</v>
       </c>
       <c r="B67" t="n">
-        <v>79927</v>
+        <v>79919</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7484,21 +7434,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6464</v>
+        <v>6461</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7508,10 +7458,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753769</v>
+        <v>753654</v>
       </c>
       <c r="R67" t="n">
-        <v>7218019</v>
+        <v>7218008</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7570,10 +7520,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125023407</v>
+        <v>125023375</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7586,21 +7536,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7610,10 +7560,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753671</v>
+        <v>753750</v>
       </c>
       <c r="R68" t="n">
-        <v>7218008</v>
+        <v>7218028</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7672,10 +7622,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125023323</v>
+        <v>125023369</v>
       </c>
       <c r="B69" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7688,21 +7638,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7712,10 +7662,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753504</v>
+        <v>753797</v>
       </c>
       <c r="R69" t="n">
-        <v>7217889</v>
+        <v>7218005</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7774,10 +7724,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125023389</v>
+        <v>125023439</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7786,25 +7736,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7814,10 +7764,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753729</v>
+        <v>753568</v>
       </c>
       <c r="R70" t="n">
-        <v>7218042</v>
+        <v>7217716</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7850,6 +7800,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7876,10 +7831,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125023350</v>
+        <v>125023402</v>
       </c>
       <c r="B71" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7892,21 +7847,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7916,10 +7871,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753789</v>
+        <v>753752</v>
       </c>
       <c r="R71" t="n">
-        <v>7217812</v>
+        <v>7217878</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7978,10 +7933,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125023394</v>
+        <v>125023407</v>
       </c>
       <c r="B72" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7994,21 +7949,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8018,10 +7973,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753596</v>
+        <v>753671</v>
       </c>
       <c r="R72" t="n">
-        <v>7217939</v>
+        <v>7218008</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8080,7 +8035,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125023348</v>
+        <v>125023352</v>
       </c>
       <c r="B73" t="n">
         <v>79891</v>
@@ -8120,10 +8075,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>753817</v>
+        <v>753763</v>
       </c>
       <c r="R73" t="n">
-        <v>7217853</v>
+        <v>7217831</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8182,10 +8137,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125023349</v>
+        <v>125023324</v>
       </c>
       <c r="B74" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8198,21 +8153,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8222,10 +8177,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>753795</v>
+        <v>753480</v>
       </c>
       <c r="R74" t="n">
-        <v>7217800</v>
+        <v>7218033</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8284,10 +8239,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125023336</v>
+        <v>125023401</v>
       </c>
       <c r="B75" t="n">
-        <v>90962</v>
+        <v>78810</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8300,21 +8255,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8324,10 +8279,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>753566</v>
+        <v>753780</v>
       </c>
       <c r="R75" t="n">
-        <v>7217862</v>
+        <v>7217865</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8386,10 +8341,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125023320</v>
+        <v>125023335</v>
       </c>
       <c r="B76" t="n">
-        <v>91012</v>
+        <v>79920</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8398,25 +8353,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8426,10 +8381,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>753687</v>
+        <v>753790</v>
       </c>
       <c r="R76" t="n">
-        <v>7217999</v>
+        <v>7217992</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8488,10 +8443,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125023318</v>
+        <v>125023348</v>
       </c>
       <c r="B77" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8500,25 +8455,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8528,10 +8483,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>753680</v>
+        <v>753817</v>
       </c>
       <c r="R77" t="n">
-        <v>7218004</v>
+        <v>7217853</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8590,10 +8545,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125023412</v>
+        <v>125023367</v>
       </c>
       <c r="B78" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8606,21 +8561,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8630,10 +8585,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>753568</v>
+        <v>753786</v>
       </c>
       <c r="R78" t="n">
-        <v>7217875</v>
+        <v>7217962</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8692,10 +8647,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125023409</v>
+        <v>125023328</v>
       </c>
       <c r="B79" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8708,21 +8663,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8732,10 +8687,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>753562</v>
+        <v>753742</v>
       </c>
       <c r="R79" t="n">
-        <v>7217917</v>
+        <v>7217926</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8794,10 +8749,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125023402</v>
+        <v>125023391</v>
       </c>
       <c r="B80" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8806,25 +8761,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8834,10 +8789,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>753752</v>
+        <v>753706</v>
       </c>
       <c r="R80" t="n">
-        <v>7217878</v>
+        <v>7218039</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8896,10 +8851,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125023337</v>
+        <v>125023445</v>
       </c>
       <c r="B81" t="n">
-        <v>79795</v>
+        <v>57513</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8908,25 +8863,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8936,10 +8891,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>753523</v>
+        <v>753715</v>
       </c>
       <c r="R81" t="n">
-        <v>7218086</v>
+        <v>7218026</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8972,6 +8927,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8998,10 +8958,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125023347</v>
+        <v>125023442</v>
       </c>
       <c r="B82" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9014,21 +8974,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9038,10 +8998,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>753850</v>
+        <v>753726</v>
       </c>
       <c r="R82" t="n">
-        <v>7217843</v>
+        <v>7218039</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9074,6 +9034,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9100,10 +9065,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125023431</v>
+        <v>125023336</v>
       </c>
       <c r="B83" t="n">
-        <v>79926</v>
+        <v>90962</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9112,25 +9077,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6463</v>
+        <v>112</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9140,10 +9105,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>753774</v>
+        <v>753566</v>
       </c>
       <c r="R83" t="n">
-        <v>7217939</v>
+        <v>7217862</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9202,10 +9167,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125023421</v>
+        <v>125023350</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9218,21 +9183,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9242,10 +9207,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>753573</v>
+        <v>753789</v>
       </c>
       <c r="R84" t="n">
-        <v>7217745</v>
+        <v>7217812</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9304,10 +9269,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125023423</v>
+        <v>125023334</v>
       </c>
       <c r="B85" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9316,25 +9281,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9344,10 +9309,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>753610</v>
+        <v>753752</v>
       </c>
       <c r="R85" t="n">
-        <v>7217727</v>
+        <v>7217919</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9406,10 +9371,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125023333</v>
+        <v>125023421</v>
       </c>
       <c r="B86" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9422,21 +9387,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9446,10 +9411,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>753781</v>
+        <v>753573</v>
       </c>
       <c r="R86" t="n">
-        <v>7217902</v>
+        <v>7217745</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9508,10 +9473,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125023418</v>
+        <v>125023319</v>
       </c>
       <c r="B87" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9520,25 +9485,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9548,10 +9513,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>753406</v>
+        <v>753506</v>
       </c>
       <c r="R87" t="n">
-        <v>7217999</v>
+        <v>7217904</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9610,10 +9575,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125023417</v>
+        <v>125023345</v>
       </c>
       <c r="B88" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9626,21 +9591,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9650,10 +9615,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>753474</v>
+        <v>753790</v>
       </c>
       <c r="R88" t="n">
-        <v>7218026</v>
+        <v>7217981</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9712,10 +9677,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125023444</v>
+        <v>125023412</v>
       </c>
       <c r="B89" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9728,21 +9693,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9752,10 +9717,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>753746</v>
+        <v>753568</v>
       </c>
       <c r="R89" t="n">
-        <v>7217930</v>
+        <v>7217875</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9788,11 +9753,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9819,10 +9779,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125023392</v>
+        <v>125023405</v>
       </c>
       <c r="B90" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9831,25 +9791,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9859,10 +9819,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>753718</v>
+        <v>753748</v>
       </c>
       <c r="R90" t="n">
-        <v>7218035</v>
+        <v>7218047</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9921,10 +9881,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125023381</v>
+        <v>125023326</v>
       </c>
       <c r="B91" t="n">
-        <v>79927</v>
+        <v>57513</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9933,38 +9893,46 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>753722</v>
+        <v>753598</v>
       </c>
       <c r="R91" t="n">
-        <v>7218033</v>
+        <v>7217744</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9997,6 +9965,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10023,10 +9996,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125023378</v>
+        <v>125023395</v>
       </c>
       <c r="B92" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10039,21 +10012,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10063,10 +10036,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>753722</v>
+        <v>753472</v>
       </c>
       <c r="R92" t="n">
-        <v>7218033</v>
+        <v>7218031</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10125,7 +10098,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125023375</v>
+        <v>125023354</v>
       </c>
       <c r="B93" t="n">
         <v>79891</v>
@@ -10165,10 +10138,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>753750</v>
+        <v>753773</v>
       </c>
       <c r="R93" t="n">
-        <v>7218028</v>
+        <v>7217842</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10227,10 +10200,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125023374</v>
+        <v>125023446</v>
       </c>
       <c r="B94" t="n">
-        <v>79891</v>
+        <v>91221</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10239,25 +10212,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>1106</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10267,10 +10240,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>753763</v>
+        <v>753567</v>
       </c>
       <c r="R94" t="n">
-        <v>7218015</v>
+        <v>7217721</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10311,6 +10284,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10329,10 +10303,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125023395</v>
+        <v>125023316</v>
       </c>
       <c r="B95" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10345,34 +10319,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>753472</v>
+        <v>753568</v>
       </c>
       <c r="R95" t="n">
-        <v>7218031</v>
+        <v>7217733</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10405,6 +10387,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10431,10 +10418,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125023388</v>
+        <v>125023398</v>
       </c>
       <c r="B96" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10443,38 +10430,45 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>753742</v>
+        <v>753778</v>
       </c>
       <c r="R96" t="n">
-        <v>7217924</v>
+        <v>7217858</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10509,12 +10503,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125023406</v>
+        <v>125023355</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753718</v>
+        <v>753792</v>
       </c>
       <c r="R4" t="n">
-        <v>7218042</v>
+        <v>7217850</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125023320</v>
+        <v>125023374</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,21 +1025,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753687</v>
+        <v>753763</v>
       </c>
       <c r="R5" t="n">
-        <v>7217999</v>
+        <v>7218015</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125023403</v>
+        <v>125023373</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,21 +1127,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753762</v>
+        <v>753768</v>
       </c>
       <c r="R6" t="n">
-        <v>7218015</v>
+        <v>7218016</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125023372</v>
+        <v>125023405</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>753790</v>
+        <v>753748</v>
       </c>
       <c r="R7" t="n">
-        <v>7217992</v>
+        <v>7218047</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125023325</v>
+        <v>125023419</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,42 +1331,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>753575</v>
+        <v>753550</v>
       </c>
       <c r="R8" t="n">
-        <v>7217959</v>
+        <v>7217725</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,11 +1391,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125023327</v>
+        <v>125023325</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,34 +1433,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>753740</v>
+        <v>753575</v>
       </c>
       <c r="R9" t="n">
-        <v>7217891</v>
+        <v>7217959</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,6 +1501,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125023399</v>
+        <v>125023444</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,21 +1548,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>753751</v>
+        <v>753746</v>
       </c>
       <c r="R10" t="n">
-        <v>7217806</v>
+        <v>7217930</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,6 +1608,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125023417</v>
+        <v>125023343</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>753474</v>
+        <v>753760</v>
       </c>
       <c r="R11" t="n">
-        <v>7218026</v>
+        <v>7218023</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,12 +1717,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1736,10 +1747,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023396</v>
+        <v>125023349</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,41 +1763,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>753626</v>
+        <v>753795</v>
       </c>
       <c r="R12" t="n">
-        <v>7218004</v>
+        <v>7217800</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,18 +1825,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1851,10 +1849,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125023315</v>
+        <v>125023389</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,25 +1861,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1889,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753491</v>
+        <v>753729</v>
       </c>
       <c r="R13" t="n">
-        <v>7217766</v>
+        <v>7218042</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,11 +1925,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1958,10 +1951,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125023381</v>
+        <v>125023321</v>
       </c>
       <c r="B14" t="n">
-        <v>79927</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,25 +1963,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1998,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753722</v>
+        <v>753679</v>
       </c>
       <c r="R14" t="n">
-        <v>7218033</v>
+        <v>7218005</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,7 +2053,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125023360</v>
+        <v>125023358</v>
       </c>
       <c r="B15" t="n">
         <v>79891</v>
@@ -2100,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>753752</v>
+        <v>753758</v>
       </c>
       <c r="R15" t="n">
-        <v>7217944</v>
+        <v>7217900</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2155,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125023374</v>
+        <v>125023350</v>
       </c>
       <c r="B16" t="n">
         <v>79891</v>
@@ -2202,10 +2195,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753763</v>
+        <v>753789</v>
       </c>
       <c r="R16" t="n">
-        <v>7218015</v>
+        <v>7217812</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2264,10 +2257,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125023343</v>
+        <v>125023426</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2280,21 +2273,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2304,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753760</v>
+        <v>753597</v>
       </c>
       <c r="R17" t="n">
-        <v>7218023</v>
+        <v>7217728</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,18 +2335,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2372,10 +2359,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125023333</v>
+        <v>125023434</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,34 +2375,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753781</v>
+        <v>753797</v>
       </c>
       <c r="R18" t="n">
-        <v>7217902</v>
+        <v>7217988</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2448,6 +2443,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125023441</v>
+        <v>125023354</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2490,21 +2490,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753798</v>
+        <v>753773</v>
       </c>
       <c r="R19" t="n">
-        <v>7217948</v>
+        <v>7217842</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,11 +2550,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125023338</v>
+        <v>125023409</v>
       </c>
       <c r="B20" t="n">
-        <v>8720</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2593,25 +2588,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100798</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smal trollknäppare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Danosoma conspersum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2621,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753699</v>
+        <v>753562</v>
       </c>
       <c r="R20" t="n">
-        <v>7217618</v>
+        <v>7217917</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2665,7 +2660,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2684,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125023388</v>
+        <v>125023351</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2696,25 +2690,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2724,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753742</v>
+        <v>753758</v>
       </c>
       <c r="R21" t="n">
-        <v>7217924</v>
+        <v>7217819</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2786,10 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125023358</v>
+        <v>125023381</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2798,25 +2792,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2826,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753758</v>
+        <v>753722</v>
       </c>
       <c r="R22" t="n">
-        <v>7217900</v>
+        <v>7218033</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2888,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125023363</v>
+        <v>125023341</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>79919</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2900,25 +2894,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2928,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753782</v>
+        <v>753654</v>
       </c>
       <c r="R23" t="n">
-        <v>7217946</v>
+        <v>7218008</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,7 +2984,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125023357</v>
+        <v>125023378</v>
       </c>
       <c r="B24" t="n">
         <v>79891</v>
@@ -3030,10 +3024,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753793</v>
+        <v>753722</v>
       </c>
       <c r="R24" t="n">
-        <v>7217856</v>
+        <v>7218033</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,10 +3086,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125023349</v>
+        <v>125023413</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3108,21 +3102,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3132,10 +3126,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753795</v>
+        <v>753517</v>
       </c>
       <c r="R25" t="n">
-        <v>7217800</v>
+        <v>7217918</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3194,10 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125023404</v>
+        <v>125023319</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3206,25 +3200,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3234,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753743</v>
+        <v>753506</v>
       </c>
       <c r="R26" t="n">
-        <v>7218044</v>
+        <v>7217904</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3296,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125023430</v>
+        <v>125023442</v>
       </c>
       <c r="B27" t="n">
-        <v>79926</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3308,25 +3302,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3336,10 +3330,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753789</v>
+        <v>753726</v>
       </c>
       <c r="R27" t="n">
-        <v>7217809</v>
+        <v>7218039</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,6 +3366,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3398,10 +3397,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125023389</v>
+        <v>125023435</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3410,38 +3409,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753729</v>
+        <v>753562</v>
       </c>
       <c r="R28" t="n">
-        <v>7218042</v>
+        <v>7217727</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3474,6 +3481,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3500,10 +3512,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125023359</v>
+        <v>125023420</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3516,21 +3528,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3540,10 +3552,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753753</v>
+        <v>753559</v>
       </c>
       <c r="R29" t="n">
-        <v>7217910</v>
+        <v>7217734</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,10 +3614,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125023429</v>
+        <v>125023394</v>
       </c>
       <c r="B30" t="n">
-        <v>79926</v>
+        <v>91030</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3614,25 +3626,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3642,10 +3654,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753792</v>
+        <v>753596</v>
       </c>
       <c r="R30" t="n">
-        <v>7217798</v>
+        <v>7217939</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3704,10 +3716,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125023365</v>
+        <v>125023423</v>
       </c>
       <c r="B31" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3720,21 +3732,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3744,10 +3756,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753784</v>
+        <v>753610</v>
       </c>
       <c r="R31" t="n">
-        <v>7217948</v>
+        <v>7217727</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3806,10 +3818,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125023323</v>
+        <v>125023432</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>79926</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3818,25 +3830,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3846,10 +3858,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753504</v>
+        <v>753769</v>
       </c>
       <c r="R32" t="n">
-        <v>7217889</v>
+        <v>7218019</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3908,10 +3920,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125023423</v>
+        <v>125023337</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>79795</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3920,25 +3932,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3948,10 +3960,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753610</v>
+        <v>753523</v>
       </c>
       <c r="R33" t="n">
-        <v>7217727</v>
+        <v>7218086</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4010,10 +4022,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125023390</v>
+        <v>125023352</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4022,25 +4034,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4050,10 +4062,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753701</v>
+        <v>753763</v>
       </c>
       <c r="R34" t="n">
-        <v>7218031</v>
+        <v>7217831</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4112,10 +4124,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125023337</v>
+        <v>125023402</v>
       </c>
       <c r="B35" t="n">
-        <v>79795</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4124,25 +4136,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4152,10 +4164,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753523</v>
+        <v>753752</v>
       </c>
       <c r="R35" t="n">
-        <v>7218086</v>
+        <v>7217878</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4214,10 +4226,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125023435</v>
+        <v>125023375</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4230,42 +4242,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753562</v>
+        <v>753750</v>
       </c>
       <c r="R36" t="n">
-        <v>7217727</v>
+        <v>7218028</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4298,11 +4302,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4329,10 +4328,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125023321</v>
+        <v>125023365</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4345,21 +4344,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4369,10 +4368,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753679</v>
+        <v>753784</v>
       </c>
       <c r="R37" t="n">
-        <v>7218005</v>
+        <v>7217948</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4431,10 +4430,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125023426</v>
+        <v>125023430</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4443,20 +4442,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4471,10 +4470,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753597</v>
+        <v>753789</v>
       </c>
       <c r="R38" t="n">
-        <v>7217728</v>
+        <v>7217809</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4533,10 +4532,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125023418</v>
+        <v>125023368</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4549,21 +4548,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4573,10 +4572,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753406</v>
+        <v>753808</v>
       </c>
       <c r="R39" t="n">
-        <v>7217999</v>
+        <v>7217964</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4635,10 +4634,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125023416</v>
+        <v>125023326</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4651,34 +4650,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753470</v>
+        <v>753598</v>
       </c>
       <c r="R40" t="n">
-        <v>7218024</v>
+        <v>7217744</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4711,6 +4718,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4737,10 +4749,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125023351</v>
+        <v>125023333</v>
       </c>
       <c r="B41" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4753,21 +4765,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4777,10 +4789,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753758</v>
+        <v>753781</v>
       </c>
       <c r="R41" t="n">
-        <v>7217819</v>
+        <v>7217902</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4839,10 +4851,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125023373</v>
+        <v>125023320</v>
       </c>
       <c r="B42" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4855,21 +4867,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4879,10 +4891,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753768</v>
+        <v>753687</v>
       </c>
       <c r="R42" t="n">
-        <v>7218016</v>
+        <v>7217999</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4941,10 +4953,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125023347</v>
+        <v>125023335</v>
       </c>
       <c r="B43" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4953,25 +4965,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4981,10 +4993,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753850</v>
+        <v>753790</v>
       </c>
       <c r="R43" t="n">
-        <v>7217843</v>
+        <v>7217992</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5043,10 +5055,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125023330</v>
+        <v>125023431</v>
       </c>
       <c r="B44" t="n">
-        <v>57666</v>
+        <v>79926</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5055,25 +5067,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5083,10 +5095,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753730</v>
+        <v>753774</v>
       </c>
       <c r="R44" t="n">
-        <v>7217943</v>
+        <v>7217939</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5145,10 +5157,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125023387</v>
+        <v>125023334</v>
       </c>
       <c r="B45" t="n">
-        <v>78546</v>
+        <v>79920</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5157,25 +5169,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5185,10 +5197,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753816</v>
+        <v>753752</v>
       </c>
       <c r="R45" t="n">
-        <v>7217838</v>
+        <v>7217919</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5247,10 +5259,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125023414</v>
+        <v>125023366</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5263,21 +5275,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5287,10 +5299,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753630</v>
+        <v>753778</v>
       </c>
       <c r="R46" t="n">
-        <v>7218006</v>
+        <v>7217945</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5349,10 +5361,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125023431</v>
+        <v>125023445</v>
       </c>
       <c r="B47" t="n">
-        <v>79926</v>
+        <v>57513</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5361,25 +5373,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5389,10 +5401,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753774</v>
+        <v>753715</v>
       </c>
       <c r="R47" t="n">
-        <v>7217939</v>
+        <v>7218026</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5425,6 +5437,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5451,10 +5468,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125023378</v>
+        <v>125023407</v>
       </c>
       <c r="B48" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5467,21 +5484,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5491,10 +5508,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753722</v>
+        <v>753671</v>
       </c>
       <c r="R48" t="n">
-        <v>7218033</v>
+        <v>7218008</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5553,10 +5570,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125023444</v>
+        <v>125023336</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>90962</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5569,21 +5586,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5593,10 +5610,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753746</v>
+        <v>753566</v>
       </c>
       <c r="R49" t="n">
-        <v>7217930</v>
+        <v>7217862</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5629,11 +5646,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5660,10 +5672,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125023409</v>
+        <v>125023318</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5672,25 +5684,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5700,10 +5712,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753562</v>
+        <v>753680</v>
       </c>
       <c r="R50" t="n">
-        <v>7217917</v>
+        <v>7218004</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5762,10 +5774,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125023366</v>
+        <v>125023411</v>
       </c>
       <c r="B51" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5778,21 +5790,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5802,10 +5814,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753778</v>
+        <v>753557</v>
       </c>
       <c r="R51" t="n">
-        <v>7217945</v>
+        <v>7217895</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5864,10 +5876,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125023318</v>
+        <v>125023345</v>
       </c>
       <c r="B52" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5876,25 +5888,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5904,10 +5916,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>753680</v>
+        <v>753790</v>
       </c>
       <c r="R52" t="n">
-        <v>7218004</v>
+        <v>7217981</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5966,10 +5978,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125023413</v>
+        <v>125023328</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5982,21 +5994,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6006,10 +6018,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>753517</v>
+        <v>753742</v>
       </c>
       <c r="R53" t="n">
-        <v>7217918</v>
+        <v>7217926</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6068,10 +6080,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125023432</v>
+        <v>125023392</v>
       </c>
       <c r="B54" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6080,25 +6092,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6108,10 +6120,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753769</v>
+        <v>753718</v>
       </c>
       <c r="R54" t="n">
-        <v>7218019</v>
+        <v>7218035</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6170,10 +6182,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125023380</v>
+        <v>125023443</v>
       </c>
       <c r="B55" t="n">
-        <v>79927</v>
+        <v>57513</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6182,25 +6194,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6210,10 +6222,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753769</v>
+        <v>753575</v>
       </c>
       <c r="R55" t="n">
-        <v>7218019</v>
+        <v>7217751</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6246,6 +6258,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6272,10 +6289,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125023411</v>
+        <v>125023429</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6284,20 +6301,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6312,10 +6329,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753557</v>
+        <v>753792</v>
       </c>
       <c r="R56" t="n">
-        <v>7217895</v>
+        <v>7217798</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6374,7 +6391,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125023355</v>
+        <v>125023357</v>
       </c>
       <c r="B57" t="n">
         <v>79891</v>
@@ -6414,10 +6431,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753792</v>
+        <v>753793</v>
       </c>
       <c r="R57" t="n">
-        <v>7217850</v>
+        <v>7217856</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6476,7 +6493,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125023368</v>
+        <v>125023347</v>
       </c>
       <c r="B58" t="n">
         <v>79891</v>
@@ -6516,10 +6533,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753808</v>
+        <v>753850</v>
       </c>
       <c r="R58" t="n">
-        <v>7217964</v>
+        <v>7217843</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6578,10 +6595,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125023434</v>
+        <v>125023342</v>
       </c>
       <c r="B59" t="n">
-        <v>57513</v>
+        <v>78547</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6594,42 +6611,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753797</v>
+        <v>753722</v>
       </c>
       <c r="R59" t="n">
-        <v>7217988</v>
+        <v>7217596</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6664,17 +6673,13 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6693,10 +6698,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125023438</v>
+        <v>125023418</v>
       </c>
       <c r="B60" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6709,21 +6714,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6733,10 +6738,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753612</v>
+        <v>753406</v>
       </c>
       <c r="R60" t="n">
-        <v>7217703</v>
+        <v>7217999</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6769,11 +6774,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6800,10 +6800,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125023443</v>
+        <v>125023421</v>
       </c>
       <c r="B61" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6816,21 +6816,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6840,10 +6840,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753575</v>
+        <v>753573</v>
       </c>
       <c r="R61" t="n">
-        <v>7217751</v>
+        <v>7217745</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6876,11 +6876,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6907,10 +6902,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125023342</v>
+        <v>125023406</v>
       </c>
       <c r="B62" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6923,21 +6918,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6947,10 +6942,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753722</v>
+        <v>753718</v>
       </c>
       <c r="R62" t="n">
-        <v>7217596</v>
+        <v>7218042</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6991,7 +6986,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7010,10 +7004,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125023420</v>
+        <v>125023323</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7026,21 +7020,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7050,10 +7044,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753559</v>
+        <v>753504</v>
       </c>
       <c r="R63" t="n">
-        <v>7217734</v>
+        <v>7217889</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7112,10 +7106,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125023392</v>
+        <v>125023338</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>8720</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7128,21 +7122,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100798</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal trollknäppare</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Danosoma conspersum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyllenhal, 1808)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7152,10 +7146,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753718</v>
+        <v>753699</v>
       </c>
       <c r="R64" t="n">
-        <v>7218035</v>
+        <v>7217618</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7196,6 +7190,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7214,10 +7209,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125023394</v>
+        <v>125023399</v>
       </c>
       <c r="B65" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7230,21 +7225,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7254,10 +7249,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753596</v>
+        <v>753751</v>
       </c>
       <c r="R65" t="n">
-        <v>7217939</v>
+        <v>7217806</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7316,10 +7311,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125023419</v>
+        <v>125023390</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7328,25 +7323,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7356,10 +7351,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753550</v>
+        <v>753701</v>
       </c>
       <c r="R66" t="n">
-        <v>7217725</v>
+        <v>7218031</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7418,10 +7413,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125023341</v>
+        <v>125023359</v>
       </c>
       <c r="B67" t="n">
-        <v>79919</v>
+        <v>79891</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7430,25 +7425,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7458,10 +7453,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753654</v>
+        <v>753753</v>
       </c>
       <c r="R67" t="n">
-        <v>7218008</v>
+        <v>7217910</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7520,7 +7515,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125023375</v>
+        <v>125023367</v>
       </c>
       <c r="B68" t="n">
         <v>79891</v>
@@ -7560,10 +7555,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753750</v>
+        <v>753786</v>
       </c>
       <c r="R68" t="n">
-        <v>7218028</v>
+        <v>7217962</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7622,10 +7617,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125023369</v>
+        <v>125023446</v>
       </c>
       <c r="B69" t="n">
-        <v>79891</v>
+        <v>91221</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7634,25 +7629,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>1106</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7662,10 +7657,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753797</v>
+        <v>753567</v>
       </c>
       <c r="R69" t="n">
-        <v>7218005</v>
+        <v>7217721</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7706,6 +7701,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7724,10 +7720,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125023439</v>
+        <v>125023363</v>
       </c>
       <c r="B70" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7740,21 +7736,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7764,10 +7760,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753568</v>
+        <v>753782</v>
       </c>
       <c r="R70" t="n">
-        <v>7217716</v>
+        <v>7217946</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7800,11 +7796,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7831,10 +7822,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125023402</v>
+        <v>125023369</v>
       </c>
       <c r="B71" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7847,21 +7838,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7871,10 +7862,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753752</v>
+        <v>753797</v>
       </c>
       <c r="R71" t="n">
-        <v>7217878</v>
+        <v>7218005</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7933,10 +7924,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125023407</v>
+        <v>125023395</v>
       </c>
       <c r="B72" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7949,21 +7940,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7973,10 +7964,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753671</v>
+        <v>753472</v>
       </c>
       <c r="R72" t="n">
-        <v>7218008</v>
+        <v>7218031</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8035,10 +8026,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125023352</v>
+        <v>125023403</v>
       </c>
       <c r="B73" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8051,21 +8042,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8075,10 +8066,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>753763</v>
+        <v>753762</v>
       </c>
       <c r="R73" t="n">
-        <v>7217831</v>
+        <v>7218015</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8137,10 +8128,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125023324</v>
+        <v>125023388</v>
       </c>
       <c r="B74" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8149,25 +8140,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8177,10 +8168,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>753480</v>
+        <v>753742</v>
       </c>
       <c r="R74" t="n">
-        <v>7218033</v>
+        <v>7217924</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8341,10 +8332,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125023335</v>
+        <v>125023398</v>
       </c>
       <c r="B76" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8353,38 +8344,45 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>753790</v>
+        <v>753778</v>
       </c>
       <c r="R76" t="n">
-        <v>7217992</v>
+        <v>7217858</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8419,12 +8417,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8443,10 +8447,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125023348</v>
+        <v>125023396</v>
       </c>
       <c r="B77" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8459,34 +8463,41 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>753817</v>
+        <v>753626</v>
       </c>
       <c r="R77" t="n">
-        <v>7217853</v>
+        <v>7218004</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8521,12 +8532,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8545,7 +8562,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125023367</v>
+        <v>125023348</v>
       </c>
       <c r="B78" t="n">
         <v>79891</v>
@@ -8585,10 +8602,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>753786</v>
+        <v>753817</v>
       </c>
       <c r="R78" t="n">
-        <v>7217962</v>
+        <v>7217853</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8647,10 +8664,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125023328</v>
+        <v>125023324</v>
       </c>
       <c r="B79" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8663,21 +8680,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8687,10 +8704,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>753742</v>
+        <v>753480</v>
       </c>
       <c r="R79" t="n">
-        <v>7217926</v>
+        <v>7218033</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8749,10 +8766,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125023391</v>
+        <v>125023412</v>
       </c>
       <c r="B80" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8761,25 +8778,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8789,10 +8806,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>753706</v>
+        <v>753568</v>
       </c>
       <c r="R80" t="n">
-        <v>7218039</v>
+        <v>7217875</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8851,10 +8868,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125023445</v>
+        <v>125023417</v>
       </c>
       <c r="B81" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8867,21 +8884,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8891,7 +8908,7 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>753715</v>
+        <v>753474</v>
       </c>
       <c r="R81" t="n">
         <v>7218026</v>
@@ -8927,11 +8944,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8958,10 +8970,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125023442</v>
+        <v>125023360</v>
       </c>
       <c r="B82" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8974,21 +8986,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8998,10 +9010,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>753726</v>
+        <v>753752</v>
       </c>
       <c r="R82" t="n">
-        <v>7218039</v>
+        <v>7217944</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9034,11 +9046,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9065,10 +9072,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125023336</v>
+        <v>125023438</v>
       </c>
       <c r="B83" t="n">
-        <v>90962</v>
+        <v>57513</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9081,21 +9088,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9105,10 +9112,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>753566</v>
+        <v>753612</v>
       </c>
       <c r="R83" t="n">
-        <v>7217862</v>
+        <v>7217703</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9141,6 +9148,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9167,10 +9179,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125023350</v>
+        <v>125023330</v>
       </c>
       <c r="B84" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9183,21 +9195,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9207,10 +9219,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>753789</v>
+        <v>753730</v>
       </c>
       <c r="R84" t="n">
-        <v>7217812</v>
+        <v>7217943</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9269,10 +9281,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125023334</v>
+        <v>125023327</v>
       </c>
       <c r="B85" t="n">
-        <v>79920</v>
+        <v>57666</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9281,25 +9293,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9309,10 +9321,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>753752</v>
+        <v>753740</v>
       </c>
       <c r="R85" t="n">
-        <v>7217919</v>
+        <v>7217891</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9371,7 +9383,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125023421</v>
+        <v>125023416</v>
       </c>
       <c r="B86" t="n">
         <v>78810</v>
@@ -9411,10 +9423,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>753573</v>
+        <v>753470</v>
       </c>
       <c r="R86" t="n">
-        <v>7217745</v>
+        <v>7218024</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9473,10 +9485,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125023319</v>
+        <v>125023414</v>
       </c>
       <c r="B87" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9485,25 +9497,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9513,10 +9525,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>753506</v>
+        <v>753630</v>
       </c>
       <c r="R87" t="n">
-        <v>7217904</v>
+        <v>7218006</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9575,10 +9587,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125023345</v>
+        <v>125023404</v>
       </c>
       <c r="B88" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9591,21 +9603,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9615,10 +9627,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>753790</v>
+        <v>753743</v>
       </c>
       <c r="R88" t="n">
-        <v>7217981</v>
+        <v>7218044</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9677,10 +9689,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125023412</v>
+        <v>125023380</v>
       </c>
       <c r="B89" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9689,25 +9701,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9717,10 +9729,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>753568</v>
+        <v>753769</v>
       </c>
       <c r="R89" t="n">
-        <v>7217875</v>
+        <v>7218019</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9779,10 +9791,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125023405</v>
+        <v>125023439</v>
       </c>
       <c r="B90" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9795,21 +9807,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9819,10 +9831,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>753748</v>
+        <v>753568</v>
       </c>
       <c r="R90" t="n">
-        <v>7218047</v>
+        <v>7217716</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9855,6 +9867,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9881,7 +9898,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125023326</v>
+        <v>125023316</v>
       </c>
       <c r="B91" t="n">
         <v>57513</v>
@@ -9919,7 +9936,7 @@
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -9929,10 +9946,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>753598</v>
+        <v>753568</v>
       </c>
       <c r="R91" t="n">
-        <v>7217744</v>
+        <v>7217733</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9969,7 +9986,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9996,10 +10013,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125023395</v>
+        <v>125023391</v>
       </c>
       <c r="B92" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10008,25 +10025,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10036,10 +10053,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>753472</v>
+        <v>753706</v>
       </c>
       <c r="R92" t="n">
-        <v>7218031</v>
+        <v>7218039</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10098,10 +10115,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125023354</v>
+        <v>125023315</v>
       </c>
       <c r="B93" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10114,21 +10131,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10138,10 +10155,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>753773</v>
+        <v>753491</v>
       </c>
       <c r="R93" t="n">
-        <v>7217842</v>
+        <v>7217766</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10174,6 +10191,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10200,10 +10222,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125023446</v>
+        <v>125023441</v>
       </c>
       <c r="B94" t="n">
-        <v>91221</v>
+        <v>57513</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10212,25 +10234,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1106</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10240,10 +10262,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>753567</v>
+        <v>753798</v>
       </c>
       <c r="R94" t="n">
-        <v>7217721</v>
+        <v>7217948</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10278,13 +10300,17 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10303,10 +10329,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125023316</v>
+        <v>125023372</v>
       </c>
       <c r="B95" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10319,42 +10345,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>753568</v>
+        <v>753790</v>
       </c>
       <c r="R95" t="n">
-        <v>7217733</v>
+        <v>7217992</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10387,11 +10405,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10418,10 +10431,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125023398</v>
+        <v>125023387</v>
       </c>
       <c r="B96" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10434,41 +10447,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>753778</v>
+        <v>753816</v>
       </c>
       <c r="R96" t="n">
-        <v>7217858</v>
+        <v>7217838</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10503,18 +10509,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10533,10 +10533,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125023383</v>
+        <v>125023317</v>
       </c>
       <c r="B97" t="n">
-        <v>91410</v>
+        <v>78842</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10549,16 +10549,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6040186</v>
+        <v>185</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10571,10 +10576,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>753603</v>
+        <v>753719</v>
       </c>
       <c r="R97" t="n">
-        <v>7217932</v>
+        <v>7217616</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10634,10 +10639,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125023317</v>
+        <v>125023383</v>
       </c>
       <c r="B98" t="n">
-        <v>78842</v>
+        <v>91410</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10650,21 +10655,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>185</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10677,10 +10677,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>753719</v>
+        <v>753603</v>
       </c>
       <c r="R98" t="n">
-        <v>7217616</v>
+        <v>7217932</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125023355</v>
+        <v>125023342</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753792</v>
+        <v>753722</v>
       </c>
       <c r="R4" t="n">
-        <v>7217850</v>
+        <v>7217596</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,6 +991,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1009,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125023374</v>
+        <v>125023337</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>79795</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,25 +1022,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753763</v>
+        <v>753523</v>
       </c>
       <c r="R5" t="n">
-        <v>7218015</v>
+        <v>7218086</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125023373</v>
+        <v>125023366</v>
       </c>
       <c r="B6" t="n">
         <v>79891</v>
@@ -1151,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753768</v>
+        <v>753778</v>
       </c>
       <c r="R6" t="n">
-        <v>7218016</v>
+        <v>7217945</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125023405</v>
+        <v>125023330</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,21 +1230,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>753748</v>
+        <v>753730</v>
       </c>
       <c r="R7" t="n">
-        <v>7218047</v>
+        <v>7217943</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125023419</v>
+        <v>125023432</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,20 +1328,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1355,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>753550</v>
+        <v>753769</v>
       </c>
       <c r="R8" t="n">
-        <v>7217725</v>
+        <v>7218019</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125023325</v>
+        <v>125023362</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,42 +1434,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>753575</v>
+        <v>753752</v>
       </c>
       <c r="R9" t="n">
-        <v>7217959</v>
+        <v>7217944</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,11 +1494,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125023444</v>
+        <v>125023404</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,21 +1536,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1572,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>753746</v>
+        <v>753743</v>
       </c>
       <c r="R10" t="n">
-        <v>7217930</v>
+        <v>7218044</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,11 +1596,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125023343</v>
+        <v>125023443</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,21 +1638,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>753760</v>
+        <v>753575</v>
       </c>
       <c r="R11" t="n">
-        <v>7218023</v>
+        <v>7217751</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,7 +1702,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1728,7 +1711,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1747,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023349</v>
+        <v>125023444</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1763,21 +1745,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1787,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>753795</v>
+        <v>753746</v>
       </c>
       <c r="R12" t="n">
-        <v>7217800</v>
+        <v>7217930</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,6 +1805,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125023389</v>
+        <v>125023324</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1861,25 +1848,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1889,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753729</v>
+        <v>753480</v>
       </c>
       <c r="R13" t="n">
-        <v>7218042</v>
+        <v>7218033</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125023321</v>
+        <v>125023378</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1967,21 +1954,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1991,10 +1978,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753679</v>
+        <v>753722</v>
       </c>
       <c r="R14" t="n">
-        <v>7218005</v>
+        <v>7218033</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2040,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125023358</v>
+        <v>125023375</v>
       </c>
       <c r="B15" t="n">
         <v>79891</v>
@@ -2093,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>753758</v>
+        <v>753750</v>
       </c>
       <c r="R15" t="n">
-        <v>7217900</v>
+        <v>7218028</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2155,7 +2142,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125023350</v>
+        <v>125023359</v>
       </c>
       <c r="B16" t="n">
         <v>79891</v>
@@ -2195,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753789</v>
+        <v>753753</v>
       </c>
       <c r="R16" t="n">
-        <v>7217812</v>
+        <v>7217910</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2257,10 +2244,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125023426</v>
+        <v>125023387</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2273,21 +2260,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2297,10 +2284,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753597</v>
+        <v>753816</v>
       </c>
       <c r="R17" t="n">
-        <v>7217728</v>
+        <v>7217838</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,10 +2346,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125023434</v>
+        <v>125023430</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>79926</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2371,46 +2358,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753797</v>
+        <v>753789</v>
       </c>
       <c r="R18" t="n">
-        <v>7217988</v>
+        <v>7217809</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,11 +2422,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,10 +2448,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125023354</v>
+        <v>125023419</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2490,21 +2464,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2514,10 +2488,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753773</v>
+        <v>753550</v>
       </c>
       <c r="R19" t="n">
-        <v>7217842</v>
+        <v>7217725</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2576,7 +2550,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125023409</v>
+        <v>125023411</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2616,10 +2590,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753562</v>
+        <v>753557</v>
       </c>
       <c r="R20" t="n">
-        <v>7217917</v>
+        <v>7217895</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,10 +2652,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125023351</v>
+        <v>125023326</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2694,34 +2668,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753758</v>
+        <v>753598</v>
       </c>
       <c r="R21" t="n">
-        <v>7217819</v>
+        <v>7217744</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,6 +2736,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2780,10 +2767,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125023381</v>
+        <v>125023350</v>
       </c>
       <c r="B22" t="n">
-        <v>79927</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2792,25 +2779,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2807,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753722</v>
+        <v>753789</v>
       </c>
       <c r="R22" t="n">
-        <v>7218033</v>
+        <v>7217812</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2882,10 +2869,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125023341</v>
+        <v>125023414</v>
       </c>
       <c r="B23" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2894,25 +2881,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2922,10 +2909,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753654</v>
+        <v>753630</v>
       </c>
       <c r="R23" t="n">
-        <v>7218008</v>
+        <v>7218006</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,10 +2971,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125023378</v>
+        <v>125023426</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3000,21 +2987,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3024,10 +3011,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753722</v>
+        <v>753597</v>
       </c>
       <c r="R24" t="n">
-        <v>7218033</v>
+        <v>7217728</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3086,10 +3073,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125023413</v>
+        <v>125023316</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3102,34 +3089,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753517</v>
+        <v>753568</v>
       </c>
       <c r="R25" t="n">
-        <v>7217918</v>
+        <v>7217733</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3162,6 +3157,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3188,10 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125023319</v>
+        <v>125023358</v>
       </c>
       <c r="B26" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3200,25 +3200,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753506</v>
+        <v>753758</v>
       </c>
       <c r="R26" t="n">
-        <v>7217904</v>
+        <v>7217900</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125023442</v>
+        <v>125023334</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3302,25 +3302,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753726</v>
+        <v>753752</v>
       </c>
       <c r="R27" t="n">
-        <v>7218039</v>
+        <v>7217919</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3366,11 +3366,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3397,10 +3392,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125023435</v>
+        <v>125023399</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3413,42 +3408,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753562</v>
+        <v>753751</v>
       </c>
       <c r="R28" t="n">
-        <v>7217727</v>
+        <v>7217806</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3481,11 +3468,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3512,10 +3494,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125023420</v>
+        <v>125023336</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>90962</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3528,21 +3510,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3552,10 +3534,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753559</v>
+        <v>753566</v>
       </c>
       <c r="R29" t="n">
-        <v>7217734</v>
+        <v>7217862</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125023394</v>
+        <v>125023319</v>
       </c>
       <c r="B30" t="n">
-        <v>91030</v>
+        <v>90977</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3626,25 +3608,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3654,10 +3636,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753596</v>
+        <v>753506</v>
       </c>
       <c r="R30" t="n">
-        <v>7217939</v>
+        <v>7217904</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3716,7 +3698,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125023423</v>
+        <v>125023398</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3750,16 +3732,23 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753610</v>
+        <v>753778</v>
       </c>
       <c r="R31" t="n">
-        <v>7217727</v>
+        <v>7217858</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3794,12 +3783,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3818,10 +3813,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125023432</v>
+        <v>125023423</v>
       </c>
       <c r="B32" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3830,20 +3825,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3858,10 +3853,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753769</v>
+        <v>753610</v>
       </c>
       <c r="R32" t="n">
-        <v>7218019</v>
+        <v>7217727</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3920,10 +3915,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125023337</v>
+        <v>125023412</v>
       </c>
       <c r="B33" t="n">
-        <v>79795</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3932,25 +3927,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3960,10 +3955,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753523</v>
+        <v>753568</v>
       </c>
       <c r="R33" t="n">
-        <v>7218086</v>
+        <v>7217875</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4022,10 +4017,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125023352</v>
+        <v>125023327</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4038,21 +4033,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4062,10 +4057,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753763</v>
+        <v>753740</v>
       </c>
       <c r="R34" t="n">
-        <v>7217831</v>
+        <v>7217891</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4124,10 +4119,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125023402</v>
+        <v>125023355</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4140,21 +4135,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4164,10 +4159,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753752</v>
+        <v>753792</v>
       </c>
       <c r="R35" t="n">
-        <v>7217878</v>
+        <v>7217850</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4226,7 +4221,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125023375</v>
+        <v>125023373</v>
       </c>
       <c r="B36" t="n">
         <v>79891</v>
@@ -4266,10 +4261,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753750</v>
+        <v>753768</v>
       </c>
       <c r="R36" t="n">
-        <v>7218028</v>
+        <v>7218016</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4328,7 +4323,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125023365</v>
+        <v>125023369</v>
       </c>
       <c r="B37" t="n">
         <v>79891</v>
@@ -4368,10 +4363,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753784</v>
+        <v>753797</v>
       </c>
       <c r="R37" t="n">
-        <v>7217948</v>
+        <v>7218005</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4430,10 +4425,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125023430</v>
+        <v>125023434</v>
       </c>
       <c r="B38" t="n">
-        <v>79926</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4442,38 +4437,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753789</v>
+        <v>753797</v>
       </c>
       <c r="R38" t="n">
-        <v>7217809</v>
+        <v>7217988</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4506,6 +4509,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4532,10 +4540,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125023368</v>
+        <v>125023315</v>
       </c>
       <c r="B39" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4548,21 +4556,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4572,10 +4580,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753808</v>
+        <v>753491</v>
       </c>
       <c r="R39" t="n">
-        <v>7217964</v>
+        <v>7217766</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4608,6 +4616,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4634,7 +4647,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125023326</v>
+        <v>125023439</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -4668,24 +4681,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753598</v>
+        <v>753568</v>
       </c>
       <c r="R40" t="n">
-        <v>7217744</v>
+        <v>7217716</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4722,7 +4727,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4749,7 +4754,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125023333</v>
+        <v>125023328</v>
       </c>
       <c r="B41" t="n">
         <v>57666</v>
@@ -4789,10 +4794,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753781</v>
+        <v>753742</v>
       </c>
       <c r="R41" t="n">
-        <v>7217902</v>
+        <v>7217926</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4851,10 +4856,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125023320</v>
+        <v>125023380</v>
       </c>
       <c r="B42" t="n">
-        <v>91012</v>
+        <v>79927</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4863,25 +4868,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4891,10 +4896,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753687</v>
+        <v>753769</v>
       </c>
       <c r="R42" t="n">
-        <v>7217999</v>
+        <v>7218019</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4953,10 +4958,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125023335</v>
+        <v>125023407</v>
       </c>
       <c r="B43" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4965,25 +4970,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4993,10 +4998,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753790</v>
+        <v>753671</v>
       </c>
       <c r="R43" t="n">
-        <v>7217992</v>
+        <v>7218008</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5055,10 +5060,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125023431</v>
+        <v>125023413</v>
       </c>
       <c r="B44" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5067,20 +5072,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5095,10 +5100,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753774</v>
+        <v>753517</v>
       </c>
       <c r="R44" t="n">
-        <v>7217939</v>
+        <v>7217918</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5157,10 +5162,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125023334</v>
+        <v>125023401</v>
       </c>
       <c r="B45" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5169,25 +5174,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5197,10 +5202,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753752</v>
+        <v>753780</v>
       </c>
       <c r="R45" t="n">
-        <v>7217919</v>
+        <v>7217865</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5259,10 +5264,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125023366</v>
+        <v>125023389</v>
       </c>
       <c r="B46" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5271,25 +5276,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5299,10 +5304,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753778</v>
+        <v>753729</v>
       </c>
       <c r="R46" t="n">
-        <v>7217945</v>
+        <v>7218042</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5361,10 +5366,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125023445</v>
+        <v>125023446</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>91221</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5373,25 +5378,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1106</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5401,10 +5406,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753715</v>
+        <v>753567</v>
       </c>
       <c r="R47" t="n">
-        <v>7218026</v>
+        <v>7217721</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5439,17 +5444,13 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5468,10 +5469,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125023407</v>
+        <v>125023363</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5484,21 +5485,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5508,10 +5509,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753671</v>
+        <v>753782</v>
       </c>
       <c r="R48" t="n">
-        <v>7218008</v>
+        <v>7217946</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5570,10 +5571,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125023336</v>
+        <v>125023372</v>
       </c>
       <c r="B49" t="n">
-        <v>90962</v>
+        <v>79891</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5586,21 +5587,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5610,10 +5611,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753566</v>
+        <v>753790</v>
       </c>
       <c r="R49" t="n">
-        <v>7217862</v>
+        <v>7217992</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5672,10 +5673,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125023318</v>
+        <v>125023368</v>
       </c>
       <c r="B50" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5684,25 +5685,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5712,10 +5713,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753680</v>
+        <v>753808</v>
       </c>
       <c r="R50" t="n">
-        <v>7218004</v>
+        <v>7217964</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5774,10 +5775,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125023411</v>
+        <v>125023325</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5790,34 +5791,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753557</v>
+        <v>753575</v>
       </c>
       <c r="R51" t="n">
-        <v>7217895</v>
+        <v>7217959</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5850,6 +5859,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5876,10 +5890,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125023345</v>
+        <v>125023445</v>
       </c>
       <c r="B52" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5892,21 +5906,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5916,10 +5930,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>753790</v>
+        <v>753715</v>
       </c>
       <c r="R52" t="n">
-        <v>7217981</v>
+        <v>7218026</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5952,6 +5966,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5978,10 +5997,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125023328</v>
+        <v>125023442</v>
       </c>
       <c r="B53" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5994,21 +6013,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6018,10 +6037,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>753742</v>
+        <v>753726</v>
       </c>
       <c r="R53" t="n">
-        <v>7217926</v>
+        <v>7218039</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6054,6 +6073,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6080,10 +6104,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125023392</v>
+        <v>125023335</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6092,25 +6116,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6120,10 +6144,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753718</v>
+        <v>753790</v>
       </c>
       <c r="R54" t="n">
-        <v>7218035</v>
+        <v>7217992</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6182,10 +6206,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125023443</v>
+        <v>125023357</v>
       </c>
       <c r="B55" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6198,21 +6222,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6222,10 +6246,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753575</v>
+        <v>753793</v>
       </c>
       <c r="R55" t="n">
-        <v>7217751</v>
+        <v>7217856</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6258,11 +6282,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6289,10 +6308,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125023429</v>
+        <v>125023406</v>
       </c>
       <c r="B56" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6301,20 +6320,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6329,10 +6348,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753792</v>
+        <v>753718</v>
       </c>
       <c r="R56" t="n">
-        <v>7217798</v>
+        <v>7218042</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6391,10 +6410,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125023357</v>
+        <v>125023435</v>
       </c>
       <c r="B57" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6407,34 +6426,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753793</v>
+        <v>753562</v>
       </c>
       <c r="R57" t="n">
-        <v>7217856</v>
+        <v>7217727</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6467,6 +6494,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6493,10 +6525,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125023347</v>
+        <v>125023338</v>
       </c>
       <c r="B58" t="n">
-        <v>79891</v>
+        <v>8720</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6505,25 +6537,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100798</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smal trollknäppare</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Danosoma conspersum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyllenhal, 1808)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6533,10 +6565,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753850</v>
+        <v>753699</v>
       </c>
       <c r="R58" t="n">
-        <v>7217843</v>
+        <v>7217618</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6577,6 +6609,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6595,10 +6628,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125023342</v>
+        <v>125023320</v>
       </c>
       <c r="B59" t="n">
-        <v>78547</v>
+        <v>91012</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6611,21 +6644,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6635,10 +6668,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753722</v>
+        <v>753687</v>
       </c>
       <c r="R59" t="n">
-        <v>7217596</v>
+        <v>7217999</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6679,7 +6712,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6698,10 +6730,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125023418</v>
+        <v>125023394</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6714,21 +6746,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6738,10 +6770,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753406</v>
+        <v>753596</v>
       </c>
       <c r="R60" t="n">
-        <v>7217999</v>
+        <v>7217939</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6800,10 +6832,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125023421</v>
+        <v>125023348</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6816,21 +6848,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6840,10 +6872,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753573</v>
+        <v>753817</v>
       </c>
       <c r="R61" t="n">
-        <v>7217745</v>
+        <v>7217853</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6902,10 +6934,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125023406</v>
+        <v>125023429</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6914,20 +6946,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6942,10 +6974,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753718</v>
+        <v>753792</v>
       </c>
       <c r="R62" t="n">
-        <v>7218042</v>
+        <v>7217798</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7004,10 +7036,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125023323</v>
+        <v>125023367</v>
       </c>
       <c r="B63" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7020,21 +7052,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7044,10 +7076,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753504</v>
+        <v>753786</v>
       </c>
       <c r="R63" t="n">
-        <v>7217889</v>
+        <v>7217962</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7106,10 +7138,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125023338</v>
+        <v>125023354</v>
       </c>
       <c r="B64" t="n">
-        <v>8720</v>
+        <v>79891</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7118,25 +7150,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100798</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Smal trollknäppare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Danosoma conspersum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7146,10 +7178,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753699</v>
+        <v>753773</v>
       </c>
       <c r="R64" t="n">
-        <v>7217618</v>
+        <v>7217842</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7190,7 +7222,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7209,10 +7240,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125023399</v>
+        <v>125023352</v>
       </c>
       <c r="B65" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7225,21 +7256,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7249,10 +7280,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753751</v>
+        <v>753763</v>
       </c>
       <c r="R65" t="n">
-        <v>7217806</v>
+        <v>7217831</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7413,10 +7444,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125023359</v>
+        <v>125023396</v>
       </c>
       <c r="B67" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7429,34 +7460,41 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753753</v>
+        <v>753626</v>
       </c>
       <c r="R67" t="n">
-        <v>7217910</v>
+        <v>7218004</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7491,12 +7529,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7515,10 +7559,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125023367</v>
+        <v>125023402</v>
       </c>
       <c r="B68" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7531,21 +7575,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7555,10 +7599,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753786</v>
+        <v>753752</v>
       </c>
       <c r="R68" t="n">
-        <v>7217962</v>
+        <v>7217878</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7617,10 +7661,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125023446</v>
+        <v>125023405</v>
       </c>
       <c r="B69" t="n">
-        <v>91221</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7629,25 +7673,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1106</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7657,10 +7701,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753567</v>
+        <v>753748</v>
       </c>
       <c r="R69" t="n">
-        <v>7217721</v>
+        <v>7218047</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7701,7 +7745,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7720,10 +7763,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125023363</v>
+        <v>125023418</v>
       </c>
       <c r="B70" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7736,21 +7779,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7760,10 +7803,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753782</v>
+        <v>753406</v>
       </c>
       <c r="R70" t="n">
-        <v>7217946</v>
+        <v>7217999</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7822,10 +7865,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125023369</v>
+        <v>125023421</v>
       </c>
       <c r="B71" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7838,21 +7881,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7862,10 +7905,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753797</v>
+        <v>753573</v>
       </c>
       <c r="R71" t="n">
-        <v>7218005</v>
+        <v>7217745</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7924,10 +7967,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125023395</v>
+        <v>125023403</v>
       </c>
       <c r="B72" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7940,21 +7983,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7964,10 +8007,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753472</v>
+        <v>753762</v>
       </c>
       <c r="R72" t="n">
-        <v>7218031</v>
+        <v>7218015</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8026,10 +8069,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125023403</v>
+        <v>125023343</v>
       </c>
       <c r="B73" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8042,21 +8085,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8066,10 +8109,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>753762</v>
+        <v>753760</v>
       </c>
       <c r="R73" t="n">
-        <v>7218015</v>
+        <v>7218023</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8104,12 +8147,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8128,10 +8177,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125023388</v>
+        <v>125023417</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8140,25 +8189,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8168,10 +8217,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>753742</v>
+        <v>753474</v>
       </c>
       <c r="R74" t="n">
-        <v>7217924</v>
+        <v>7218026</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8230,10 +8279,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125023401</v>
+        <v>125023323</v>
       </c>
       <c r="B75" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8246,21 +8295,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8270,10 +8319,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>753780</v>
+        <v>753504</v>
       </c>
       <c r="R75" t="n">
-        <v>7217865</v>
+        <v>7217889</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8332,10 +8381,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125023398</v>
+        <v>125023318</v>
       </c>
       <c r="B76" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8344,45 +8393,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>753778</v>
+        <v>753680</v>
       </c>
       <c r="R76" t="n">
-        <v>7217858</v>
+        <v>7218004</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8417,18 +8459,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8447,10 +8483,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125023396</v>
+        <v>125023441</v>
       </c>
       <c r="B77" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8463,41 +8499,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>753626</v>
+        <v>753798</v>
       </c>
       <c r="R77" t="n">
-        <v>7218004</v>
+        <v>7217948</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8534,7 +8563,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8543,7 +8572,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8562,10 +8590,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125023348</v>
+        <v>125023391</v>
       </c>
       <c r="B78" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8574,25 +8602,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8602,10 +8630,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>753817</v>
+        <v>753706</v>
       </c>
       <c r="R78" t="n">
-        <v>7217853</v>
+        <v>7218039</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8664,10 +8692,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125023324</v>
+        <v>125023388</v>
       </c>
       <c r="B79" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8676,25 +8704,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8704,10 +8732,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>753480</v>
+        <v>753742</v>
       </c>
       <c r="R79" t="n">
-        <v>7218033</v>
+        <v>7217924</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8766,10 +8794,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125023412</v>
+        <v>125023392</v>
       </c>
       <c r="B80" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8778,25 +8806,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8806,10 +8834,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>753568</v>
+        <v>753718</v>
       </c>
       <c r="R80" t="n">
-        <v>7217875</v>
+        <v>7218035</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8868,10 +8896,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125023417</v>
+        <v>125023351</v>
       </c>
       <c r="B81" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8884,21 +8912,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8908,10 +8936,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>753474</v>
+        <v>753758</v>
       </c>
       <c r="R81" t="n">
-        <v>7218026</v>
+        <v>7217819</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8970,7 +8998,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125023360</v>
+        <v>125023345</v>
       </c>
       <c r="B82" t="n">
         <v>79891</v>
@@ -9010,10 +9038,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>753752</v>
+        <v>753790</v>
       </c>
       <c r="R82" t="n">
-        <v>7217944</v>
+        <v>7217981</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9072,10 +9100,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125023438</v>
+        <v>125023409</v>
       </c>
       <c r="B83" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9088,21 +9116,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9112,10 +9140,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>753612</v>
+        <v>753562</v>
       </c>
       <c r="R83" t="n">
-        <v>7217703</v>
+        <v>7217917</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9148,11 +9176,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9179,7 +9202,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125023330</v>
+        <v>125023333</v>
       </c>
       <c r="B84" t="n">
         <v>57666</v>
@@ -9219,10 +9242,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>753730</v>
+        <v>753781</v>
       </c>
       <c r="R84" t="n">
-        <v>7217943</v>
+        <v>7217902</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9281,10 +9304,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125023327</v>
+        <v>125023365</v>
       </c>
       <c r="B85" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9297,21 +9320,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9321,10 +9344,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>753740</v>
+        <v>753784</v>
       </c>
       <c r="R85" t="n">
-        <v>7217891</v>
+        <v>7217948</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9383,10 +9406,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125023416</v>
+        <v>125023321</v>
       </c>
       <c r="B86" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9399,21 +9422,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9423,10 +9446,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>753470</v>
+        <v>753679</v>
       </c>
       <c r="R86" t="n">
-        <v>7218024</v>
+        <v>7218005</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9485,10 +9508,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125023414</v>
+        <v>125023431</v>
       </c>
       <c r="B87" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9497,20 +9520,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9525,10 +9548,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>753630</v>
+        <v>753774</v>
       </c>
       <c r="R87" t="n">
-        <v>7218006</v>
+        <v>7217939</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9587,10 +9610,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125023404</v>
+        <v>125023349</v>
       </c>
       <c r="B88" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9603,21 +9626,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9627,10 +9650,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>753743</v>
+        <v>753795</v>
       </c>
       <c r="R88" t="n">
-        <v>7218044</v>
+        <v>7217800</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9689,10 +9712,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125023380</v>
+        <v>125023438</v>
       </c>
       <c r="B89" t="n">
-        <v>79927</v>
+        <v>57513</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9701,25 +9724,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9729,10 +9752,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>753769</v>
+        <v>753612</v>
       </c>
       <c r="R89" t="n">
-        <v>7218019</v>
+        <v>7217703</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9765,6 +9788,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9791,10 +9819,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125023439</v>
+        <v>125023395</v>
       </c>
       <c r="B90" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9807,21 +9835,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9831,10 +9859,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>753568</v>
+        <v>753472</v>
       </c>
       <c r="R90" t="n">
-        <v>7217716</v>
+        <v>7218031</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9867,11 +9895,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9898,10 +9921,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125023316</v>
+        <v>125023347</v>
       </c>
       <c r="B91" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9914,42 +9937,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>753568</v>
+        <v>753850</v>
       </c>
       <c r="R91" t="n">
-        <v>7217733</v>
+        <v>7217843</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9982,11 +9997,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10013,10 +10023,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125023391</v>
+        <v>125023420</v>
       </c>
       <c r="B92" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10025,25 +10035,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10053,10 +10063,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>753706</v>
+        <v>753559</v>
       </c>
       <c r="R92" t="n">
-        <v>7218039</v>
+        <v>7217734</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10115,10 +10125,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125023315</v>
+        <v>125023381</v>
       </c>
       <c r="B93" t="n">
-        <v>57513</v>
+        <v>79927</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10127,25 +10137,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10155,10 +10165,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>753491</v>
+        <v>753722</v>
       </c>
       <c r="R93" t="n">
-        <v>7217766</v>
+        <v>7218033</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10191,11 +10201,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10222,10 +10227,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125023441</v>
+        <v>125023341</v>
       </c>
       <c r="B94" t="n">
-        <v>57513</v>
+        <v>79919</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10234,25 +10239,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10262,10 +10267,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>753798</v>
+        <v>753654</v>
       </c>
       <c r="R94" t="n">
-        <v>7217948</v>
+        <v>7218008</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10298,11 +10303,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10329,7 +10329,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125023372</v>
+        <v>125023374</v>
       </c>
       <c r="B95" t="n">
         <v>79891</v>
@@ -10369,10 +10369,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>753790</v>
+        <v>753763</v>
       </c>
       <c r="R95" t="n">
-        <v>7217992</v>
+        <v>7218015</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10431,10 +10431,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125023387</v>
+        <v>125023416</v>
       </c>
       <c r="B96" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10447,21 +10447,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10471,10 +10471,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>753816</v>
+        <v>753470</v>
       </c>
       <c r="R96" t="n">
-        <v>7217838</v>
+        <v>7218024</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10533,10 +10533,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125023317</v>
+        <v>125023383</v>
       </c>
       <c r="B97" t="n">
-        <v>78842</v>
+        <v>91410</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10549,21 +10549,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10576,10 +10571,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>753719</v>
+        <v>753603</v>
       </c>
       <c r="R97" t="n">
-        <v>7217616</v>
+        <v>7217932</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10639,10 +10634,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125023383</v>
+        <v>125023317</v>
       </c>
       <c r="B98" t="n">
-        <v>91410</v>
+        <v>78842</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10655,16 +10650,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6040186</v>
+        <v>185</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10677,10 +10677,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>753603</v>
+        <v>753719</v>
       </c>
       <c r="R98" t="n">
-        <v>7217932</v>
+        <v>7217616</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -5775,7 +5775,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125023325</v>
+        <v>125023442</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -5809,24 +5809,16 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753575</v>
+        <v>753726</v>
       </c>
       <c r="R51" t="n">
-        <v>7217959</v>
+        <v>7218039</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5863,7 +5855,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5890,7 +5882,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125023445</v>
+        <v>125023325</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -5924,16 +5916,24 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>753715</v>
+        <v>753575</v>
       </c>
       <c r="R52" t="n">
-        <v>7218026</v>
+        <v>7217959</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Avskalad gran</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5997,7 +5997,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125023442</v>
+        <v>125023445</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>753726</v>
+        <v>753715</v>
       </c>
       <c r="R53" t="n">
-        <v>7218039</v>
+        <v>7218026</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Barksprätt</t>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6104,10 +6104,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125023335</v>
+        <v>125023406</v>
       </c>
       <c r="B54" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6116,25 +6116,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753790</v>
+        <v>753718</v>
       </c>
       <c r="R54" t="n">
-        <v>7217992</v>
+        <v>7218042</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6206,10 +6206,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125023357</v>
+        <v>125023435</v>
       </c>
       <c r="B55" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6222,34 +6222,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753793</v>
+        <v>753562</v>
       </c>
       <c r="R55" t="n">
-        <v>7217856</v>
+        <v>7217727</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6282,6 +6290,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6308,10 +6321,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125023406</v>
+        <v>125023335</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6320,25 +6333,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6348,10 +6361,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753718</v>
+        <v>753790</v>
       </c>
       <c r="R56" t="n">
-        <v>7218042</v>
+        <v>7217992</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6410,10 +6423,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125023435</v>
+        <v>125023357</v>
       </c>
       <c r="B57" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6426,42 +6439,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753562</v>
+        <v>753793</v>
       </c>
       <c r="R57" t="n">
-        <v>7217727</v>
+        <v>7217856</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6494,11 +6499,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6525,10 +6525,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125023338</v>
+        <v>125023320</v>
       </c>
       <c r="B58" t="n">
-        <v>8720</v>
+        <v>91012</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6537,25 +6537,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100798</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Smal trollknäppare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Danosoma conspersum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753699</v>
+        <v>753687</v>
       </c>
       <c r="R58" t="n">
-        <v>7217618</v>
+        <v>7217999</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6609,7 +6609,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6628,10 +6627,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125023320</v>
+        <v>125023394</v>
       </c>
       <c r="B59" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6644,21 +6643,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6668,10 +6667,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753687</v>
+        <v>753596</v>
       </c>
       <c r="R59" t="n">
-        <v>7217999</v>
+        <v>7217939</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6730,10 +6729,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125023394</v>
+        <v>125023348</v>
       </c>
       <c r="B60" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6746,21 +6745,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6770,10 +6769,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753596</v>
+        <v>753817</v>
       </c>
       <c r="R60" t="n">
-        <v>7217939</v>
+        <v>7217853</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6832,10 +6831,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125023348</v>
+        <v>125023429</v>
       </c>
       <c r="B61" t="n">
-        <v>79891</v>
+        <v>79926</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6844,25 +6843,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6872,10 +6871,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753817</v>
+        <v>753792</v>
       </c>
       <c r="R61" t="n">
-        <v>7217853</v>
+        <v>7217798</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6934,10 +6933,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125023429</v>
+        <v>125023367</v>
       </c>
       <c r="B62" t="n">
-        <v>79926</v>
+        <v>79891</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6946,25 +6945,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6974,10 +6973,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753792</v>
+        <v>753786</v>
       </c>
       <c r="R62" t="n">
-        <v>7217798</v>
+        <v>7217962</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7036,7 +7035,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125023367</v>
+        <v>125023354</v>
       </c>
       <c r="B63" t="n">
         <v>79891</v>
@@ -7076,10 +7075,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753786</v>
+        <v>753773</v>
       </c>
       <c r="R63" t="n">
-        <v>7217962</v>
+        <v>7217842</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7138,7 +7137,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125023354</v>
+        <v>125023352</v>
       </c>
       <c r="B64" t="n">
         <v>79891</v>
@@ -7178,10 +7177,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753773</v>
+        <v>753763</v>
       </c>
       <c r="R64" t="n">
-        <v>7217842</v>
+        <v>7217831</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7240,10 +7239,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125023352</v>
+        <v>125023338</v>
       </c>
       <c r="B65" t="n">
-        <v>79891</v>
+        <v>8720</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7252,25 +7251,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>100798</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smal trollknäppare</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Danosoma conspersum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyllenhal, 1808)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7280,10 +7279,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753763</v>
+        <v>753699</v>
       </c>
       <c r="R65" t="n">
-        <v>7217831</v>
+        <v>7217618</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7324,6 +7323,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -9712,10 +9712,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125023438</v>
+        <v>125023347</v>
       </c>
       <c r="B89" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9728,21 +9728,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>753612</v>
+        <v>753850</v>
       </c>
       <c r="R89" t="n">
-        <v>7217703</v>
+        <v>7217843</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9788,11 +9788,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9819,10 +9814,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125023395</v>
+        <v>125023438</v>
       </c>
       <c r="B90" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9835,21 +9830,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9859,10 +9854,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>753472</v>
+        <v>753612</v>
       </c>
       <c r="R90" t="n">
-        <v>7218031</v>
+        <v>7217703</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9895,6 +9890,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9921,10 +9921,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125023347</v>
+        <v>125023395</v>
       </c>
       <c r="B91" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9937,21 +9937,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9961,10 +9961,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>753850</v>
+        <v>753472</v>
       </c>
       <c r="R91" t="n">
-        <v>7217843</v>
+        <v>7218031</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125023342</v>
+        <v>125023429</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>79926</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753722</v>
+        <v>753792</v>
       </c>
       <c r="R4" t="n">
-        <v>7217596</v>
+        <v>7217798</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125023337</v>
+        <v>125023419</v>
       </c>
       <c r="B5" t="n">
-        <v>79795</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1021,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753523</v>
+        <v>753550</v>
       </c>
       <c r="R5" t="n">
-        <v>7218086</v>
+        <v>7217725</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125023366</v>
+        <v>125023416</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,21 +1127,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1152,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753778</v>
+        <v>753470</v>
       </c>
       <c r="R6" t="n">
-        <v>7217945</v>
+        <v>7218024</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125023330</v>
+        <v>125023413</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1254,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>753730</v>
+        <v>753517</v>
       </c>
       <c r="R7" t="n">
-        <v>7217943</v>
+        <v>7217918</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125023432</v>
+        <v>125023404</v>
       </c>
       <c r="B8" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,20 +1327,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1356,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>753769</v>
+        <v>753743</v>
       </c>
       <c r="R8" t="n">
-        <v>7218019</v>
+        <v>7218044</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125023362</v>
+        <v>125023401</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>753752</v>
+        <v>753780</v>
       </c>
       <c r="R9" t="n">
-        <v>7217944</v>
+        <v>7217865</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125023404</v>
+        <v>125023387</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,21 +1535,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1560,10 +1559,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>753743</v>
+        <v>753816</v>
       </c>
       <c r="R10" t="n">
-        <v>7218044</v>
+        <v>7217838</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125023443</v>
+        <v>125023351</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,21 +1637,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1662,10 +1661,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>753575</v>
+        <v>753758</v>
       </c>
       <c r="R11" t="n">
-        <v>7217751</v>
+        <v>7217819</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,11 +1697,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1729,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023444</v>
+        <v>125023348</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1745,21 +1739,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1769,10 +1763,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>753746</v>
+        <v>753817</v>
       </c>
       <c r="R12" t="n">
-        <v>7217930</v>
+        <v>7217853</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,11 +1799,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1836,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125023324</v>
+        <v>125023337</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>79795</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,25 +1837,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1876,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753480</v>
+        <v>753523</v>
       </c>
       <c r="R13" t="n">
-        <v>7218033</v>
+        <v>7218086</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125023378</v>
+        <v>125023318</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,25 +1939,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1978,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753722</v>
+        <v>753680</v>
       </c>
       <c r="R14" t="n">
-        <v>7218033</v>
+        <v>7218004</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,10 +2029,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125023375</v>
+        <v>125023439</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2056,21 +2045,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2080,10 +2069,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>753750</v>
+        <v>753568</v>
       </c>
       <c r="R15" t="n">
-        <v>7218028</v>
+        <v>7217716</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2116,6 +2105,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2142,7 +2136,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125023359</v>
+        <v>125023369</v>
       </c>
       <c r="B16" t="n">
         <v>79891</v>
@@ -2182,10 +2176,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753753</v>
+        <v>753797</v>
       </c>
       <c r="R16" t="n">
-        <v>7217910</v>
+        <v>7218005</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,10 +2238,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125023387</v>
+        <v>125023434</v>
       </c>
       <c r="B17" t="n">
-        <v>78546</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2260,34 +2254,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753816</v>
+        <v>753797</v>
       </c>
       <c r="R17" t="n">
-        <v>7217838</v>
+        <v>7217988</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,6 +2322,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2346,10 +2353,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125023430</v>
+        <v>125023324</v>
       </c>
       <c r="B18" t="n">
-        <v>79926</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2358,25 +2365,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2386,10 +2393,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753789</v>
+        <v>753480</v>
       </c>
       <c r="R18" t="n">
-        <v>7217809</v>
+        <v>7218033</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2448,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125023419</v>
+        <v>125023360</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2464,21 +2471,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2488,10 +2495,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753550</v>
+        <v>753752</v>
       </c>
       <c r="R19" t="n">
-        <v>7217725</v>
+        <v>7217944</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,10 +2557,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125023411</v>
+        <v>125023367</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2566,21 +2573,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2590,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753557</v>
+        <v>753786</v>
       </c>
       <c r="R20" t="n">
-        <v>7217895</v>
+        <v>7217962</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2652,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125023326</v>
+        <v>125023392</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2664,46 +2671,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753598</v>
+        <v>753718</v>
       </c>
       <c r="R21" t="n">
-        <v>7217744</v>
+        <v>7218035</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2736,11 +2735,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2767,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125023350</v>
+        <v>125023342</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2783,21 +2777,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2807,10 +2801,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753789</v>
+        <v>753722</v>
       </c>
       <c r="R22" t="n">
-        <v>7217812</v>
+        <v>7217596</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2851,6 +2845,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2869,7 +2864,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125023414</v>
+        <v>125023420</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2909,10 +2904,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753630</v>
+        <v>753559</v>
       </c>
       <c r="R23" t="n">
-        <v>7218006</v>
+        <v>7217734</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2971,10 +2966,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125023426</v>
+        <v>125023359</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2987,21 +2982,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3011,10 +3006,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753597</v>
+        <v>753753</v>
       </c>
       <c r="R24" t="n">
-        <v>7217728</v>
+        <v>7217910</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3073,10 +3068,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125023316</v>
+        <v>125023358</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3089,42 +3084,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753568</v>
+        <v>753758</v>
       </c>
       <c r="R25" t="n">
-        <v>7217733</v>
+        <v>7217900</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3157,11 +3144,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3188,7 +3170,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125023358</v>
+        <v>125023378</v>
       </c>
       <c r="B26" t="n">
         <v>79891</v>
@@ -3228,10 +3210,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753758</v>
+        <v>753722</v>
       </c>
       <c r="R26" t="n">
-        <v>7217900</v>
+        <v>7218033</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3290,10 +3272,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125023334</v>
+        <v>125023357</v>
       </c>
       <c r="B27" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3302,25 +3284,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3330,10 +3312,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753752</v>
+        <v>753793</v>
       </c>
       <c r="R27" t="n">
-        <v>7217919</v>
+        <v>7217856</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3392,10 +3374,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125023399</v>
+        <v>125023352</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3408,21 +3390,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3432,10 +3414,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753751</v>
+        <v>753763</v>
       </c>
       <c r="R28" t="n">
-        <v>7217806</v>
+        <v>7217831</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3596,10 +3578,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125023319</v>
+        <v>125023333</v>
       </c>
       <c r="B30" t="n">
-        <v>90977</v>
+        <v>57666</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3608,25 +3590,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3636,10 +3618,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753506</v>
+        <v>753781</v>
       </c>
       <c r="R30" t="n">
-        <v>7217904</v>
+        <v>7217902</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3698,10 +3680,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125023398</v>
+        <v>125023389</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3710,45 +3692,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753778</v>
+        <v>753729</v>
       </c>
       <c r="R31" t="n">
-        <v>7217858</v>
+        <v>7218042</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3783,18 +3758,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3813,10 +3782,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125023423</v>
+        <v>125023341</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3825,25 +3794,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3853,10 +3822,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753610</v>
+        <v>753654</v>
       </c>
       <c r="R32" t="n">
-        <v>7217727</v>
+        <v>7218008</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3915,10 +3884,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125023412</v>
+        <v>125023374</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3931,21 +3900,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3955,10 +3924,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753568</v>
+        <v>753763</v>
       </c>
       <c r="R33" t="n">
-        <v>7217875</v>
+        <v>7218015</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4017,10 +3986,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125023327</v>
+        <v>125023347</v>
       </c>
       <c r="B34" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4033,21 +4002,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4057,10 +4026,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753740</v>
+        <v>753850</v>
       </c>
       <c r="R34" t="n">
-        <v>7217891</v>
+        <v>7217843</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4119,7 +4088,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125023355</v>
+        <v>125023363</v>
       </c>
       <c r="B35" t="n">
         <v>79891</v>
@@ -4159,10 +4128,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753792</v>
+        <v>753782</v>
       </c>
       <c r="R35" t="n">
-        <v>7217850</v>
+        <v>7217946</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4221,10 +4190,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125023373</v>
+        <v>125023418</v>
       </c>
       <c r="B36" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4237,21 +4206,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4261,10 +4230,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753768</v>
+        <v>753406</v>
       </c>
       <c r="R36" t="n">
-        <v>7218016</v>
+        <v>7217999</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4323,10 +4292,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125023369</v>
+        <v>125023423</v>
       </c>
       <c r="B37" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4339,21 +4308,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4363,10 +4332,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753797</v>
+        <v>753610</v>
       </c>
       <c r="R37" t="n">
-        <v>7218005</v>
+        <v>7217727</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4425,7 +4394,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125023434</v>
+        <v>125023445</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4459,24 +4428,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753797</v>
+        <v>753715</v>
       </c>
       <c r="R38" t="n">
-        <v>7217988</v>
+        <v>7218026</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4513,7 +4474,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4540,10 +4501,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125023315</v>
+        <v>125023328</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4556,21 +4517,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4580,10 +4541,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753491</v>
+        <v>753742</v>
       </c>
       <c r="R39" t="n">
-        <v>7217766</v>
+        <v>7217926</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4616,11 +4577,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4647,10 +4603,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125023439</v>
+        <v>125023350</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4663,21 +4619,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4687,10 +4643,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753568</v>
+        <v>753789</v>
       </c>
       <c r="R40" t="n">
-        <v>7217716</v>
+        <v>7217812</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4723,11 +4679,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4754,10 +4705,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125023328</v>
+        <v>125023316</v>
       </c>
       <c r="B41" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4770,34 +4721,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753742</v>
+        <v>753568</v>
       </c>
       <c r="R41" t="n">
-        <v>7217926</v>
+        <v>7217733</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4830,6 +4789,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4856,10 +4820,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125023380</v>
+        <v>125023412</v>
       </c>
       <c r="B42" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4868,25 +4832,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4896,10 +4860,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753769</v>
+        <v>753568</v>
       </c>
       <c r="R42" t="n">
-        <v>7218019</v>
+        <v>7217875</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4958,7 +4922,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125023407</v>
+        <v>125023414</v>
       </c>
       <c r="B43" t="n">
         <v>78810</v>
@@ -4998,10 +4962,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753671</v>
+        <v>753630</v>
       </c>
       <c r="R43" t="n">
-        <v>7218008</v>
+        <v>7218006</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5060,10 +5024,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125023413</v>
+        <v>125023443</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5076,21 +5040,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5100,10 +5064,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753517</v>
+        <v>753575</v>
       </c>
       <c r="R44" t="n">
-        <v>7217918</v>
+        <v>7217751</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5136,6 +5100,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5162,10 +5131,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125023401</v>
+        <v>125023365</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5178,21 +5147,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5202,10 +5171,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753780</v>
+        <v>753784</v>
       </c>
       <c r="R45" t="n">
-        <v>7217865</v>
+        <v>7217948</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5264,10 +5233,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125023389</v>
+        <v>125023354</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5276,25 +5245,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5304,10 +5273,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753729</v>
+        <v>753773</v>
       </c>
       <c r="R46" t="n">
-        <v>7218042</v>
+        <v>7217842</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5366,10 +5335,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125023446</v>
+        <v>125023430</v>
       </c>
       <c r="B47" t="n">
-        <v>91221</v>
+        <v>79926</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5378,25 +5347,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1106</v>
+        <v>6463</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5406,10 +5375,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753567</v>
+        <v>753789</v>
       </c>
       <c r="R47" t="n">
-        <v>7217721</v>
+        <v>7217809</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5450,7 +5419,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5469,10 +5437,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125023363</v>
+        <v>125023402</v>
       </c>
       <c r="B48" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5485,21 +5453,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5509,10 +5477,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753782</v>
+        <v>753752</v>
       </c>
       <c r="R48" t="n">
-        <v>7217946</v>
+        <v>7217878</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5571,10 +5539,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125023372</v>
+        <v>125023438</v>
       </c>
       <c r="B49" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5587,21 +5555,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5611,10 +5579,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753790</v>
+        <v>753612</v>
       </c>
       <c r="R49" t="n">
-        <v>7217992</v>
+        <v>7217703</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5647,6 +5615,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5673,7 +5646,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125023368</v>
+        <v>125023375</v>
       </c>
       <c r="B50" t="n">
         <v>79891</v>
@@ -5713,10 +5686,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753808</v>
+        <v>753750</v>
       </c>
       <c r="R50" t="n">
-        <v>7217964</v>
+        <v>7218028</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5775,7 +5748,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125023442</v>
+        <v>125023444</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -5815,10 +5788,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753726</v>
+        <v>753746</v>
       </c>
       <c r="R51" t="n">
-        <v>7218039</v>
+        <v>7217930</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5855,7 +5828,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Barksprätt</t>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5882,10 +5855,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125023325</v>
+        <v>125023343</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5898,42 +5871,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>753575</v>
+        <v>753760</v>
       </c>
       <c r="R52" t="n">
-        <v>7217959</v>
+        <v>7218023</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5970,7 +5935,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5979,6 +5944,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5997,10 +5963,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125023445</v>
+        <v>125023421</v>
       </c>
       <c r="B53" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6013,21 +5979,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6037,10 +6003,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>753715</v>
+        <v>753573</v>
       </c>
       <c r="R53" t="n">
-        <v>7218026</v>
+        <v>7217745</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6073,11 +6039,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6104,10 +6065,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125023406</v>
+        <v>125023315</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6120,21 +6081,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6144,10 +6105,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753718</v>
+        <v>753491</v>
       </c>
       <c r="R54" t="n">
-        <v>7218042</v>
+        <v>7217766</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6180,6 +6141,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6206,10 +6172,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125023435</v>
+        <v>125023446</v>
       </c>
       <c r="B55" t="n">
-        <v>57513</v>
+        <v>91221</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6218,46 +6184,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1106</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753562</v>
+        <v>753567</v>
       </c>
       <c r="R55" t="n">
-        <v>7217727</v>
+        <v>7217721</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6292,17 +6250,13 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färsk bohål</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6321,10 +6275,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125023335</v>
+        <v>125023355</v>
       </c>
       <c r="B56" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6333,25 +6287,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6361,10 +6315,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753790</v>
+        <v>753792</v>
       </c>
       <c r="R56" t="n">
-        <v>7217992</v>
+        <v>7217850</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6423,10 +6377,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125023357</v>
+        <v>125023432</v>
       </c>
       <c r="B57" t="n">
-        <v>79891</v>
+        <v>79926</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6435,25 +6389,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6463,10 +6417,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753793</v>
+        <v>753769</v>
       </c>
       <c r="R57" t="n">
-        <v>7217856</v>
+        <v>7218019</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6525,10 +6479,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125023320</v>
+        <v>125023399</v>
       </c>
       <c r="B58" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6541,21 +6495,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6565,10 +6519,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753687</v>
+        <v>753751</v>
       </c>
       <c r="R58" t="n">
-        <v>7217999</v>
+        <v>7217806</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6627,10 +6581,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125023394</v>
+        <v>125023409</v>
       </c>
       <c r="B59" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6643,21 +6597,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6667,10 +6621,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753596</v>
+        <v>753562</v>
       </c>
       <c r="R59" t="n">
-        <v>7217939</v>
+        <v>7217917</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6729,10 +6683,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125023348</v>
+        <v>125023441</v>
       </c>
       <c r="B60" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6745,21 +6699,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6769,10 +6723,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753817</v>
+        <v>753798</v>
       </c>
       <c r="R60" t="n">
-        <v>7217853</v>
+        <v>7217948</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6805,6 +6759,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6831,10 +6790,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125023429</v>
+        <v>125023391</v>
       </c>
       <c r="B61" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6843,25 +6802,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6871,10 +6830,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753792</v>
+        <v>753706</v>
       </c>
       <c r="R61" t="n">
-        <v>7217798</v>
+        <v>7218039</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6933,10 +6892,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125023367</v>
+        <v>125023338</v>
       </c>
       <c r="B62" t="n">
-        <v>79891</v>
+        <v>8720</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6945,25 +6904,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100798</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smal trollknäppare</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Danosoma conspersum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyllenhal, 1808)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6973,10 +6932,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753786</v>
+        <v>753699</v>
       </c>
       <c r="R62" t="n">
-        <v>7217962</v>
+        <v>7217618</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7017,6 +6976,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7035,10 +6995,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125023354</v>
+        <v>125023380</v>
       </c>
       <c r="B63" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7047,25 +7007,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7075,10 +7035,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753773</v>
+        <v>753769</v>
       </c>
       <c r="R63" t="n">
-        <v>7217842</v>
+        <v>7218019</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7137,7 +7097,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125023352</v>
+        <v>125023372</v>
       </c>
       <c r="B64" t="n">
         <v>79891</v>
@@ -7177,10 +7137,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753763</v>
+        <v>753790</v>
       </c>
       <c r="R64" t="n">
-        <v>7217831</v>
+        <v>7217992</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7239,10 +7199,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125023338</v>
+        <v>125023411</v>
       </c>
       <c r="B65" t="n">
-        <v>8720</v>
+        <v>78810</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7251,25 +7211,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100798</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Smal trollknäppare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Danosoma conspersum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7279,10 +7239,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753699</v>
+        <v>753557</v>
       </c>
       <c r="R65" t="n">
-        <v>7217618</v>
+        <v>7217895</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7323,7 +7283,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7342,10 +7301,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125023390</v>
+        <v>125023406</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7354,25 +7313,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7382,10 +7341,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753701</v>
+        <v>753718</v>
       </c>
       <c r="R66" t="n">
-        <v>7218031</v>
+        <v>7218042</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7444,10 +7403,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125023396</v>
+        <v>125023323</v>
       </c>
       <c r="B67" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7460,41 +7419,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753626</v>
+        <v>753504</v>
       </c>
       <c r="R67" t="n">
-        <v>7218004</v>
+        <v>7217889</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7529,18 +7481,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7559,10 +7505,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125023402</v>
+        <v>125023431</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7571,20 +7517,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7599,10 +7545,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753752</v>
+        <v>753774</v>
       </c>
       <c r="R68" t="n">
-        <v>7217878</v>
+        <v>7217939</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7661,10 +7607,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125023405</v>
+        <v>125023349</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7677,21 +7623,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7701,10 +7647,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753748</v>
+        <v>753795</v>
       </c>
       <c r="R69" t="n">
-        <v>7218047</v>
+        <v>7217800</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7763,10 +7709,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125023418</v>
+        <v>125023326</v>
       </c>
       <c r="B70" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7779,34 +7725,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753406</v>
+        <v>753598</v>
       </c>
       <c r="R70" t="n">
-        <v>7217999</v>
+        <v>7217744</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7839,6 +7793,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7865,10 +7824,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125023421</v>
+        <v>125023330</v>
       </c>
       <c r="B71" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7881,21 +7840,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7905,10 +7864,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753573</v>
+        <v>753730</v>
       </c>
       <c r="R71" t="n">
-        <v>7217745</v>
+        <v>7217943</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7967,10 +7926,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125023403</v>
+        <v>125023395</v>
       </c>
       <c r="B72" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7983,21 +7942,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8007,10 +7966,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753762</v>
+        <v>753472</v>
       </c>
       <c r="R72" t="n">
-        <v>7218015</v>
+        <v>7218031</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8069,10 +8028,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125023343</v>
+        <v>125023403</v>
       </c>
       <c r="B73" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8085,21 +8044,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8109,10 +8068,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>753760</v>
+        <v>753762</v>
       </c>
       <c r="R73" t="n">
-        <v>7218023</v>
+        <v>7218015</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8147,18 +8106,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8279,10 +8232,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125023323</v>
+        <v>125023325</v>
       </c>
       <c r="B75" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8295,34 +8248,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>753504</v>
+        <v>753575</v>
       </c>
       <c r="R75" t="n">
-        <v>7217889</v>
+        <v>7217959</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8355,6 +8316,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8381,10 +8347,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125023318</v>
+        <v>125023327</v>
       </c>
       <c r="B76" t="n">
-        <v>90977</v>
+        <v>57666</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8393,25 +8359,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8421,10 +8387,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>753680</v>
+        <v>753740</v>
       </c>
       <c r="R76" t="n">
-        <v>7218004</v>
+        <v>7217891</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8483,10 +8449,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125023441</v>
+        <v>125023390</v>
       </c>
       <c r="B77" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8495,25 +8461,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8523,10 +8489,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>753798</v>
+        <v>753701</v>
       </c>
       <c r="R77" t="n">
-        <v>7217948</v>
+        <v>7218031</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8559,11 +8525,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8590,10 +8551,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125023391</v>
+        <v>125023396</v>
       </c>
       <c r="B78" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8602,38 +8563,45 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>753706</v>
+        <v>753626</v>
       </c>
       <c r="R78" t="n">
-        <v>7218039</v>
+        <v>7218004</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8668,12 +8636,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8692,10 +8666,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125023388</v>
+        <v>125023335</v>
       </c>
       <c r="B79" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8704,25 +8678,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8732,10 +8706,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>753742</v>
+        <v>753790</v>
       </c>
       <c r="R79" t="n">
-        <v>7217924</v>
+        <v>7217992</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8794,10 +8768,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125023392</v>
+        <v>125023381</v>
       </c>
       <c r="B80" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8806,25 +8780,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8834,10 +8808,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>753718</v>
+        <v>753722</v>
       </c>
       <c r="R80" t="n">
-        <v>7218035</v>
+        <v>7218033</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8896,10 +8870,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125023351</v>
+        <v>125023320</v>
       </c>
       <c r="B81" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8912,21 +8886,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8936,10 +8910,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>753758</v>
+        <v>753687</v>
       </c>
       <c r="R81" t="n">
-        <v>7217819</v>
+        <v>7217999</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8998,10 +8972,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125023345</v>
+        <v>125023394</v>
       </c>
       <c r="B82" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9014,21 +8988,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9038,10 +9012,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>753790</v>
+        <v>753596</v>
       </c>
       <c r="R82" t="n">
-        <v>7217981</v>
+        <v>7217939</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9100,7 +9074,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125023409</v>
+        <v>125023426</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -9140,10 +9114,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>753562</v>
+        <v>753597</v>
       </c>
       <c r="R83" t="n">
-        <v>7217917</v>
+        <v>7217728</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9202,10 +9176,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125023333</v>
+        <v>125023368</v>
       </c>
       <c r="B84" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9218,21 +9192,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9242,10 +9216,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>753781</v>
+        <v>753808</v>
       </c>
       <c r="R84" t="n">
-        <v>7217902</v>
+        <v>7217964</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9304,10 +9278,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125023365</v>
+        <v>125023398</v>
       </c>
       <c r="B85" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9320,34 +9294,41 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>753784</v>
+        <v>753778</v>
       </c>
       <c r="R85" t="n">
-        <v>7217948</v>
+        <v>7217858</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9382,12 +9363,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9406,10 +9393,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125023321</v>
+        <v>125023442</v>
       </c>
       <c r="B86" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9422,21 +9409,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9446,10 +9433,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>753679</v>
+        <v>753726</v>
       </c>
       <c r="R86" t="n">
-        <v>7218005</v>
+        <v>7218039</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9482,6 +9469,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9508,10 +9500,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125023431</v>
+        <v>125023388</v>
       </c>
       <c r="B87" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9520,25 +9512,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9548,10 +9540,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>753774</v>
+        <v>753742</v>
       </c>
       <c r="R87" t="n">
-        <v>7217939</v>
+        <v>7217924</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9610,10 +9602,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125023349</v>
+        <v>125023435</v>
       </c>
       <c r="B88" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9626,34 +9618,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>753795</v>
+        <v>753562</v>
       </c>
       <c r="R88" t="n">
-        <v>7217800</v>
+        <v>7217727</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9686,6 +9686,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9712,10 +9717,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125023347</v>
+        <v>125023321</v>
       </c>
       <c r="B89" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9728,21 +9733,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9752,10 +9757,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>753850</v>
+        <v>753679</v>
       </c>
       <c r="R89" t="n">
-        <v>7217843</v>
+        <v>7218005</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9814,10 +9819,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125023438</v>
+        <v>125023345</v>
       </c>
       <c r="B90" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9830,21 +9835,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9854,10 +9859,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>753612</v>
+        <v>753790</v>
       </c>
       <c r="R90" t="n">
-        <v>7217703</v>
+        <v>7217981</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9890,11 +9895,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9921,10 +9921,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125023395</v>
+        <v>125023334</v>
       </c>
       <c r="B91" t="n">
-        <v>91030</v>
+        <v>79920</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9933,25 +9933,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9961,10 +9961,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>753472</v>
+        <v>753752</v>
       </c>
       <c r="R91" t="n">
-        <v>7218031</v>
+        <v>7217919</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10023,7 +10023,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125023420</v>
+        <v>125023405</v>
       </c>
       <c r="B92" t="n">
         <v>78810</v>
@@ -10063,10 +10063,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>753559</v>
+        <v>753748</v>
       </c>
       <c r="R92" t="n">
-        <v>7217734</v>
+        <v>7218047</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10125,10 +10125,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125023381</v>
+        <v>125023319</v>
       </c>
       <c r="B93" t="n">
-        <v>79927</v>
+        <v>90977</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10141,21 +10141,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10165,10 +10165,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>753722</v>
+        <v>753506</v>
       </c>
       <c r="R93" t="n">
-        <v>7218033</v>
+        <v>7217904</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10227,10 +10227,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125023341</v>
+        <v>125023373</v>
       </c>
       <c r="B94" t="n">
-        <v>79919</v>
+        <v>79891</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10239,25 +10239,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10267,10 +10267,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>753654</v>
+        <v>753768</v>
       </c>
       <c r="R94" t="n">
-        <v>7218008</v>
+        <v>7218016</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10329,7 +10329,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125023374</v>
+        <v>125023366</v>
       </c>
       <c r="B95" t="n">
         <v>79891</v>
@@ -10369,10 +10369,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>753763</v>
+        <v>753778</v>
       </c>
       <c r="R95" t="n">
-        <v>7218015</v>
+        <v>7217945</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10431,7 +10431,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125023416</v>
+        <v>125023407</v>
       </c>
       <c r="B96" t="n">
         <v>78810</v>
@@ -10471,10 +10471,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>753470</v>
+        <v>753671</v>
       </c>
       <c r="R96" t="n">
-        <v>7218024</v>
+        <v>7218008</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125023401</v>
+        <v>125023439</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>753780</v>
+        <v>753568</v>
       </c>
       <c r="R9" t="n">
-        <v>7217865</v>
+        <v>7217716</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,6 +1493,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125023387</v>
+        <v>125023401</v>
       </c>
       <c r="B10" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1559,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>753816</v>
+        <v>753780</v>
       </c>
       <c r="R10" t="n">
-        <v>7217838</v>
+        <v>7217865</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,10 +1626,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125023351</v>
+        <v>125023387</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1637,21 +1642,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1661,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>753758</v>
+        <v>753816</v>
       </c>
       <c r="R11" t="n">
-        <v>7217819</v>
+        <v>7217838</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1728,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023348</v>
+        <v>125023351</v>
       </c>
       <c r="B12" t="n">
         <v>79891</v>
@@ -1763,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>753817</v>
+        <v>753758</v>
       </c>
       <c r="R12" t="n">
-        <v>7217853</v>
+        <v>7217819</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,10 +1830,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125023337</v>
+        <v>125023348</v>
       </c>
       <c r="B13" t="n">
-        <v>79795</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,25 +1842,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1865,10 +1870,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753523</v>
+        <v>753817</v>
       </c>
       <c r="R13" t="n">
-        <v>7218086</v>
+        <v>7217853</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,10 +1932,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125023318</v>
+        <v>125023337</v>
       </c>
       <c r="B14" t="n">
-        <v>90977</v>
+        <v>79795</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1943,21 +1948,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1967,10 +1972,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753680</v>
+        <v>753523</v>
       </c>
       <c r="R14" t="n">
-        <v>7218004</v>
+        <v>7218086</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,10 +2034,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125023439</v>
+        <v>125023318</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,25 +2046,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2069,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>753568</v>
+        <v>753680</v>
       </c>
       <c r="R15" t="n">
-        <v>7217716</v>
+        <v>7218004</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,11 +2110,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3578,10 +3578,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125023333</v>
+        <v>125023341</v>
       </c>
       <c r="B30" t="n">
-        <v>57666</v>
+        <v>79919</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3590,25 +3590,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753781</v>
+        <v>753654</v>
       </c>
       <c r="R30" t="n">
-        <v>7217902</v>
+        <v>7218008</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3680,10 +3680,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125023389</v>
+        <v>125023374</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3692,25 +3692,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3720,10 +3720,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753729</v>
+        <v>753763</v>
       </c>
       <c r="R31" t="n">
-        <v>7218042</v>
+        <v>7218015</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3782,10 +3782,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125023341</v>
+        <v>125023347</v>
       </c>
       <c r="B32" t="n">
-        <v>79919</v>
+        <v>79891</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3794,25 +3794,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3822,10 +3822,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753654</v>
+        <v>753850</v>
       </c>
       <c r="R32" t="n">
-        <v>7218008</v>
+        <v>7217843</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125023374</v>
+        <v>125023333</v>
       </c>
       <c r="B33" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3900,21 +3900,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753763</v>
+        <v>753781</v>
       </c>
       <c r="R33" t="n">
-        <v>7218015</v>
+        <v>7217902</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3986,10 +3986,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125023347</v>
+        <v>125023389</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3998,25 +3998,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4026,10 +4026,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753850</v>
+        <v>753729</v>
       </c>
       <c r="R34" t="n">
-        <v>7217843</v>
+        <v>7218042</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5748,10 +5748,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125023444</v>
+        <v>125023343</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5764,21 +5764,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753746</v>
+        <v>753760</v>
       </c>
       <c r="R51" t="n">
-        <v>7217930</v>
+        <v>7218023</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Avskalad gran</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5837,6 +5837,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5855,10 +5856,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125023343</v>
+        <v>125023444</v>
       </c>
       <c r="B52" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5871,21 +5872,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5895,10 +5896,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>753760</v>
+        <v>753746</v>
       </c>
       <c r="R52" t="n">
-        <v>7218023</v>
+        <v>7217930</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5935,7 +5936,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5944,7 +5945,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125023315</v>
+        <v>125023446</v>
       </c>
       <c r="B54" t="n">
-        <v>57513</v>
+        <v>91221</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6077,25 +6077,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1106</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753491</v>
+        <v>753567</v>
       </c>
       <c r="R54" t="n">
-        <v>7217766</v>
+        <v>7217721</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6143,17 +6143,13 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6172,10 +6168,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125023446</v>
+        <v>125023315</v>
       </c>
       <c r="B55" t="n">
-        <v>91221</v>
+        <v>57513</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6184,25 +6180,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1106</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6212,10 +6208,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753567</v>
+        <v>753491</v>
       </c>
       <c r="R55" t="n">
-        <v>7217721</v>
+        <v>7217766</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6250,13 +6246,17 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6892,10 +6892,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125023338</v>
+        <v>125023380</v>
       </c>
       <c r="B62" t="n">
-        <v>8720</v>
+        <v>79927</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6904,25 +6904,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100798</v>
+        <v>6464</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Smal trollknäppare</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Danosoma conspersum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6932,10 +6932,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753699</v>
+        <v>753769</v>
       </c>
       <c r="R62" t="n">
-        <v>7217618</v>
+        <v>7218019</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6976,7 +6976,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6995,10 +6994,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125023380</v>
+        <v>125023372</v>
       </c>
       <c r="B63" t="n">
-        <v>79927</v>
+        <v>79891</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7007,25 +7006,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7035,10 +7034,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753769</v>
+        <v>753790</v>
       </c>
       <c r="R63" t="n">
-        <v>7218019</v>
+        <v>7217992</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7097,10 +7096,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125023372</v>
+        <v>125023411</v>
       </c>
       <c r="B64" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7113,21 +7112,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7137,10 +7136,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753790</v>
+        <v>753557</v>
       </c>
       <c r="R64" t="n">
-        <v>7217992</v>
+        <v>7217895</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7199,7 +7198,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125023411</v>
+        <v>125023406</v>
       </c>
       <c r="B65" t="n">
         <v>78810</v>
@@ -7239,10 +7238,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753557</v>
+        <v>753718</v>
       </c>
       <c r="R65" t="n">
-        <v>7217895</v>
+        <v>7218042</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7301,10 +7300,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125023406</v>
+        <v>125023338</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>8720</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7313,25 +7312,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100798</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smal trollknäppare</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Danosoma conspersum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyllenhal, 1808)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7341,10 +7340,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753718</v>
+        <v>753699</v>
       </c>
       <c r="R66" t="n">
-        <v>7218042</v>
+        <v>7217618</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7385,6 +7384,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125023429</v>
+        <v>125023404</v>
       </c>
       <c r="B4" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,20 +919,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753792</v>
+        <v>753743</v>
       </c>
       <c r="R4" t="n">
-        <v>7217798</v>
+        <v>7218044</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125023419</v>
+        <v>125023363</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,21 +1025,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753550</v>
+        <v>753782</v>
       </c>
       <c r="R5" t="n">
-        <v>7217725</v>
+        <v>7217946</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125023416</v>
+        <v>125023380</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,25 +1123,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753470</v>
+        <v>753769</v>
       </c>
       <c r="R6" t="n">
-        <v>7218024</v>
+        <v>7218019</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125023413</v>
+        <v>125023405</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>753517</v>
+        <v>753748</v>
       </c>
       <c r="R7" t="n">
-        <v>7217918</v>
+        <v>7218047</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125023404</v>
+        <v>125023414</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>753743</v>
+        <v>753630</v>
       </c>
       <c r="R8" t="n">
-        <v>7218044</v>
+        <v>7218006</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125023439</v>
+        <v>125023351</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>753568</v>
+        <v>753758</v>
       </c>
       <c r="R9" t="n">
-        <v>7217716</v>
+        <v>7217819</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,11 +1493,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125023401</v>
+        <v>125023337</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79795</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,25 +1531,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1564,10 +1559,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>753780</v>
+        <v>753523</v>
       </c>
       <c r="R10" t="n">
-        <v>7217865</v>
+        <v>7218086</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125023387</v>
+        <v>125023392</v>
       </c>
       <c r="B11" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,25 +1633,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1666,10 +1661,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>753816</v>
+        <v>753718</v>
       </c>
       <c r="R11" t="n">
-        <v>7217838</v>
+        <v>7218035</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023351</v>
+        <v>125023328</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1744,21 +1739,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1768,10 +1763,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>753758</v>
+        <v>753742</v>
       </c>
       <c r="R12" t="n">
-        <v>7217819</v>
+        <v>7217926</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125023348</v>
+        <v>125023416</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1846,21 +1841,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1870,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753817</v>
+        <v>753470</v>
       </c>
       <c r="R13" t="n">
-        <v>7217853</v>
+        <v>7218024</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125023337</v>
+        <v>125023431</v>
       </c>
       <c r="B14" t="n">
-        <v>79795</v>
+        <v>79926</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1948,21 +1943,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1972,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753523</v>
+        <v>753774</v>
       </c>
       <c r="R14" t="n">
-        <v>7218086</v>
+        <v>7217939</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,10 +2029,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125023318</v>
+        <v>125023350</v>
       </c>
       <c r="B15" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2046,25 +2041,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2074,10 +2069,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>753680</v>
+        <v>753789</v>
       </c>
       <c r="R15" t="n">
-        <v>7218004</v>
+        <v>7217812</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2131,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125023369</v>
+        <v>125023374</v>
       </c>
       <c r="B16" t="n">
         <v>79891</v>
@@ -2176,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753797</v>
+        <v>753763</v>
       </c>
       <c r="R16" t="n">
-        <v>7218005</v>
+        <v>7218015</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,7 +2233,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125023434</v>
+        <v>125023316</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2276,7 +2271,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2286,10 +2281,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753797</v>
+        <v>753568</v>
       </c>
       <c r="R17" t="n">
-        <v>7217988</v>
+        <v>7217733</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,7 +2321,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
+          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2353,10 +2348,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125023324</v>
+        <v>125023435</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2369,34 +2364,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753480</v>
+        <v>753562</v>
       </c>
       <c r="R18" t="n">
-        <v>7218033</v>
+        <v>7217727</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,6 +2432,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2455,10 +2463,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125023360</v>
+        <v>125023325</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2471,34 +2479,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753752</v>
+        <v>753575</v>
       </c>
       <c r="R19" t="n">
-        <v>7217944</v>
+        <v>7217959</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,6 +2547,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2557,10 +2578,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125023367</v>
+        <v>125023338</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>8720</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2569,25 +2590,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smal trollknäppare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Danosoma conspersum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyllenhal, 1808)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2597,10 +2618,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753786</v>
+        <v>753699</v>
       </c>
       <c r="R20" t="n">
-        <v>7217962</v>
+        <v>7217618</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2641,6 +2662,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2659,10 +2681,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125023392</v>
+        <v>125023401</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2671,25 +2693,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2699,10 +2721,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753718</v>
+        <v>753780</v>
       </c>
       <c r="R21" t="n">
-        <v>7218035</v>
+        <v>7217865</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2761,10 +2783,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125023342</v>
+        <v>125023394</v>
       </c>
       <c r="B22" t="n">
-        <v>78547</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2777,21 +2799,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2801,10 +2823,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753722</v>
+        <v>753596</v>
       </c>
       <c r="R22" t="n">
-        <v>7217596</v>
+        <v>7217939</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2845,7 +2867,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2864,7 +2885,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125023420</v>
+        <v>125023407</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2904,10 +2925,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753559</v>
+        <v>753671</v>
       </c>
       <c r="R23" t="n">
-        <v>7217734</v>
+        <v>7218008</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2966,10 +2987,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125023359</v>
+        <v>125023335</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2978,25 +2999,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3006,10 +3027,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753753</v>
+        <v>753790</v>
       </c>
       <c r="R24" t="n">
-        <v>7217910</v>
+        <v>7217992</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3068,7 +3089,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125023358</v>
+        <v>125023352</v>
       </c>
       <c r="B25" t="n">
         <v>79891</v>
@@ -3108,10 +3129,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753758</v>
+        <v>753763</v>
       </c>
       <c r="R25" t="n">
-        <v>7217900</v>
+        <v>7217831</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3170,7 +3191,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125023378</v>
+        <v>125023368</v>
       </c>
       <c r="B26" t="n">
         <v>79891</v>
@@ -3210,10 +3231,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753722</v>
+        <v>753808</v>
       </c>
       <c r="R26" t="n">
-        <v>7218033</v>
+        <v>7217964</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3272,10 +3293,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125023357</v>
+        <v>125023429</v>
       </c>
       <c r="B27" t="n">
-        <v>79891</v>
+        <v>79926</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3284,25 +3305,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3312,10 +3333,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753793</v>
+        <v>753792</v>
       </c>
       <c r="R27" t="n">
-        <v>7217856</v>
+        <v>7217798</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3374,10 +3395,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125023352</v>
+        <v>125023342</v>
       </c>
       <c r="B28" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3390,21 +3411,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3414,10 +3435,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753763</v>
+        <v>753722</v>
       </c>
       <c r="R28" t="n">
-        <v>7217831</v>
+        <v>7217596</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3458,6 +3479,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3476,10 +3498,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125023336</v>
+        <v>125023432</v>
       </c>
       <c r="B29" t="n">
-        <v>90962</v>
+        <v>79926</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3488,25 +3510,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>112</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3516,10 +3538,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753566</v>
+        <v>753769</v>
       </c>
       <c r="R29" t="n">
-        <v>7217862</v>
+        <v>7218019</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3578,10 +3600,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125023341</v>
+        <v>125023349</v>
       </c>
       <c r="B30" t="n">
-        <v>79919</v>
+        <v>79891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3590,25 +3612,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3618,10 +3640,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753654</v>
+        <v>753795</v>
       </c>
       <c r="R30" t="n">
-        <v>7218008</v>
+        <v>7217800</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3680,7 +3702,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125023374</v>
+        <v>125023366</v>
       </c>
       <c r="B31" t="n">
         <v>79891</v>
@@ -3720,10 +3742,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753763</v>
+        <v>753778</v>
       </c>
       <c r="R31" t="n">
-        <v>7218015</v>
+        <v>7217945</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3782,10 +3804,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125023347</v>
+        <v>125023443</v>
       </c>
       <c r="B32" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3798,21 +3820,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3822,10 +3844,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753850</v>
+        <v>753575</v>
       </c>
       <c r="R32" t="n">
-        <v>7217843</v>
+        <v>7217751</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3858,6 +3880,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3884,10 +3911,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125023333</v>
+        <v>125023406</v>
       </c>
       <c r="B33" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3900,21 +3927,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3924,10 +3951,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753781</v>
+        <v>753718</v>
       </c>
       <c r="R33" t="n">
-        <v>7217902</v>
+        <v>7218042</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3986,10 +4013,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125023389</v>
+        <v>125023355</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3998,25 +4025,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4026,10 +4053,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753729</v>
+        <v>753792</v>
       </c>
       <c r="R34" t="n">
-        <v>7218042</v>
+        <v>7217850</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4088,7 +4115,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125023363</v>
+        <v>125023362</v>
       </c>
       <c r="B35" t="n">
         <v>79891</v>
@@ -4128,10 +4155,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753782</v>
+        <v>753752</v>
       </c>
       <c r="R35" t="n">
-        <v>7217946</v>
+        <v>7217944</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4190,10 +4217,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125023418</v>
+        <v>125023438</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4206,21 +4233,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4230,10 +4257,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753406</v>
+        <v>753612</v>
       </c>
       <c r="R36" t="n">
-        <v>7217999</v>
+        <v>7217703</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4266,6 +4293,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4292,10 +4324,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125023423</v>
+        <v>125023434</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4308,34 +4340,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753610</v>
+        <v>753797</v>
       </c>
       <c r="R37" t="n">
-        <v>7217727</v>
+        <v>7217988</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4368,6 +4408,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4394,10 +4439,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125023445</v>
+        <v>125023324</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4410,21 +4455,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4434,10 +4479,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753715</v>
+        <v>753480</v>
       </c>
       <c r="R38" t="n">
-        <v>7218026</v>
+        <v>7218033</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4470,11 +4515,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4501,10 +4541,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125023328</v>
+        <v>125023336</v>
       </c>
       <c r="B39" t="n">
-        <v>57666</v>
+        <v>90962</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4517,21 +4557,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>112</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4541,10 +4581,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753742</v>
+        <v>753566</v>
       </c>
       <c r="R39" t="n">
-        <v>7217926</v>
+        <v>7217862</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4603,10 +4643,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125023350</v>
+        <v>125023446</v>
       </c>
       <c r="B40" t="n">
-        <v>79891</v>
+        <v>91221</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4615,25 +4655,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1106</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4643,10 +4683,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753789</v>
+        <v>753567</v>
       </c>
       <c r="R40" t="n">
-        <v>7217812</v>
+        <v>7217721</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4687,6 +4727,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4705,10 +4746,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125023316</v>
+        <v>125023398</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4721,29 +4762,28 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4753,10 +4793,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753568</v>
+        <v>753778</v>
       </c>
       <c r="R41" t="n">
-        <v>7217733</v>
+        <v>7217858</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4793,7 +4833,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre bohål</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4802,6 +4842,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4820,10 +4861,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125023412</v>
+        <v>125023319</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4832,25 +4873,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4860,10 +4901,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753568</v>
+        <v>753506</v>
       </c>
       <c r="R42" t="n">
-        <v>7217875</v>
+        <v>7217904</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4922,7 +4963,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125023414</v>
+        <v>125023420</v>
       </c>
       <c r="B43" t="n">
         <v>78810</v>
@@ -4962,10 +5003,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753630</v>
+        <v>753559</v>
       </c>
       <c r="R43" t="n">
-        <v>7218006</v>
+        <v>7217734</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5024,10 +5065,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125023443</v>
+        <v>125023348</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5040,21 +5081,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5064,10 +5105,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753575</v>
+        <v>753817</v>
       </c>
       <c r="R44" t="n">
-        <v>7217751</v>
+        <v>7217853</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5100,11 +5141,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5131,10 +5167,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125023365</v>
+        <v>125023423</v>
       </c>
       <c r="B45" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5147,21 +5183,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5171,10 +5207,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753784</v>
+        <v>753610</v>
       </c>
       <c r="R45" t="n">
-        <v>7217948</v>
+        <v>7217727</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5233,10 +5269,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125023354</v>
+        <v>125023391</v>
       </c>
       <c r="B46" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5245,25 +5281,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5273,10 +5309,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753773</v>
+        <v>753706</v>
       </c>
       <c r="R46" t="n">
-        <v>7217842</v>
+        <v>7218039</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5335,10 +5371,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125023430</v>
+        <v>125023388</v>
       </c>
       <c r="B47" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5347,25 +5383,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5375,10 +5411,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753789</v>
+        <v>753742</v>
       </c>
       <c r="R47" t="n">
-        <v>7217809</v>
+        <v>7217924</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5437,10 +5473,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125023402</v>
+        <v>125023390</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5449,25 +5485,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5477,10 +5513,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753752</v>
+        <v>753701</v>
       </c>
       <c r="R48" t="n">
-        <v>7217878</v>
+        <v>7218031</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5539,7 +5575,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125023438</v>
+        <v>125023444</v>
       </c>
       <c r="B49" t="n">
         <v>57513</v>
@@ -5579,10 +5615,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753612</v>
+        <v>753746</v>
       </c>
       <c r="R49" t="n">
-        <v>7217703</v>
+        <v>7217930</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5619,7 +5655,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Barksprätt</t>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5646,7 +5682,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125023375</v>
+        <v>125023359</v>
       </c>
       <c r="B50" t="n">
         <v>79891</v>
@@ -5686,10 +5722,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753750</v>
+        <v>753753</v>
       </c>
       <c r="R50" t="n">
-        <v>7218028</v>
+        <v>7217910</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5748,10 +5784,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125023343</v>
+        <v>125023334</v>
       </c>
       <c r="B51" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5760,25 +5796,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5788,10 +5824,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753760</v>
+        <v>753752</v>
       </c>
       <c r="R51" t="n">
-        <v>7218023</v>
+        <v>7217919</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5826,18 +5862,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5856,10 +5886,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125023444</v>
+        <v>125023378</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5872,21 +5902,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5896,10 +5926,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>753746</v>
+        <v>753722</v>
       </c>
       <c r="R52" t="n">
-        <v>7217930</v>
+        <v>7218033</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5932,11 +5962,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5963,7 +5988,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125023421</v>
+        <v>125023411</v>
       </c>
       <c r="B53" t="n">
         <v>78810</v>
@@ -6003,10 +6028,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>753573</v>
+        <v>753557</v>
       </c>
       <c r="R53" t="n">
-        <v>7217745</v>
+        <v>7217895</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6065,10 +6090,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125023446</v>
+        <v>125023375</v>
       </c>
       <c r="B54" t="n">
-        <v>91221</v>
+        <v>79891</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6077,25 +6102,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1106</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6105,10 +6130,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753567</v>
+        <v>753750</v>
       </c>
       <c r="R54" t="n">
-        <v>7217721</v>
+        <v>7218028</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6149,7 +6174,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6168,10 +6192,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125023315</v>
+        <v>125023354</v>
       </c>
       <c r="B55" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6184,21 +6208,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6208,10 +6232,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753491</v>
+        <v>753773</v>
       </c>
       <c r="R55" t="n">
-        <v>7217766</v>
+        <v>7217842</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6244,11 +6268,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6275,10 +6294,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125023355</v>
+        <v>125023439</v>
       </c>
       <c r="B56" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6291,21 +6310,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6315,10 +6334,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753792</v>
+        <v>753568</v>
       </c>
       <c r="R56" t="n">
-        <v>7217850</v>
+        <v>7217716</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6351,6 +6370,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6377,10 +6401,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125023432</v>
+        <v>125023389</v>
       </c>
       <c r="B57" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6389,25 +6413,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6417,10 +6441,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753769</v>
+        <v>753729</v>
       </c>
       <c r="R57" t="n">
-        <v>7218019</v>
+        <v>7218042</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6479,7 +6503,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125023399</v>
+        <v>125023426</v>
       </c>
       <c r="B58" t="n">
         <v>78810</v>
@@ -6519,10 +6543,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753751</v>
+        <v>753597</v>
       </c>
       <c r="R58" t="n">
-        <v>7217806</v>
+        <v>7217728</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6581,10 +6605,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125023409</v>
+        <v>125023381</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6593,25 +6617,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6621,10 +6645,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753562</v>
+        <v>753722</v>
       </c>
       <c r="R59" t="n">
-        <v>7217917</v>
+        <v>7218033</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6683,10 +6707,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125023441</v>
+        <v>125023421</v>
       </c>
       <c r="B60" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6699,21 +6723,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6723,10 +6747,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753798</v>
+        <v>753573</v>
       </c>
       <c r="R60" t="n">
-        <v>7217948</v>
+        <v>7217745</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6759,11 +6783,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6790,10 +6809,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125023391</v>
+        <v>125023321</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6802,25 +6821,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6830,10 +6849,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753706</v>
+        <v>753679</v>
       </c>
       <c r="R61" t="n">
-        <v>7218039</v>
+        <v>7218005</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6892,10 +6911,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125023380</v>
+        <v>125023373</v>
       </c>
       <c r="B62" t="n">
-        <v>79927</v>
+        <v>79891</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6904,25 +6923,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6932,10 +6951,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753769</v>
+        <v>753768</v>
       </c>
       <c r="R62" t="n">
-        <v>7218019</v>
+        <v>7218016</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6994,7 +7013,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125023372</v>
+        <v>125023347</v>
       </c>
       <c r="B63" t="n">
         <v>79891</v>
@@ -7034,10 +7053,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753790</v>
+        <v>753850</v>
       </c>
       <c r="R63" t="n">
-        <v>7217992</v>
+        <v>7217843</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7096,10 +7115,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125023411</v>
+        <v>125023315</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7112,21 +7131,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7136,10 +7155,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753557</v>
+        <v>753491</v>
       </c>
       <c r="R64" t="n">
-        <v>7217895</v>
+        <v>7217766</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7172,6 +7191,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7198,7 +7222,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125023406</v>
+        <v>125023412</v>
       </c>
       <c r="B65" t="n">
         <v>78810</v>
@@ -7238,10 +7262,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753718</v>
+        <v>753568</v>
       </c>
       <c r="R65" t="n">
-        <v>7218042</v>
+        <v>7217875</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7300,10 +7324,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125023338</v>
+        <v>125023403</v>
       </c>
       <c r="B66" t="n">
-        <v>8720</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7312,25 +7336,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100798</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Smal trollknäppare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Danosoma conspersum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7340,10 +7364,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753699</v>
+        <v>753762</v>
       </c>
       <c r="R66" t="n">
-        <v>7217618</v>
+        <v>7218015</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7384,7 +7408,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7403,10 +7426,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125023323</v>
+        <v>125023327</v>
       </c>
       <c r="B67" t="n">
-        <v>91012</v>
+        <v>57666</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7419,21 +7442,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7443,10 +7466,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753504</v>
+        <v>753740</v>
       </c>
       <c r="R67" t="n">
-        <v>7217889</v>
+        <v>7217891</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7505,10 +7528,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125023431</v>
+        <v>125023399</v>
       </c>
       <c r="B68" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7517,20 +7540,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7545,10 +7568,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753774</v>
+        <v>753751</v>
       </c>
       <c r="R68" t="n">
-        <v>7217939</v>
+        <v>7217806</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7607,10 +7630,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125023349</v>
+        <v>125023341</v>
       </c>
       <c r="B69" t="n">
-        <v>79891</v>
+        <v>79919</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7619,25 +7642,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7647,10 +7670,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753795</v>
+        <v>753654</v>
       </c>
       <c r="R69" t="n">
-        <v>7217800</v>
+        <v>7218008</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7709,10 +7732,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125023326</v>
+        <v>125023345</v>
       </c>
       <c r="B70" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7725,42 +7748,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753598</v>
+        <v>753790</v>
       </c>
       <c r="R70" t="n">
-        <v>7217744</v>
+        <v>7217981</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7793,11 +7808,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7824,10 +7834,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125023330</v>
+        <v>125023419</v>
       </c>
       <c r="B71" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7840,21 +7850,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7864,10 +7874,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753730</v>
+        <v>753550</v>
       </c>
       <c r="R71" t="n">
-        <v>7217943</v>
+        <v>7217725</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7926,10 +7936,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125023395</v>
+        <v>125023367</v>
       </c>
       <c r="B72" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7942,21 +7952,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7966,10 +7976,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753472</v>
+        <v>753786</v>
       </c>
       <c r="R72" t="n">
-        <v>7218031</v>
+        <v>7217962</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8028,10 +8038,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125023403</v>
+        <v>125023357</v>
       </c>
       <c r="B73" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8044,21 +8054,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8068,10 +8078,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>753762</v>
+        <v>753793</v>
       </c>
       <c r="R73" t="n">
-        <v>7218015</v>
+        <v>7217856</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8130,7 +8140,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125023417</v>
+        <v>125023413</v>
       </c>
       <c r="B74" t="n">
         <v>78810</v>
@@ -8170,10 +8180,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>753474</v>
+        <v>753517</v>
       </c>
       <c r="R74" t="n">
-        <v>7218026</v>
+        <v>7217918</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8232,10 +8242,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125023325</v>
+        <v>125023372</v>
       </c>
       <c r="B75" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8248,42 +8258,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>753575</v>
+        <v>753790</v>
       </c>
       <c r="R75" t="n">
-        <v>7217959</v>
+        <v>7217992</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8316,11 +8318,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8347,10 +8344,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125023327</v>
+        <v>125023430</v>
       </c>
       <c r="B76" t="n">
-        <v>57666</v>
+        <v>79926</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8359,25 +8356,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8387,10 +8384,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>753740</v>
+        <v>753789</v>
       </c>
       <c r="R76" t="n">
-        <v>7217891</v>
+        <v>7217809</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8449,10 +8446,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125023390</v>
+        <v>125023417</v>
       </c>
       <c r="B77" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8461,25 +8458,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8489,10 +8486,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>753701</v>
+        <v>753474</v>
       </c>
       <c r="R77" t="n">
-        <v>7218031</v>
+        <v>7218026</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8551,10 +8548,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125023396</v>
+        <v>125023326</v>
       </c>
       <c r="B78" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8567,28 +8564,29 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -8598,10 +8596,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>753626</v>
+        <v>753598</v>
       </c>
       <c r="R78" t="n">
-        <v>7218004</v>
+        <v>7217744</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8638,7 +8636,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8647,7 +8645,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8666,10 +8663,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125023335</v>
+        <v>125023402</v>
       </c>
       <c r="B79" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8678,25 +8675,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8706,10 +8703,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>753790</v>
+        <v>753752</v>
       </c>
       <c r="R79" t="n">
-        <v>7217992</v>
+        <v>7217878</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8768,10 +8765,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125023381</v>
+        <v>125023343</v>
       </c>
       <c r="B80" t="n">
-        <v>79927</v>
+        <v>79891</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8780,25 +8777,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8808,10 +8805,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>753722</v>
+        <v>753760</v>
       </c>
       <c r="R80" t="n">
-        <v>7218033</v>
+        <v>7218023</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8846,12 +8843,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8972,7 +8975,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125023394</v>
+        <v>125023395</v>
       </c>
       <c r="B82" t="n">
         <v>91030</v>
@@ -9012,10 +9015,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>753596</v>
+        <v>753472</v>
       </c>
       <c r="R82" t="n">
-        <v>7217939</v>
+        <v>7218031</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9074,10 +9077,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125023426</v>
+        <v>125023442</v>
       </c>
       <c r="B83" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9090,21 +9093,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9114,10 +9117,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>753597</v>
+        <v>753726</v>
       </c>
       <c r="R83" t="n">
-        <v>7217728</v>
+        <v>7218039</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9150,6 +9153,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9176,10 +9184,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125023368</v>
+        <v>125023330</v>
       </c>
       <c r="B84" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9192,21 +9200,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9216,10 +9224,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>753808</v>
+        <v>753730</v>
       </c>
       <c r="R84" t="n">
-        <v>7217964</v>
+        <v>7217943</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9278,10 +9286,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125023398</v>
+        <v>125023333</v>
       </c>
       <c r="B85" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9294,41 +9302,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>753778</v>
+        <v>753781</v>
       </c>
       <c r="R85" t="n">
-        <v>7217858</v>
+        <v>7217902</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9363,18 +9364,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9393,7 +9388,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125023442</v>
+        <v>125023441</v>
       </c>
       <c r="B86" t="n">
         <v>57513</v>
@@ -9433,10 +9428,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>753726</v>
+        <v>753798</v>
       </c>
       <c r="R86" t="n">
-        <v>7218039</v>
+        <v>7217948</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9500,10 +9495,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125023388</v>
+        <v>125023369</v>
       </c>
       <c r="B87" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9512,25 +9507,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9540,10 +9535,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>753742</v>
+        <v>753797</v>
       </c>
       <c r="R87" t="n">
-        <v>7217924</v>
+        <v>7218005</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9602,10 +9597,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125023435</v>
+        <v>125023323</v>
       </c>
       <c r="B88" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9618,42 +9613,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>753562</v>
+        <v>753504</v>
       </c>
       <c r="R88" t="n">
-        <v>7217727</v>
+        <v>7217889</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9686,11 +9673,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9717,10 +9699,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125023321</v>
+        <v>125023365</v>
       </c>
       <c r="B89" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9733,21 +9715,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9757,10 +9739,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>753679</v>
+        <v>753784</v>
       </c>
       <c r="R89" t="n">
-        <v>7218005</v>
+        <v>7217948</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9819,10 +9801,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125023345</v>
+        <v>125023396</v>
       </c>
       <c r="B90" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9835,34 +9817,41 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>753790</v>
+        <v>753626</v>
       </c>
       <c r="R90" t="n">
-        <v>7217981</v>
+        <v>7218004</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9897,12 +9886,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9921,10 +9916,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125023334</v>
+        <v>125023387</v>
       </c>
       <c r="B91" t="n">
-        <v>79920</v>
+        <v>78546</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9933,25 +9928,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9961,10 +9956,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>753752</v>
+        <v>753816</v>
       </c>
       <c r="R91" t="n">
-        <v>7217919</v>
+        <v>7217838</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10023,10 +10018,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125023405</v>
+        <v>125023445</v>
       </c>
       <c r="B92" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10039,21 +10034,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10063,10 +10058,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>753748</v>
+        <v>753715</v>
       </c>
       <c r="R92" t="n">
-        <v>7218047</v>
+        <v>7218026</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10099,6 +10094,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10125,7 +10125,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125023319</v>
+        <v>125023318</v>
       </c>
       <c r="B93" t="n">
         <v>90977</v>
@@ -10165,10 +10165,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>753506</v>
+        <v>753680</v>
       </c>
       <c r="R93" t="n">
-        <v>7217904</v>
+        <v>7218004</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10227,10 +10227,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125023373</v>
+        <v>125023418</v>
       </c>
       <c r="B94" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10243,21 +10243,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10267,10 +10267,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>753768</v>
+        <v>753406</v>
       </c>
       <c r="R94" t="n">
-        <v>7218016</v>
+        <v>7217999</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10329,7 +10329,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125023366</v>
+        <v>125023358</v>
       </c>
       <c r="B95" t="n">
         <v>79891</v>
@@ -10369,10 +10369,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>753778</v>
+        <v>753758</v>
       </c>
       <c r="R95" t="n">
-        <v>7217945</v>
+        <v>7217900</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10431,7 +10431,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125023407</v>
+        <v>125023409</v>
       </c>
       <c r="B96" t="n">
         <v>78810</v>
@@ -10471,10 +10471,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>753671</v>
+        <v>753562</v>
       </c>
       <c r="R96" t="n">
-        <v>7218008</v>
+        <v>7217917</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10533,10 +10533,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125023383</v>
+        <v>125023317</v>
       </c>
       <c r="B97" t="n">
-        <v>91410</v>
+        <v>78842</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10549,16 +10549,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6040186</v>
+        <v>185</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10571,10 +10576,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>753603</v>
+        <v>753719</v>
       </c>
       <c r="R97" t="n">
-        <v>7217932</v>
+        <v>7217616</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10634,10 +10639,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125023317</v>
+        <v>125023383</v>
       </c>
       <c r="B98" t="n">
-        <v>78842</v>
+        <v>91410</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10650,21 +10655,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>185</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10677,10 +10677,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>753719</v>
+        <v>753603</v>
       </c>
       <c r="R98" t="n">
-        <v>7217616</v>
+        <v>7217932</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125023404</v>
+        <v>125023441</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753743</v>
+        <v>753798</v>
       </c>
       <c r="R4" t="n">
-        <v>7218044</v>
+        <v>7217948</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,6 +983,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125023363</v>
+        <v>125023402</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,21 +1030,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753782</v>
+        <v>753752</v>
       </c>
       <c r="R5" t="n">
-        <v>7217946</v>
+        <v>7217878</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125023380</v>
+        <v>125023414</v>
       </c>
       <c r="B6" t="n">
-        <v>79927</v>
+        <v>78947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,25 +1128,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753769</v>
+        <v>753630</v>
       </c>
       <c r="R6" t="n">
-        <v>7218019</v>
+        <v>7218006</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125023405</v>
+        <v>125023388</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,25 +1230,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>753748</v>
+        <v>753742</v>
       </c>
       <c r="R7" t="n">
-        <v>7218047</v>
+        <v>7217924</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125023414</v>
+        <v>125023333</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57793</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,21 +1336,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>753630</v>
+        <v>753781</v>
       </c>
       <c r="R8" t="n">
-        <v>7218006</v>
+        <v>7217902</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125023351</v>
+        <v>125023355</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>753758</v>
+        <v>753792</v>
       </c>
       <c r="R9" t="n">
-        <v>7217819</v>
+        <v>7217850</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125023337</v>
+        <v>125023434</v>
       </c>
       <c r="B10" t="n">
-        <v>79795</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,38 +1536,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>753523</v>
+        <v>753797</v>
       </c>
       <c r="R10" t="n">
-        <v>7218086</v>
+        <v>7217988</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,6 +1608,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1621,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125023392</v>
+        <v>125023380</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>80064</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1661,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>753718</v>
+        <v>753769</v>
       </c>
       <c r="R11" t="n">
-        <v>7218035</v>
+        <v>7218019</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023328</v>
+        <v>125023373</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>80028</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1739,21 +1757,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1763,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>753742</v>
+        <v>753768</v>
       </c>
       <c r="R12" t="n">
-        <v>7217926</v>
+        <v>7218016</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125023416</v>
+        <v>125023372</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>80028</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1841,21 +1859,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1865,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753470</v>
+        <v>753790</v>
       </c>
       <c r="R13" t="n">
-        <v>7218024</v>
+        <v>7217992</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125023431</v>
+        <v>125023396</v>
       </c>
       <c r="B14" t="n">
-        <v>79926</v>
+        <v>78947</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,20 +1957,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1961,16 +1979,23 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753774</v>
+        <v>753626</v>
       </c>
       <c r="R14" t="n">
-        <v>7217939</v>
+        <v>7218004</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,12 +2030,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2029,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125023350</v>
+        <v>125023446</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>91375</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,25 +2072,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1106</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2069,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>753789</v>
+        <v>753567</v>
       </c>
       <c r="R15" t="n">
-        <v>7217812</v>
+        <v>7217721</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,6 +2144,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2131,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125023374</v>
+        <v>125023442</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2147,21 +2179,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753763</v>
+        <v>753726</v>
       </c>
       <c r="R16" t="n">
-        <v>7218015</v>
+        <v>7218039</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2207,6 +2239,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2233,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125023316</v>
+        <v>125023406</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2249,42 +2286,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753568</v>
+        <v>753718</v>
       </c>
       <c r="R17" t="n">
-        <v>7217733</v>
+        <v>7218042</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,11 +2346,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2348,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125023435</v>
+        <v>125023365</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2364,42 +2388,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753562</v>
+        <v>753784</v>
       </c>
       <c r="R18" t="n">
-        <v>7217727</v>
+        <v>7217948</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2432,11 +2448,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2463,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125023325</v>
+        <v>125023354</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2479,42 +2490,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753575</v>
+        <v>753773</v>
       </c>
       <c r="R19" t="n">
-        <v>7217959</v>
+        <v>7217842</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2547,11 +2550,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2578,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125023338</v>
+        <v>125023366</v>
       </c>
       <c r="B20" t="n">
-        <v>8720</v>
+        <v>80028</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2590,25 +2588,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100798</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smal trollknäppare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Danosoma conspersum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2618,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753699</v>
+        <v>753778</v>
       </c>
       <c r="R20" t="n">
-        <v>7217618</v>
+        <v>7217945</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2662,7 +2660,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2681,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125023401</v>
+        <v>125023405</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2721,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753780</v>
+        <v>753748</v>
       </c>
       <c r="R21" t="n">
-        <v>7217865</v>
+        <v>7218047</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,10 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125023394</v>
+        <v>125023416</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>78947</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2799,21 +2796,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2823,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753596</v>
+        <v>753470</v>
       </c>
       <c r="R22" t="n">
-        <v>7217939</v>
+        <v>7218024</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125023407</v>
+        <v>125023432</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>80063</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2897,20 +2894,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2925,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753671</v>
+        <v>753769</v>
       </c>
       <c r="R23" t="n">
-        <v>7218008</v>
+        <v>7218019</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,10 +2984,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125023335</v>
+        <v>125023357</v>
       </c>
       <c r="B24" t="n">
-        <v>79920</v>
+        <v>80028</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2999,25 +2996,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3027,10 +3024,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753790</v>
+        <v>753793</v>
       </c>
       <c r="R24" t="n">
-        <v>7217992</v>
+        <v>7217856</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,10 +3086,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125023352</v>
+        <v>125023387</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>78683</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3105,21 +3102,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3129,10 +3126,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753763</v>
+        <v>753816</v>
       </c>
       <c r="R25" t="n">
-        <v>7217831</v>
+        <v>7217838</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,10 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125023368</v>
+        <v>125023423</v>
       </c>
       <c r="B26" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3207,21 +3204,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3231,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753808</v>
+        <v>753610</v>
       </c>
       <c r="R26" t="n">
-        <v>7217964</v>
+        <v>7217727</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3293,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125023429</v>
+        <v>125023343</v>
       </c>
       <c r="B27" t="n">
-        <v>79926</v>
+        <v>80028</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3305,25 +3302,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3333,10 +3330,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753792</v>
+        <v>753760</v>
       </c>
       <c r="R27" t="n">
-        <v>7217798</v>
+        <v>7218023</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3371,12 +3368,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3395,10 +3398,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125023342</v>
+        <v>125023349</v>
       </c>
       <c r="B28" t="n">
-        <v>78547</v>
+        <v>80028</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3411,21 +3414,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3435,10 +3438,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753722</v>
+        <v>753795</v>
       </c>
       <c r="R28" t="n">
-        <v>7217596</v>
+        <v>7217800</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3479,7 +3482,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3498,10 +3500,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125023432</v>
+        <v>125023391</v>
       </c>
       <c r="B29" t="n">
-        <v>79926</v>
+        <v>98269</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3510,25 +3512,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,10 +3540,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753769</v>
+        <v>753706</v>
       </c>
       <c r="R29" t="n">
-        <v>7218019</v>
+        <v>7218039</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3600,10 +3602,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125023349</v>
+        <v>125023390</v>
       </c>
       <c r="B30" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3612,25 +3614,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3640,10 +3642,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753795</v>
+        <v>753701</v>
       </c>
       <c r="R30" t="n">
-        <v>7217800</v>
+        <v>7218031</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3702,10 +3704,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125023366</v>
+        <v>125023418</v>
       </c>
       <c r="B31" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3718,21 +3720,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3742,10 +3744,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753778</v>
+        <v>753406</v>
       </c>
       <c r="R31" t="n">
-        <v>7217945</v>
+        <v>7217999</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3804,10 +3806,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125023443</v>
+        <v>125023316</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3838,16 +3840,24 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753575</v>
+        <v>753568</v>
       </c>
       <c r="R32" t="n">
-        <v>7217751</v>
+        <v>7217733</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3884,7 +3894,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Barksprätt</t>
+          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3911,10 +3921,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125023406</v>
+        <v>125023401</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3951,10 +3961,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753718</v>
+        <v>753780</v>
       </c>
       <c r="R33" t="n">
-        <v>7218042</v>
+        <v>7217865</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4013,10 +4023,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125023355</v>
+        <v>125023403</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4029,21 +4039,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4053,10 +4063,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753792</v>
+        <v>753762</v>
       </c>
       <c r="R34" t="n">
-        <v>7217850</v>
+        <v>7218015</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4115,10 +4125,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125023362</v>
+        <v>125023444</v>
       </c>
       <c r="B35" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4131,21 +4141,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4155,10 +4165,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753752</v>
+        <v>753746</v>
       </c>
       <c r="R35" t="n">
-        <v>7217944</v>
+        <v>7217930</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4191,6 +4201,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4217,10 +4232,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125023438</v>
+        <v>125023411</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4233,21 +4248,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4257,10 +4272,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753612</v>
+        <v>753557</v>
       </c>
       <c r="R36" t="n">
-        <v>7217703</v>
+        <v>7217895</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4293,11 +4308,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4324,10 +4334,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125023434</v>
+        <v>125023321</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>91166</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4340,42 +4350,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753797</v>
+        <v>753679</v>
       </c>
       <c r="R37" t="n">
-        <v>7217988</v>
+        <v>7218005</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4408,11 +4410,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4442,7 +4439,7 @@
         <v>125023324</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4541,10 +4538,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125023336</v>
+        <v>125023367</v>
       </c>
       <c r="B39" t="n">
-        <v>90962</v>
+        <v>80028</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4557,21 +4554,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4581,10 +4578,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753566</v>
+        <v>753786</v>
       </c>
       <c r="R39" t="n">
-        <v>7217862</v>
+        <v>7217962</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4643,10 +4640,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125023446</v>
+        <v>125023352</v>
       </c>
       <c r="B40" t="n">
-        <v>91221</v>
+        <v>80028</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4655,25 +4652,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1106</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4683,10 +4680,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753567</v>
+        <v>753763</v>
       </c>
       <c r="R40" t="n">
-        <v>7217721</v>
+        <v>7217831</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4727,7 +4724,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4746,10 +4742,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125023398</v>
+        <v>125023347</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>80028</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4762,41 +4758,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753778</v>
+        <v>753850</v>
       </c>
       <c r="R41" t="n">
-        <v>7217858</v>
+        <v>7217843</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4831,18 +4820,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4861,10 +4844,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125023319</v>
+        <v>125023338</v>
       </c>
       <c r="B42" t="n">
-        <v>90977</v>
+        <v>8720</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4873,25 +4856,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>100798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Smal trollknäppare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Danosoma conspersum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyllenhal, 1808)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4901,10 +4884,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753506</v>
+        <v>753699</v>
       </c>
       <c r="R42" t="n">
-        <v>7217904</v>
+        <v>7217618</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4945,6 +4928,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4963,10 +4947,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125023420</v>
+        <v>125023438</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4979,21 +4963,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5003,10 +4987,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753559</v>
+        <v>753612</v>
       </c>
       <c r="R43" t="n">
-        <v>7217734</v>
+        <v>7217703</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5039,6 +5023,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5065,10 +5054,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125023348</v>
+        <v>125023325</v>
       </c>
       <c r="B44" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5081,34 +5070,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753817</v>
+        <v>753575</v>
       </c>
       <c r="R44" t="n">
-        <v>7217853</v>
+        <v>7217959</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5141,6 +5138,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5167,10 +5169,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125023423</v>
+        <v>125023389</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5179,25 +5181,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5207,10 +5209,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753610</v>
+        <v>753729</v>
       </c>
       <c r="R45" t="n">
-        <v>7217727</v>
+        <v>7218042</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5269,10 +5271,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125023391</v>
+        <v>125023395</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>91184</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5281,25 +5283,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5309,10 +5311,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753706</v>
+        <v>753472</v>
       </c>
       <c r="R46" t="n">
-        <v>7218039</v>
+        <v>7218031</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5371,10 +5373,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125023388</v>
+        <v>125023319</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>91131</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5383,25 +5385,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5411,10 +5413,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753742</v>
+        <v>753506</v>
       </c>
       <c r="R47" t="n">
-        <v>7217924</v>
+        <v>7217904</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5473,10 +5475,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125023390</v>
+        <v>125023378</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5485,25 +5487,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5513,10 +5515,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753701</v>
+        <v>753722</v>
       </c>
       <c r="R48" t="n">
-        <v>7218031</v>
+        <v>7218033</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5575,10 +5577,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125023444</v>
+        <v>125023419</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5591,21 +5593,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5615,10 +5617,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753746</v>
+        <v>753550</v>
       </c>
       <c r="R49" t="n">
-        <v>7217930</v>
+        <v>7217725</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5651,11 +5653,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5682,10 +5679,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125023359</v>
+        <v>125023374</v>
       </c>
       <c r="B50" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5722,10 +5719,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753753</v>
+        <v>753763</v>
       </c>
       <c r="R50" t="n">
-        <v>7217910</v>
+        <v>7218015</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5784,10 +5781,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125023334</v>
+        <v>125023445</v>
       </c>
       <c r="B51" t="n">
-        <v>79920</v>
+        <v>57635</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5796,25 +5793,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5824,10 +5821,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753752</v>
+        <v>753715</v>
       </c>
       <c r="R51" t="n">
-        <v>7217919</v>
+        <v>7218026</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5860,6 +5857,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5886,10 +5888,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125023378</v>
+        <v>125023426</v>
       </c>
       <c r="B52" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5902,21 +5904,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5926,10 +5928,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>753722</v>
+        <v>753597</v>
       </c>
       <c r="R52" t="n">
-        <v>7218033</v>
+        <v>7217728</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5988,10 +5990,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125023411</v>
+        <v>125023399</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6028,10 +6030,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>753557</v>
+        <v>753751</v>
       </c>
       <c r="R53" t="n">
-        <v>7217895</v>
+        <v>7217806</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6090,10 +6092,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125023375</v>
+        <v>125023350</v>
       </c>
       <c r="B54" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6130,10 +6132,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753750</v>
+        <v>753789</v>
       </c>
       <c r="R54" t="n">
-        <v>7218028</v>
+        <v>7217812</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6192,10 +6194,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125023354</v>
+        <v>125023412</v>
       </c>
       <c r="B55" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6208,21 +6210,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6232,10 +6234,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753773</v>
+        <v>753568</v>
       </c>
       <c r="R55" t="n">
-        <v>7217842</v>
+        <v>7217875</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6294,10 +6296,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125023439</v>
+        <v>125023351</v>
       </c>
       <c r="B56" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6310,21 +6312,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6334,10 +6336,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753568</v>
+        <v>753758</v>
       </c>
       <c r="R56" t="n">
-        <v>7217716</v>
+        <v>7217819</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6370,11 +6372,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6401,10 +6398,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125023389</v>
+        <v>125023421</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6413,25 +6410,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6441,10 +6438,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753729</v>
+        <v>753573</v>
       </c>
       <c r="R57" t="n">
-        <v>7218042</v>
+        <v>7217745</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6503,10 +6500,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125023426</v>
+        <v>125023334</v>
       </c>
       <c r="B58" t="n">
-        <v>78810</v>
+        <v>80057</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6515,25 +6512,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6543,10 +6540,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753597</v>
+        <v>753752</v>
       </c>
       <c r="R58" t="n">
-        <v>7217728</v>
+        <v>7217919</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6605,10 +6602,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125023381</v>
+        <v>125023315</v>
       </c>
       <c r="B59" t="n">
-        <v>79927</v>
+        <v>57635</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6617,25 +6614,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6645,10 +6642,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753722</v>
+        <v>753491</v>
       </c>
       <c r="R59" t="n">
-        <v>7218033</v>
+        <v>7217766</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6681,6 +6678,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6707,10 +6709,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125023421</v>
+        <v>125023413</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6747,10 +6749,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753573</v>
+        <v>753517</v>
       </c>
       <c r="R60" t="n">
-        <v>7217745</v>
+        <v>7217918</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6809,10 +6811,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125023321</v>
+        <v>125023362</v>
       </c>
       <c r="B61" t="n">
-        <v>91012</v>
+        <v>80028</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6825,21 +6827,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6849,10 +6851,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753679</v>
+        <v>753752</v>
       </c>
       <c r="R61" t="n">
-        <v>7218005</v>
+        <v>7217944</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6911,10 +6913,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125023373</v>
+        <v>125023430</v>
       </c>
       <c r="B62" t="n">
-        <v>79891</v>
+        <v>80063</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6923,25 +6925,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6951,10 +6953,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753768</v>
+        <v>753789</v>
       </c>
       <c r="R62" t="n">
-        <v>7218016</v>
+        <v>7217809</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7013,10 +7015,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125023347</v>
+        <v>125023368</v>
       </c>
       <c r="B63" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7053,10 +7055,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753850</v>
+        <v>753808</v>
       </c>
       <c r="R63" t="n">
-        <v>7217843</v>
+        <v>7217964</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7115,10 +7117,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125023315</v>
+        <v>125023342</v>
       </c>
       <c r="B64" t="n">
-        <v>57513</v>
+        <v>78684</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7131,21 +7133,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7155,10 +7157,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753491</v>
+        <v>753722</v>
       </c>
       <c r="R64" t="n">
-        <v>7217766</v>
+        <v>7217596</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7193,17 +7195,13 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7222,10 +7220,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125023412</v>
+        <v>125023323</v>
       </c>
       <c r="B65" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7238,21 +7236,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7262,10 +7260,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753568</v>
+        <v>753504</v>
       </c>
       <c r="R65" t="n">
-        <v>7217875</v>
+        <v>7217889</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7324,10 +7322,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125023403</v>
+        <v>125023335</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>80057</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7336,25 +7334,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7364,10 +7362,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753762</v>
+        <v>753790</v>
       </c>
       <c r="R66" t="n">
-        <v>7218015</v>
+        <v>7217992</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7426,10 +7424,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125023327</v>
+        <v>125023369</v>
       </c>
       <c r="B67" t="n">
-        <v>57666</v>
+        <v>80028</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7442,21 +7440,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7466,10 +7464,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753740</v>
+        <v>753797</v>
       </c>
       <c r="R67" t="n">
-        <v>7217891</v>
+        <v>7218005</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7528,10 +7526,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125023399</v>
+        <v>125023407</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7568,10 +7566,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753751</v>
+        <v>753671</v>
       </c>
       <c r="R68" t="n">
-        <v>7217806</v>
+        <v>7218008</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7633,7 +7631,7 @@
         <v>125023341</v>
       </c>
       <c r="B69" t="n">
-        <v>79919</v>
+        <v>80056</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7735,7 +7733,7 @@
         <v>125023345</v>
       </c>
       <c r="B70" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7834,10 +7832,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125023419</v>
+        <v>125023328</v>
       </c>
       <c r="B71" t="n">
-        <v>78810</v>
+        <v>57793</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7850,21 +7848,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7874,10 +7872,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753550</v>
+        <v>753742</v>
       </c>
       <c r="R71" t="n">
-        <v>7217725</v>
+        <v>7217926</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7936,10 +7934,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125023367</v>
+        <v>125023330</v>
       </c>
       <c r="B72" t="n">
-        <v>79891</v>
+        <v>57793</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7952,21 +7950,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7976,10 +7974,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753786</v>
+        <v>753730</v>
       </c>
       <c r="R72" t="n">
-        <v>7217962</v>
+        <v>7217943</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8038,10 +8036,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125023357</v>
+        <v>125023435</v>
       </c>
       <c r="B73" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8054,34 +8052,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>753793</v>
+        <v>753562</v>
       </c>
       <c r="R73" t="n">
-        <v>7217856</v>
+        <v>7217727</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8114,6 +8120,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8140,10 +8151,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125023413</v>
+        <v>125023439</v>
       </c>
       <c r="B74" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8156,21 +8167,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8180,10 +8191,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>753517</v>
+        <v>753568</v>
       </c>
       <c r="R74" t="n">
-        <v>7217918</v>
+        <v>7217716</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8216,6 +8227,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8242,10 +8258,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125023372</v>
+        <v>125023443</v>
       </c>
       <c r="B75" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8258,21 +8274,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8282,10 +8298,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>753790</v>
+        <v>753575</v>
       </c>
       <c r="R75" t="n">
-        <v>7217992</v>
+        <v>7217751</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8318,6 +8334,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8344,10 +8365,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125023430</v>
+        <v>125023320</v>
       </c>
       <c r="B76" t="n">
-        <v>79926</v>
+        <v>91166</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8356,25 +8377,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8384,10 +8405,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>753789</v>
+        <v>753687</v>
       </c>
       <c r="R76" t="n">
-        <v>7217809</v>
+        <v>7217999</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8446,10 +8467,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125023417</v>
+        <v>125023336</v>
       </c>
       <c r="B77" t="n">
-        <v>78810</v>
+        <v>91116</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8462,21 +8483,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8486,10 +8507,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>753474</v>
+        <v>753566</v>
       </c>
       <c r="R77" t="n">
-        <v>7218026</v>
+        <v>7217862</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8548,10 +8569,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125023326</v>
+        <v>125023318</v>
       </c>
       <c r="B78" t="n">
-        <v>57513</v>
+        <v>91131</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8560,46 +8581,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>753598</v>
+        <v>753680</v>
       </c>
       <c r="R78" t="n">
-        <v>7217744</v>
+        <v>7218004</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8632,11 +8645,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8663,10 +8671,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125023402</v>
+        <v>125023394</v>
       </c>
       <c r="B79" t="n">
-        <v>78810</v>
+        <v>91184</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8679,21 +8687,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8703,10 +8711,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>753752</v>
+        <v>753596</v>
       </c>
       <c r="R79" t="n">
-        <v>7217878</v>
+        <v>7217939</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8765,10 +8773,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125023343</v>
+        <v>125023420</v>
       </c>
       <c r="B80" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8781,21 +8789,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8805,10 +8813,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>753760</v>
+        <v>753559</v>
       </c>
       <c r="R80" t="n">
-        <v>7218023</v>
+        <v>7217734</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8843,18 +8851,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8873,10 +8875,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125023320</v>
+        <v>125023381</v>
       </c>
       <c r="B81" t="n">
-        <v>91012</v>
+        <v>80064</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8885,25 +8887,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8913,10 +8915,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>753687</v>
+        <v>753722</v>
       </c>
       <c r="R81" t="n">
-        <v>7217999</v>
+        <v>7218033</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8975,10 +8977,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125023395</v>
+        <v>125023429</v>
       </c>
       <c r="B82" t="n">
-        <v>91030</v>
+        <v>80063</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8987,25 +8989,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9015,10 +9017,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>753472</v>
+        <v>753792</v>
       </c>
       <c r="R82" t="n">
-        <v>7218031</v>
+        <v>7217798</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9077,10 +9079,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125023442</v>
+        <v>125023398</v>
       </c>
       <c r="B83" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9093,34 +9095,41 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>753726</v>
+        <v>753778</v>
       </c>
       <c r="R83" t="n">
-        <v>7218039</v>
+        <v>7217858</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9157,7 +9166,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Barksprätt</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9166,6 +9175,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9184,10 +9194,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125023330</v>
+        <v>125023417</v>
       </c>
       <c r="B84" t="n">
-        <v>57666</v>
+        <v>78947</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9200,21 +9210,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9224,10 +9234,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>753730</v>
+        <v>753474</v>
       </c>
       <c r="R84" t="n">
-        <v>7217943</v>
+        <v>7218026</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9286,10 +9296,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125023333</v>
+        <v>125023327</v>
       </c>
       <c r="B85" t="n">
-        <v>57666</v>
+        <v>57793</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9326,10 +9336,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>753781</v>
+        <v>753740</v>
       </c>
       <c r="R85" t="n">
-        <v>7217902</v>
+        <v>7217891</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9388,10 +9398,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125023441</v>
+        <v>125023359</v>
       </c>
       <c r="B86" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9404,21 +9414,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9428,10 +9438,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>753798</v>
+        <v>753753</v>
       </c>
       <c r="R86" t="n">
-        <v>7217948</v>
+        <v>7217910</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9464,11 +9474,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9495,10 +9500,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125023369</v>
+        <v>125023337</v>
       </c>
       <c r="B87" t="n">
-        <v>79891</v>
+        <v>79932</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9507,25 +9512,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9535,10 +9540,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>753797</v>
+        <v>753523</v>
       </c>
       <c r="R87" t="n">
-        <v>7218005</v>
+        <v>7218086</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9597,10 +9602,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125023323</v>
+        <v>125023392</v>
       </c>
       <c r="B88" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9609,25 +9614,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9637,10 +9642,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>753504</v>
+        <v>753718</v>
       </c>
       <c r="R88" t="n">
-        <v>7217889</v>
+        <v>7218035</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9699,10 +9704,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125023365</v>
+        <v>125023431</v>
       </c>
       <c r="B89" t="n">
-        <v>79891</v>
+        <v>80063</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9711,25 +9716,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9739,10 +9744,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>753784</v>
+        <v>753774</v>
       </c>
       <c r="R89" t="n">
-        <v>7217948</v>
+        <v>7217939</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9801,10 +9806,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125023396</v>
+        <v>125023358</v>
       </c>
       <c r="B90" t="n">
-        <v>78810</v>
+        <v>80028</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9817,41 +9822,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>753626</v>
+        <v>753758</v>
       </c>
       <c r="R90" t="n">
-        <v>7218004</v>
+        <v>7217900</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9886,18 +9884,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9916,10 +9908,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125023387</v>
+        <v>125023348</v>
       </c>
       <c r="B91" t="n">
-        <v>78546</v>
+        <v>80028</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9932,21 +9924,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9956,10 +9948,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>753816</v>
+        <v>753817</v>
       </c>
       <c r="R91" t="n">
-        <v>7217838</v>
+        <v>7217853</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10018,10 +10010,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125023445</v>
+        <v>125023375</v>
       </c>
       <c r="B92" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10034,21 +10026,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10058,10 +10050,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>753715</v>
+        <v>753750</v>
       </c>
       <c r="R92" t="n">
-        <v>7218026</v>
+        <v>7218028</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10094,11 +10086,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10125,10 +10112,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125023318</v>
+        <v>125023409</v>
       </c>
       <c r="B93" t="n">
-        <v>90977</v>
+        <v>78947</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10137,25 +10124,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10165,10 +10152,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>753680</v>
+        <v>753562</v>
       </c>
       <c r="R93" t="n">
-        <v>7218004</v>
+        <v>7217917</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10227,10 +10214,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125023418</v>
+        <v>125023363</v>
       </c>
       <c r="B94" t="n">
-        <v>78810</v>
+        <v>80028</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10243,21 +10230,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10267,10 +10254,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>753406</v>
+        <v>753782</v>
       </c>
       <c r="R94" t="n">
-        <v>7217999</v>
+        <v>7217946</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10329,10 +10316,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125023358</v>
+        <v>125023404</v>
       </c>
       <c r="B95" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10345,21 +10332,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10369,10 +10356,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>753758</v>
+        <v>753743</v>
       </c>
       <c r="R95" t="n">
-        <v>7217900</v>
+        <v>7218044</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10431,10 +10418,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125023409</v>
+        <v>125023326</v>
       </c>
       <c r="B96" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10447,34 +10434,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>753562</v>
+        <v>753598</v>
       </c>
       <c r="R96" t="n">
-        <v>7217917</v>
+        <v>7217744</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10507,6 +10502,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10536,7 +10536,7 @@
         <v>125023317</v>
       </c>
       <c r="B97" t="n">
-        <v>78842</v>
+        <v>78979</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>125023383</v>
       </c>
       <c r="B98" t="n">
-        <v>91410</v>
+        <v>91570</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>125023339</v>
       </c>
       <c r="B99" t="n">
-        <v>92285</v>
+        <v>92440</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125023442</v>
+        <v>125023365</v>
       </c>
       <c r="B16" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,21 +2179,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753726</v>
+        <v>753784</v>
       </c>
       <c r="R16" t="n">
-        <v>7218039</v>
+        <v>7217948</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,11 +2239,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125023406</v>
+        <v>125023354</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753718</v>
+        <v>753773</v>
       </c>
       <c r="R17" t="n">
-        <v>7218042</v>
+        <v>7217842</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2367,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125023365</v>
+        <v>125023366</v>
       </c>
       <c r="B18" t="n">
         <v>80028</v>
@@ -2412,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753784</v>
+        <v>753778</v>
       </c>
       <c r="R18" t="n">
-        <v>7217948</v>
+        <v>7217945</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2474,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125023354</v>
+        <v>125023442</v>
       </c>
       <c r="B19" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2490,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2514,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753773</v>
+        <v>753726</v>
       </c>
       <c r="R19" t="n">
-        <v>7217842</v>
+        <v>7218039</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,6 +2545,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125023366</v>
+        <v>125023406</v>
       </c>
       <c r="B20" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2592,21 +2592,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753778</v>
+        <v>753718</v>
       </c>
       <c r="R20" t="n">
-        <v>7217945</v>
+        <v>7218042</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3921,10 +3921,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125023401</v>
+        <v>125023321</v>
       </c>
       <c r="B33" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3937,21 +3937,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753780</v>
+        <v>753679</v>
       </c>
       <c r="R33" t="n">
-        <v>7217865</v>
+        <v>7218005</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4023,7 +4023,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125023403</v>
+        <v>125023411</v>
       </c>
       <c r="B34" t="n">
         <v>78947</v>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753762</v>
+        <v>753557</v>
       </c>
       <c r="R34" t="n">
-        <v>7218015</v>
+        <v>7217895</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4125,10 +4125,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125023444</v>
+        <v>125023401</v>
       </c>
       <c r="B35" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4141,21 +4141,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753746</v>
+        <v>753780</v>
       </c>
       <c r="R35" t="n">
-        <v>7217930</v>
+        <v>7217865</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4201,11 +4201,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4232,7 +4227,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125023411</v>
+        <v>125023403</v>
       </c>
       <c r="B36" t="n">
         <v>78947</v>
@@ -4272,10 +4267,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753557</v>
+        <v>753762</v>
       </c>
       <c r="R36" t="n">
-        <v>7217895</v>
+        <v>7218015</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4334,10 +4329,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125023321</v>
+        <v>125023444</v>
       </c>
       <c r="B37" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4350,21 +4345,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4374,10 +4369,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753679</v>
+        <v>753746</v>
       </c>
       <c r="R37" t="n">
-        <v>7218005</v>
+        <v>7217930</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4410,6 +4405,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4844,10 +4844,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125023338</v>
+        <v>125023438</v>
       </c>
       <c r="B42" t="n">
-        <v>8720</v>
+        <v>57635</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4856,25 +4856,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100798</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smal trollknäppare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Danosoma conspersum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753699</v>
+        <v>753612</v>
       </c>
       <c r="R42" t="n">
-        <v>7217618</v>
+        <v>7217703</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4922,13 +4922,17 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4947,7 +4951,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125023438</v>
+        <v>125023325</v>
       </c>
       <c r="B43" t="n">
         <v>57635</v>
@@ -4981,16 +4985,24 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753612</v>
+        <v>753575</v>
       </c>
       <c r="R43" t="n">
-        <v>7217703</v>
+        <v>7217959</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5027,7 +5039,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Barksprätt</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5054,10 +5066,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125023325</v>
+        <v>125023338</v>
       </c>
       <c r="B44" t="n">
-        <v>57635</v>
+        <v>8720</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5066,46 +5078,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>100798</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smal trollknäppare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Danosoma conspersum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyllenhal, 1808)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753575</v>
+        <v>753699</v>
       </c>
       <c r="R44" t="n">
-        <v>7217959</v>
+        <v>7217618</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5140,17 +5144,13 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6709,10 +6709,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125023413</v>
+        <v>125023342</v>
       </c>
       <c r="B60" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6725,21 +6725,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753517</v>
+        <v>753722</v>
       </c>
       <c r="R60" t="n">
-        <v>7217918</v>
+        <v>7217596</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6793,6 +6793,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6811,10 +6812,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125023362</v>
+        <v>125023413</v>
       </c>
       <c r="B61" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6827,21 +6828,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6851,10 +6852,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753752</v>
+        <v>753517</v>
       </c>
       <c r="R61" t="n">
-        <v>7217944</v>
+        <v>7217918</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6913,10 +6914,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125023430</v>
+        <v>125023362</v>
       </c>
       <c r="B62" t="n">
-        <v>80063</v>
+        <v>80028</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6925,25 +6926,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6953,10 +6954,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753789</v>
+        <v>753752</v>
       </c>
       <c r="R62" t="n">
-        <v>7217809</v>
+        <v>7217944</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7015,10 +7016,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125023368</v>
+        <v>125023430</v>
       </c>
       <c r="B63" t="n">
-        <v>80028</v>
+        <v>80063</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7027,25 +7028,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7055,10 +7056,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753808</v>
+        <v>753789</v>
       </c>
       <c r="R63" t="n">
-        <v>7217964</v>
+        <v>7217809</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7117,10 +7118,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125023342</v>
+        <v>125023368</v>
       </c>
       <c r="B64" t="n">
-        <v>78684</v>
+        <v>80028</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7133,21 +7134,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7157,10 +7158,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753722</v>
+        <v>753808</v>
       </c>
       <c r="R64" t="n">
-        <v>7217596</v>
+        <v>7217964</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7201,7 +7202,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7628,10 +7628,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125023341</v>
+        <v>125023328</v>
       </c>
       <c r="B69" t="n">
-        <v>80056</v>
+        <v>57793</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7640,25 +7640,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753654</v>
+        <v>753742</v>
       </c>
       <c r="R69" t="n">
-        <v>7218008</v>
+        <v>7217926</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7730,10 +7730,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125023345</v>
+        <v>125023330</v>
       </c>
       <c r="B70" t="n">
-        <v>80028</v>
+        <v>57793</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7746,21 +7746,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753790</v>
+        <v>753730</v>
       </c>
       <c r="R70" t="n">
-        <v>7217981</v>
+        <v>7217943</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7832,10 +7832,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125023328</v>
+        <v>125023341</v>
       </c>
       <c r="B71" t="n">
-        <v>57793</v>
+        <v>80056</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7844,25 +7844,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753742</v>
+        <v>753654</v>
       </c>
       <c r="R71" t="n">
-        <v>7217926</v>
+        <v>7218008</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7934,10 +7934,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125023330</v>
+        <v>125023345</v>
       </c>
       <c r="B72" t="n">
-        <v>57793</v>
+        <v>80028</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7950,21 +7950,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753730</v>
+        <v>753790</v>
       </c>
       <c r="R72" t="n">
-        <v>7217943</v>
+        <v>7217981</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9602,10 +9602,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125023392</v>
+        <v>125023431</v>
       </c>
       <c r="B88" t="n">
-        <v>98269</v>
+        <v>80063</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9614,25 +9614,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>753718</v>
+        <v>753774</v>
       </c>
       <c r="R88" t="n">
-        <v>7218035</v>
+        <v>7217939</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9704,10 +9704,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125023431</v>
+        <v>125023358</v>
       </c>
       <c r="B89" t="n">
-        <v>80063</v>
+        <v>80028</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9716,25 +9716,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9744,10 +9744,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>753774</v>
+        <v>753758</v>
       </c>
       <c r="R89" t="n">
-        <v>7217939</v>
+        <v>7217900</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9806,7 +9806,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125023358</v>
+        <v>125023348</v>
       </c>
       <c r="B90" t="n">
         <v>80028</v>
@@ -9846,10 +9846,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>753758</v>
+        <v>753817</v>
       </c>
       <c r="R90" t="n">
-        <v>7217900</v>
+        <v>7217853</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9908,7 +9908,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125023348</v>
+        <v>125023375</v>
       </c>
       <c r="B91" t="n">
         <v>80028</v>
@@ -9948,10 +9948,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>753817</v>
+        <v>753750</v>
       </c>
       <c r="R91" t="n">
-        <v>7217853</v>
+        <v>7218028</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10010,10 +10010,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125023375</v>
+        <v>125023392</v>
       </c>
       <c r="B92" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10022,25 +10022,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10050,10 +10050,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>753750</v>
+        <v>753718</v>
       </c>
       <c r="R92" t="n">
-        <v>7218028</v>
+        <v>7218035</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125023441</v>
+        <v>125023417</v>
       </c>
       <c r="B4" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753798</v>
+        <v>753474</v>
       </c>
       <c r="R4" t="n">
-        <v>7217948</v>
+        <v>7218026</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,11 +983,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125023402</v>
+        <v>125023378</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,21 +1025,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753752</v>
+        <v>753722</v>
       </c>
       <c r="R5" t="n">
-        <v>7217878</v>
+        <v>7218033</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125023414</v>
+        <v>125023362</v>
       </c>
       <c r="B6" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,21 +1127,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1156,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753630</v>
+        <v>753752</v>
       </c>
       <c r="R6" t="n">
-        <v>7218006</v>
+        <v>7217944</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125023388</v>
+        <v>125023326</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,38 +1225,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>753742</v>
+        <v>753598</v>
       </c>
       <c r="R7" t="n">
-        <v>7217924</v>
+        <v>7217744</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,6 +1297,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125023333</v>
+        <v>125023363</v>
       </c>
       <c r="B8" t="n">
-        <v>57793</v>
+        <v>80028</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,21 +1344,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1360,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>753781</v>
+        <v>753782</v>
       </c>
       <c r="R8" t="n">
-        <v>7217902</v>
+        <v>7217946</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125023355</v>
+        <v>125023413</v>
       </c>
       <c r="B9" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1446,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>753792</v>
+        <v>753517</v>
       </c>
       <c r="R9" t="n">
-        <v>7217850</v>
+        <v>7217918</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125023434</v>
+        <v>125023396</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,29 +1548,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>bobygge</t>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1572,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>753797</v>
+        <v>753626</v>
       </c>
       <c r="R10" t="n">
-        <v>7217988</v>
+        <v>7218004</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,7 +1619,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1621,6 +1628,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1639,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125023380</v>
+        <v>125023441</v>
       </c>
       <c r="B11" t="n">
-        <v>80064</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1659,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>753769</v>
+        <v>753798</v>
       </c>
       <c r="R11" t="n">
-        <v>7218019</v>
+        <v>7217948</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,6 +1723,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,10 +1754,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023373</v>
+        <v>125023403</v>
       </c>
       <c r="B12" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,21 +1770,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>753768</v>
+        <v>753762</v>
       </c>
       <c r="R12" t="n">
-        <v>7218016</v>
+        <v>7218015</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125023372</v>
+        <v>125023320</v>
       </c>
       <c r="B13" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,21 +1872,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753790</v>
+        <v>753687</v>
       </c>
       <c r="R13" t="n">
-        <v>7217992</v>
+        <v>7217999</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125023396</v>
+        <v>125023372</v>
       </c>
       <c r="B14" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1961,41 +1974,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753626</v>
+        <v>753790</v>
       </c>
       <c r="R14" t="n">
-        <v>7218004</v>
+        <v>7217992</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,18 +2036,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125023446</v>
+        <v>125023335</v>
       </c>
       <c r="B15" t="n">
-        <v>91375</v>
+        <v>80057</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,25 +2072,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1106</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>753567</v>
+        <v>753790</v>
       </c>
       <c r="R15" t="n">
-        <v>7217721</v>
+        <v>7217992</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2144,7 +2144,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2163,7 +2162,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125023365</v>
+        <v>125023345</v>
       </c>
       <c r="B16" t="n">
         <v>80028</v>
@@ -2203,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753784</v>
+        <v>753790</v>
       </c>
       <c r="R16" t="n">
-        <v>7217948</v>
+        <v>7217981</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125023354</v>
+        <v>125023389</v>
       </c>
       <c r="B17" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2276,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753773</v>
+        <v>753729</v>
       </c>
       <c r="R17" t="n">
-        <v>7217842</v>
+        <v>7218042</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2366,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125023366</v>
+        <v>125023429</v>
       </c>
       <c r="B18" t="n">
-        <v>80028</v>
+        <v>80063</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2379,25 +2378,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753778</v>
+        <v>753792</v>
       </c>
       <c r="R18" t="n">
-        <v>7217945</v>
+        <v>7217798</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,10 +2468,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125023442</v>
+        <v>125023390</v>
       </c>
       <c r="B19" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2481,25 +2480,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2508,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753726</v>
+        <v>753701</v>
       </c>
       <c r="R19" t="n">
-        <v>7218039</v>
+        <v>7218031</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,11 +2544,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,10 +2570,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125023406</v>
+        <v>125023392</v>
       </c>
       <c r="B20" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2588,25 +2582,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2619,7 +2613,7 @@
         <v>753718</v>
       </c>
       <c r="R20" t="n">
-        <v>7218042</v>
+        <v>7218035</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,10 +2672,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125023405</v>
+        <v>125023341</v>
       </c>
       <c r="B21" t="n">
-        <v>78947</v>
+        <v>80056</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2690,25 +2684,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2718,10 +2712,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753748</v>
+        <v>753654</v>
       </c>
       <c r="R21" t="n">
-        <v>7218047</v>
+        <v>7218008</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,10 +2774,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125023416</v>
+        <v>125023349</v>
       </c>
       <c r="B22" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2796,21 +2790,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2814,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753470</v>
+        <v>753795</v>
       </c>
       <c r="R22" t="n">
-        <v>7218024</v>
+        <v>7217800</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2882,10 +2876,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125023432</v>
+        <v>125023374</v>
       </c>
       <c r="B23" t="n">
-        <v>80063</v>
+        <v>80028</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2894,25 +2888,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2922,10 +2916,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753769</v>
+        <v>753763</v>
       </c>
       <c r="R23" t="n">
-        <v>7218019</v>
+        <v>7218015</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,10 +2978,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125023357</v>
+        <v>125023380</v>
       </c>
       <c r="B24" t="n">
-        <v>80028</v>
+        <v>80064</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2996,25 +2990,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3024,10 +3018,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753793</v>
+        <v>753769</v>
       </c>
       <c r="R24" t="n">
-        <v>7217856</v>
+        <v>7218019</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3086,10 +3080,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125023387</v>
+        <v>125023343</v>
       </c>
       <c r="B25" t="n">
-        <v>78683</v>
+        <v>80028</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3102,21 +3096,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3126,10 +3120,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753816</v>
+        <v>753760</v>
       </c>
       <c r="R25" t="n">
-        <v>7217838</v>
+        <v>7218023</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3164,12 +3158,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125023423</v>
+        <v>125023342</v>
       </c>
       <c r="B26" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753610</v>
+        <v>753722</v>
       </c>
       <c r="R26" t="n">
-        <v>7217727</v>
+        <v>7217596</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3272,6 +3272,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3290,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125023343</v>
+        <v>125023323</v>
       </c>
       <c r="B27" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3306,21 +3307,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3330,10 +3331,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753760</v>
+        <v>753504</v>
       </c>
       <c r="R27" t="n">
-        <v>7218023</v>
+        <v>7217889</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3368,18 +3369,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3398,10 +3393,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125023349</v>
+        <v>125023446</v>
       </c>
       <c r="B28" t="n">
-        <v>80028</v>
+        <v>91375</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3410,25 +3405,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1106</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3438,10 +3433,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753795</v>
+        <v>753567</v>
       </c>
       <c r="R28" t="n">
-        <v>7217800</v>
+        <v>7217721</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3482,6 +3477,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3500,10 +3496,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125023391</v>
+        <v>125023354</v>
       </c>
       <c r="B29" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3512,25 +3508,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3540,10 +3536,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753706</v>
+        <v>753773</v>
       </c>
       <c r="R29" t="n">
-        <v>7218039</v>
+        <v>7217842</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,10 +3598,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125023390</v>
+        <v>125023430</v>
       </c>
       <c r="B30" t="n">
-        <v>98269</v>
+        <v>80063</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3614,25 +3610,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3642,10 +3638,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753701</v>
+        <v>753789</v>
       </c>
       <c r="R30" t="n">
-        <v>7218031</v>
+        <v>7217809</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3704,10 +3700,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125023418</v>
+        <v>125023366</v>
       </c>
       <c r="B31" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3720,21 +3716,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3744,10 +3740,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753406</v>
+        <v>753778</v>
       </c>
       <c r="R31" t="n">
-        <v>7217999</v>
+        <v>7217945</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3806,7 +3802,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125023316</v>
+        <v>125023444</v>
       </c>
       <c r="B32" t="n">
         <v>57635</v>
@@ -3840,24 +3836,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753568</v>
+        <v>753746</v>
       </c>
       <c r="R32" t="n">
-        <v>7217733</v>
+        <v>7217930</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3894,7 +3882,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre bohål</t>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3921,10 +3909,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125023321</v>
+        <v>125023443</v>
       </c>
       <c r="B33" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3937,21 +3925,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3961,10 +3949,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753679</v>
+        <v>753575</v>
       </c>
       <c r="R33" t="n">
-        <v>7218005</v>
+        <v>7217751</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3997,6 +3985,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4023,10 +4016,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125023411</v>
+        <v>125023325</v>
       </c>
       <c r="B34" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4039,34 +4032,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753557</v>
+        <v>753575</v>
       </c>
       <c r="R34" t="n">
-        <v>7217895</v>
+        <v>7217959</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4099,6 +4100,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4125,10 +4131,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125023401</v>
+        <v>125023438</v>
       </c>
       <c r="B35" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4141,21 +4147,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4165,10 +4171,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753780</v>
+        <v>753612</v>
       </c>
       <c r="R35" t="n">
-        <v>7217865</v>
+        <v>7217703</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4201,6 +4207,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4227,10 +4238,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125023403</v>
+        <v>125023328</v>
       </c>
       <c r="B36" t="n">
-        <v>78947</v>
+        <v>57793</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4243,21 +4254,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4267,10 +4278,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753762</v>
+        <v>753742</v>
       </c>
       <c r="R36" t="n">
-        <v>7218015</v>
+        <v>7217926</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4329,10 +4340,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125023444</v>
+        <v>125023351</v>
       </c>
       <c r="B37" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4345,21 +4356,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4369,10 +4380,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753746</v>
+        <v>753758</v>
       </c>
       <c r="R37" t="n">
-        <v>7217930</v>
+        <v>7217819</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4405,11 +4416,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4436,10 +4442,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125023324</v>
+        <v>125023334</v>
       </c>
       <c r="B38" t="n">
-        <v>91166</v>
+        <v>80057</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4448,25 +4454,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4476,10 +4482,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753480</v>
+        <v>753752</v>
       </c>
       <c r="R38" t="n">
-        <v>7218033</v>
+        <v>7217919</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4538,10 +4544,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125023367</v>
+        <v>125023405</v>
       </c>
       <c r="B39" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4554,21 +4560,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4578,10 +4584,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753786</v>
+        <v>753748</v>
       </c>
       <c r="R39" t="n">
-        <v>7217962</v>
+        <v>7218047</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4640,10 +4646,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125023352</v>
+        <v>125023432</v>
       </c>
       <c r="B40" t="n">
-        <v>80028</v>
+        <v>80063</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4652,25 +4658,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4680,10 +4686,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753763</v>
+        <v>753769</v>
       </c>
       <c r="R40" t="n">
-        <v>7217831</v>
+        <v>7218019</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4742,10 +4748,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125023347</v>
+        <v>125023337</v>
       </c>
       <c r="B41" t="n">
-        <v>80028</v>
+        <v>79932</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4754,25 +4760,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4782,10 +4788,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753850</v>
+        <v>753523</v>
       </c>
       <c r="R41" t="n">
-        <v>7217843</v>
+        <v>7218086</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4844,10 +4850,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125023438</v>
+        <v>125023409</v>
       </c>
       <c r="B42" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4860,21 +4866,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4884,10 +4890,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753612</v>
+        <v>753562</v>
       </c>
       <c r="R42" t="n">
-        <v>7217703</v>
+        <v>7217917</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4920,11 +4926,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4951,10 +4952,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125023325</v>
+        <v>125023423</v>
       </c>
       <c r="B43" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4967,42 +4968,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753575</v>
+        <v>753610</v>
       </c>
       <c r="R43" t="n">
-        <v>7217959</v>
+        <v>7217727</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5035,11 +5028,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5066,10 +5054,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125023338</v>
+        <v>125023367</v>
       </c>
       <c r="B44" t="n">
-        <v>8720</v>
+        <v>80028</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5078,25 +5066,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100798</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Smal trollknäppare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Danosoma conspersum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5106,10 +5094,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753699</v>
+        <v>753786</v>
       </c>
       <c r="R44" t="n">
-        <v>7217618</v>
+        <v>7217962</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5150,7 +5138,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5169,10 +5156,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125023389</v>
+        <v>125023358</v>
       </c>
       <c r="B45" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5181,25 +5168,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5209,10 +5196,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753729</v>
+        <v>753758</v>
       </c>
       <c r="R45" t="n">
-        <v>7218042</v>
+        <v>7217900</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5271,10 +5258,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125023395</v>
+        <v>125023416</v>
       </c>
       <c r="B46" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5287,21 +5274,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5311,10 +5298,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753472</v>
+        <v>753470</v>
       </c>
       <c r="R46" t="n">
-        <v>7218031</v>
+        <v>7218024</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5373,10 +5360,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125023319</v>
+        <v>125023442</v>
       </c>
       <c r="B47" t="n">
-        <v>91131</v>
+        <v>57635</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5385,25 +5372,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5413,10 +5400,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753506</v>
+        <v>753726</v>
       </c>
       <c r="R47" t="n">
-        <v>7217904</v>
+        <v>7218039</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5449,6 +5436,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5475,10 +5467,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125023378</v>
+        <v>125023445</v>
       </c>
       <c r="B48" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5491,21 +5483,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5515,10 +5507,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753722</v>
+        <v>753715</v>
       </c>
       <c r="R48" t="n">
-        <v>7218033</v>
+        <v>7218026</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5551,6 +5543,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5577,10 +5574,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125023419</v>
+        <v>125023338</v>
       </c>
       <c r="B49" t="n">
-        <v>78947</v>
+        <v>8720</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5589,25 +5586,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100798</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smal trollknäppare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Danosoma conspersum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyllenhal, 1808)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5617,10 +5614,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753550</v>
+        <v>753699</v>
       </c>
       <c r="R49" t="n">
-        <v>7217725</v>
+        <v>7217618</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5661,6 +5658,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5679,10 +5677,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125023374</v>
+        <v>125023381</v>
       </c>
       <c r="B50" t="n">
-        <v>80028</v>
+        <v>80064</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5691,25 +5689,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5719,10 +5717,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753763</v>
+        <v>753722</v>
       </c>
       <c r="R50" t="n">
-        <v>7218015</v>
+        <v>7218033</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5781,10 +5779,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125023445</v>
+        <v>125023401</v>
       </c>
       <c r="B51" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5797,21 +5795,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5821,10 +5819,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753715</v>
+        <v>753780</v>
       </c>
       <c r="R51" t="n">
-        <v>7218026</v>
+        <v>7217865</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5857,11 +5855,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5888,7 +5881,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125023426</v>
+        <v>125023420</v>
       </c>
       <c r="B52" t="n">
         <v>78947</v>
@@ -5928,10 +5921,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>753597</v>
+        <v>753559</v>
       </c>
       <c r="R52" t="n">
-        <v>7217728</v>
+        <v>7217734</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5990,7 +5983,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125023399</v>
+        <v>125023414</v>
       </c>
       <c r="B53" t="n">
         <v>78947</v>
@@ -6030,10 +6023,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>753751</v>
+        <v>753630</v>
       </c>
       <c r="R53" t="n">
-        <v>7217806</v>
+        <v>7218006</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6092,10 +6085,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125023350</v>
+        <v>125023315</v>
       </c>
       <c r="B54" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6108,21 +6101,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6132,10 +6125,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753789</v>
+        <v>753491</v>
       </c>
       <c r="R54" t="n">
-        <v>7217812</v>
+        <v>7217766</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6168,6 +6161,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6194,10 +6192,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125023412</v>
+        <v>125023431</v>
       </c>
       <c r="B55" t="n">
-        <v>78947</v>
+        <v>80063</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6206,20 +6204,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6234,10 +6232,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753568</v>
+        <v>753774</v>
       </c>
       <c r="R55" t="n">
-        <v>7217875</v>
+        <v>7217939</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6296,7 +6294,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125023351</v>
+        <v>125023355</v>
       </c>
       <c r="B56" t="n">
         <v>80028</v>
@@ -6336,10 +6334,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753758</v>
+        <v>753792</v>
       </c>
       <c r="R56" t="n">
-        <v>7217819</v>
+        <v>7217850</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6398,7 +6396,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125023421</v>
+        <v>125023398</v>
       </c>
       <c r="B57" t="n">
         <v>78947</v>
@@ -6432,16 +6430,23 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753573</v>
+        <v>753778</v>
       </c>
       <c r="R57" t="n">
-        <v>7217745</v>
+        <v>7217858</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6476,12 +6481,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6500,10 +6511,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125023334</v>
+        <v>125023321</v>
       </c>
       <c r="B58" t="n">
-        <v>80057</v>
+        <v>91166</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6512,25 +6523,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6540,10 +6551,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753752</v>
+        <v>753679</v>
       </c>
       <c r="R58" t="n">
-        <v>7217919</v>
+        <v>7218005</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6602,10 +6613,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125023315</v>
+        <v>125023324</v>
       </c>
       <c r="B59" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6618,21 +6629,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6642,10 +6653,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753491</v>
+        <v>753480</v>
       </c>
       <c r="R59" t="n">
-        <v>7217766</v>
+        <v>7218033</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6678,11 +6689,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6709,10 +6715,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125023342</v>
+        <v>125023391</v>
       </c>
       <c r="B60" t="n">
-        <v>78684</v>
+        <v>98269</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6721,25 +6727,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6749,10 +6755,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753722</v>
+        <v>753706</v>
       </c>
       <c r="R60" t="n">
-        <v>7217596</v>
+        <v>7218039</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6793,7 +6799,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6812,10 +6817,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125023413</v>
+        <v>125023434</v>
       </c>
       <c r="B61" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6828,34 +6833,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753517</v>
+        <v>753797</v>
       </c>
       <c r="R61" t="n">
-        <v>7217918</v>
+        <v>7217988</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6888,6 +6901,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6914,7 +6932,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125023362</v>
+        <v>125023373</v>
       </c>
       <c r="B62" t="n">
         <v>80028</v>
@@ -6954,10 +6972,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753752</v>
+        <v>753768</v>
       </c>
       <c r="R62" t="n">
-        <v>7217944</v>
+        <v>7218016</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7016,10 +7034,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125023430</v>
+        <v>125023368</v>
       </c>
       <c r="B63" t="n">
-        <v>80063</v>
+        <v>80028</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7028,25 +7046,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7056,10 +7074,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753789</v>
+        <v>753808</v>
       </c>
       <c r="R63" t="n">
-        <v>7217809</v>
+        <v>7217964</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7118,10 +7136,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125023368</v>
+        <v>125023404</v>
       </c>
       <c r="B64" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7134,21 +7152,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7158,10 +7176,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753808</v>
+        <v>753743</v>
       </c>
       <c r="R64" t="n">
-        <v>7217964</v>
+        <v>7218044</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7220,10 +7238,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125023323</v>
+        <v>125023348</v>
       </c>
       <c r="B65" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7236,21 +7254,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7260,10 +7278,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753504</v>
+        <v>753817</v>
       </c>
       <c r="R65" t="n">
-        <v>7217889</v>
+        <v>7217853</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7322,10 +7340,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125023335</v>
+        <v>125023418</v>
       </c>
       <c r="B66" t="n">
-        <v>80057</v>
+        <v>78947</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7334,25 +7352,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7362,10 +7380,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753790</v>
+        <v>753406</v>
       </c>
       <c r="R66" t="n">
-        <v>7217992</v>
+        <v>7217999</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7424,10 +7442,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125023369</v>
+        <v>125023407</v>
       </c>
       <c r="B67" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7440,21 +7458,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7464,10 +7482,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753797</v>
+        <v>753671</v>
       </c>
       <c r="R67" t="n">
-        <v>7218005</v>
+        <v>7218008</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7526,7 +7544,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125023407</v>
+        <v>125023419</v>
       </c>
       <c r="B68" t="n">
         <v>78947</v>
@@ -7566,10 +7584,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753671</v>
+        <v>753550</v>
       </c>
       <c r="R68" t="n">
-        <v>7218008</v>
+        <v>7217725</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7628,10 +7646,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125023328</v>
+        <v>125023387</v>
       </c>
       <c r="B69" t="n">
-        <v>57793</v>
+        <v>78683</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7644,21 +7662,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7668,10 +7686,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753742</v>
+        <v>753816</v>
       </c>
       <c r="R69" t="n">
-        <v>7217926</v>
+        <v>7217838</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7730,10 +7748,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125023330</v>
+        <v>125023347</v>
       </c>
       <c r="B70" t="n">
-        <v>57793</v>
+        <v>80028</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7746,21 +7764,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7770,10 +7788,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753730</v>
+        <v>753850</v>
       </c>
       <c r="R70" t="n">
-        <v>7217943</v>
+        <v>7217843</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7832,10 +7850,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125023341</v>
+        <v>125023411</v>
       </c>
       <c r="B71" t="n">
-        <v>80056</v>
+        <v>78947</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7844,25 +7862,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7872,10 +7890,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753654</v>
+        <v>753557</v>
       </c>
       <c r="R71" t="n">
-        <v>7218008</v>
+        <v>7217895</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7934,10 +7952,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125023345</v>
+        <v>125023330</v>
       </c>
       <c r="B72" t="n">
-        <v>80028</v>
+        <v>57793</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7950,21 +7968,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7974,10 +7992,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753790</v>
+        <v>753730</v>
       </c>
       <c r="R72" t="n">
-        <v>7217981</v>
+        <v>7217943</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8036,7 +8054,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125023435</v>
+        <v>125023316</v>
       </c>
       <c r="B73" t="n">
         <v>57635</v>
@@ -8074,7 +8092,7 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -8084,10 +8102,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>753562</v>
+        <v>753568</v>
       </c>
       <c r="R73" t="n">
-        <v>7217727</v>
+        <v>7217733</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8124,7 +8142,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färsk bohål</t>
+          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8151,10 +8169,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125023439</v>
+        <v>125023336</v>
       </c>
       <c r="B74" t="n">
-        <v>57635</v>
+        <v>91116</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8167,21 +8185,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8191,10 +8209,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>753568</v>
+        <v>753566</v>
       </c>
       <c r="R74" t="n">
-        <v>7217716</v>
+        <v>7217862</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8227,11 +8245,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8258,10 +8271,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125023443</v>
+        <v>125023357</v>
       </c>
       <c r="B75" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8274,21 +8287,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8298,10 +8311,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>753575</v>
+        <v>753793</v>
       </c>
       <c r="R75" t="n">
-        <v>7217751</v>
+        <v>7217856</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8334,11 +8347,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8365,10 +8373,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125023320</v>
+        <v>125023365</v>
       </c>
       <c r="B76" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8381,21 +8389,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8405,10 +8413,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>753687</v>
+        <v>753784</v>
       </c>
       <c r="R76" t="n">
-        <v>7217999</v>
+        <v>7217948</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8467,10 +8475,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125023336</v>
+        <v>125023369</v>
       </c>
       <c r="B77" t="n">
-        <v>91116</v>
+        <v>80028</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8483,21 +8491,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8507,10 +8515,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>753566</v>
+        <v>753797</v>
       </c>
       <c r="R77" t="n">
-        <v>7217862</v>
+        <v>7218005</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8569,10 +8577,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125023318</v>
+        <v>125023352</v>
       </c>
       <c r="B78" t="n">
-        <v>91131</v>
+        <v>80028</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8581,25 +8589,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8609,10 +8617,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>753680</v>
+        <v>753763</v>
       </c>
       <c r="R78" t="n">
-        <v>7218004</v>
+        <v>7217831</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8671,10 +8679,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125023394</v>
+        <v>125023318</v>
       </c>
       <c r="B79" t="n">
-        <v>91184</v>
+        <v>91131</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8683,25 +8691,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8711,10 +8719,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>753596</v>
+        <v>753680</v>
       </c>
       <c r="R79" t="n">
-        <v>7217939</v>
+        <v>7218004</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8773,10 +8781,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125023420</v>
+        <v>125023395</v>
       </c>
       <c r="B80" t="n">
-        <v>78947</v>
+        <v>91184</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8789,21 +8797,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8813,10 +8821,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>753559</v>
+        <v>753472</v>
       </c>
       <c r="R80" t="n">
-        <v>7217734</v>
+        <v>7218031</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8875,10 +8883,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125023381</v>
+        <v>125023319</v>
       </c>
       <c r="B81" t="n">
-        <v>80064</v>
+        <v>91131</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8891,21 +8899,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8915,10 +8923,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>753722</v>
+        <v>753506</v>
       </c>
       <c r="R81" t="n">
-        <v>7218033</v>
+        <v>7217904</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8977,10 +8985,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125023429</v>
+        <v>125023421</v>
       </c>
       <c r="B82" t="n">
-        <v>80063</v>
+        <v>78947</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8989,20 +8997,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9017,10 +9025,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>753792</v>
+        <v>753573</v>
       </c>
       <c r="R82" t="n">
-        <v>7217798</v>
+        <v>7217745</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9079,10 +9087,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125023398</v>
+        <v>125023333</v>
       </c>
       <c r="B83" t="n">
-        <v>78947</v>
+        <v>57793</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9095,41 +9103,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>753778</v>
+        <v>753781</v>
       </c>
       <c r="R83" t="n">
-        <v>7217858</v>
+        <v>7217902</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9164,18 +9165,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9194,10 +9189,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125023417</v>
+        <v>125023388</v>
       </c>
       <c r="B84" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9206,25 +9201,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9234,10 +9229,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>753474</v>
+        <v>753742</v>
       </c>
       <c r="R84" t="n">
-        <v>7218026</v>
+        <v>7217924</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9296,10 +9291,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125023327</v>
+        <v>125023359</v>
       </c>
       <c r="B85" t="n">
-        <v>57793</v>
+        <v>80028</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9312,21 +9307,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9336,10 +9331,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>753740</v>
+        <v>753753</v>
       </c>
       <c r="R85" t="n">
-        <v>7217891</v>
+        <v>7217910</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9398,10 +9393,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125023359</v>
+        <v>125023402</v>
       </c>
       <c r="B86" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9414,21 +9409,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9438,10 +9433,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>753753</v>
+        <v>753752</v>
       </c>
       <c r="R86" t="n">
-        <v>7217910</v>
+        <v>7217878</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9500,10 +9495,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125023337</v>
+        <v>125023426</v>
       </c>
       <c r="B87" t="n">
-        <v>79932</v>
+        <v>78947</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9512,25 +9507,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9540,10 +9535,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>753523</v>
+        <v>753597</v>
       </c>
       <c r="R87" t="n">
-        <v>7218086</v>
+        <v>7217728</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9602,10 +9597,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125023431</v>
+        <v>125023412</v>
       </c>
       <c r="B88" t="n">
-        <v>80063</v>
+        <v>78947</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9614,20 +9609,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -9642,10 +9637,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>753774</v>
+        <v>753568</v>
       </c>
       <c r="R88" t="n">
-        <v>7217939</v>
+        <v>7217875</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9704,10 +9699,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125023358</v>
+        <v>125023399</v>
       </c>
       <c r="B89" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9720,21 +9715,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9744,10 +9739,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>753758</v>
+        <v>753751</v>
       </c>
       <c r="R89" t="n">
-        <v>7217900</v>
+        <v>7217806</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9806,10 +9801,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125023348</v>
+        <v>125023435</v>
       </c>
       <c r="B90" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9822,34 +9817,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>753817</v>
+        <v>753562</v>
       </c>
       <c r="R90" t="n">
-        <v>7217853</v>
+        <v>7217727</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9882,6 +9885,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9908,10 +9916,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125023375</v>
+        <v>125023327</v>
       </c>
       <c r="B91" t="n">
-        <v>80028</v>
+        <v>57793</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9924,21 +9932,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9948,10 +9956,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>753750</v>
+        <v>753740</v>
       </c>
       <c r="R91" t="n">
-        <v>7218028</v>
+        <v>7217891</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10010,10 +10018,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125023392</v>
+        <v>125023406</v>
       </c>
       <c r="B92" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10022,25 +10030,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10053,7 +10061,7 @@
         <v>753718</v>
       </c>
       <c r="R92" t="n">
-        <v>7218035</v>
+        <v>7218042</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10112,10 +10120,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125023409</v>
+        <v>125023350</v>
       </c>
       <c r="B93" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10128,21 +10136,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10152,10 +10160,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>753562</v>
+        <v>753789</v>
       </c>
       <c r="R93" t="n">
-        <v>7217917</v>
+        <v>7217812</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10214,7 +10222,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125023363</v>
+        <v>125023375</v>
       </c>
       <c r="B94" t="n">
         <v>80028</v>
@@ -10254,10 +10262,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>753782</v>
+        <v>753750</v>
       </c>
       <c r="R94" t="n">
-        <v>7217946</v>
+        <v>7218028</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10316,10 +10324,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125023404</v>
+        <v>125023394</v>
       </c>
       <c r="B95" t="n">
-        <v>78947</v>
+        <v>91184</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10332,21 +10340,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10356,10 +10364,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>753743</v>
+        <v>753596</v>
       </c>
       <c r="R95" t="n">
-        <v>7218044</v>
+        <v>7217939</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10418,7 +10426,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125023326</v>
+        <v>125023439</v>
       </c>
       <c r="B96" t="n">
         <v>57635</v>
@@ -10452,24 +10460,16 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>753598</v>
+        <v>753568</v>
       </c>
       <c r="R96" t="n">
-        <v>7217744</v>
+        <v>7217716</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD96" t="b">

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -1754,10 +1754,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023403</v>
+        <v>125023320</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1770,21 +1770,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>753762</v>
+        <v>753687</v>
       </c>
       <c r="R12" t="n">
-        <v>7218015</v>
+        <v>7217999</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1856,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125023320</v>
+        <v>125023403</v>
       </c>
       <c r="B13" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,21 +1872,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753687</v>
+        <v>753762</v>
       </c>
       <c r="R13" t="n">
-        <v>7217999</v>
+        <v>7218015</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125023325</v>
+        <v>125023328</v>
       </c>
       <c r="B34" t="n">
-        <v>57635</v>
+        <v>57793</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4032,42 +4032,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753575</v>
+        <v>753742</v>
       </c>
       <c r="R34" t="n">
-        <v>7217959</v>
+        <v>7217926</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4100,11 +4092,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4131,10 +4118,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125023438</v>
+        <v>125023405</v>
       </c>
       <c r="B35" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4147,21 +4134,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4171,10 +4158,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753612</v>
+        <v>753748</v>
       </c>
       <c r="R35" t="n">
-        <v>7217703</v>
+        <v>7218047</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4207,11 +4194,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4238,10 +4220,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125023328</v>
+        <v>125023325</v>
       </c>
       <c r="B36" t="n">
-        <v>57793</v>
+        <v>57635</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4254,34 +4236,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753742</v>
+        <v>753575</v>
       </c>
       <c r="R36" t="n">
-        <v>7217926</v>
+        <v>7217959</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4314,6 +4304,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4340,10 +4335,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125023351</v>
+        <v>125023438</v>
       </c>
       <c r="B37" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4356,21 +4351,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4380,10 +4375,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753758</v>
+        <v>753612</v>
       </c>
       <c r="R37" t="n">
-        <v>7217819</v>
+        <v>7217703</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4416,6 +4411,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4442,10 +4442,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125023334</v>
+        <v>125023351</v>
       </c>
       <c r="B38" t="n">
-        <v>80057</v>
+        <v>80028</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4454,25 +4454,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4482,10 +4482,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753752</v>
+        <v>753758</v>
       </c>
       <c r="R38" t="n">
-        <v>7217919</v>
+        <v>7217819</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4544,10 +4544,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125023405</v>
+        <v>125023334</v>
       </c>
       <c r="B39" t="n">
-        <v>78947</v>
+        <v>80057</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4556,25 +4556,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753748</v>
+        <v>753752</v>
       </c>
       <c r="R39" t="n">
-        <v>7218047</v>
+        <v>7217919</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -6192,10 +6192,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125023431</v>
+        <v>125023398</v>
       </c>
       <c r="B55" t="n">
-        <v>80063</v>
+        <v>78947</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6204,20 +6204,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6226,16 +6226,23 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753774</v>
+        <v>753778</v>
       </c>
       <c r="R55" t="n">
-        <v>7217939</v>
+        <v>7217858</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6270,12 +6277,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6294,10 +6307,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125023355</v>
+        <v>125023321</v>
       </c>
       <c r="B56" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6310,21 +6323,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6334,10 +6347,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753792</v>
+        <v>753679</v>
       </c>
       <c r="R56" t="n">
-        <v>7217850</v>
+        <v>7218005</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6396,10 +6409,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125023398</v>
+        <v>125023324</v>
       </c>
       <c r="B57" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6412,41 +6425,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753778</v>
+        <v>753480</v>
       </c>
       <c r="R57" t="n">
-        <v>7217858</v>
+        <v>7218033</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6481,18 +6487,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125023321</v>
+        <v>125023431</v>
       </c>
       <c r="B58" t="n">
-        <v>91166</v>
+        <v>80063</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6523,25 +6523,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6551,10 +6551,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753679</v>
+        <v>753774</v>
       </c>
       <c r="R58" t="n">
-        <v>7218005</v>
+        <v>7217939</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125023324</v>
+        <v>125023355</v>
       </c>
       <c r="B59" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6629,21 +6629,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753480</v>
+        <v>753792</v>
       </c>
       <c r="R59" t="n">
-        <v>7218033</v>
+        <v>7217850</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -2570,10 +2570,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125023392</v>
+        <v>125023341</v>
       </c>
       <c r="B20" t="n">
-        <v>98269</v>
+        <v>80056</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2582,25 +2582,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753718</v>
+        <v>753654</v>
       </c>
       <c r="R20" t="n">
-        <v>7218035</v>
+        <v>7218008</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2672,10 +2672,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125023341</v>
+        <v>125023349</v>
       </c>
       <c r="B21" t="n">
-        <v>80056</v>
+        <v>80028</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2684,25 +2684,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753654</v>
+        <v>753795</v>
       </c>
       <c r="R21" t="n">
-        <v>7218008</v>
+        <v>7217800</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,7 +2774,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125023349</v>
+        <v>125023374</v>
       </c>
       <c r="B22" t="n">
         <v>80028</v>
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753795</v>
+        <v>753763</v>
       </c>
       <c r="R22" t="n">
-        <v>7217800</v>
+        <v>7218015</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,10 +2876,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125023374</v>
+        <v>125023380</v>
       </c>
       <c r="B23" t="n">
-        <v>80028</v>
+        <v>80064</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2888,25 +2888,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753763</v>
+        <v>753769</v>
       </c>
       <c r="R23" t="n">
-        <v>7218015</v>
+        <v>7218019</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2978,10 +2978,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125023380</v>
+        <v>125023343</v>
       </c>
       <c r="B24" t="n">
-        <v>80064</v>
+        <v>80028</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2990,25 +2990,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753769</v>
+        <v>753760</v>
       </c>
       <c r="R24" t="n">
-        <v>7218019</v>
+        <v>7218023</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3056,12 +3056,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3080,10 +3086,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125023343</v>
+        <v>125023392</v>
       </c>
       <c r="B25" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3092,25 +3098,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3120,10 +3126,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753760</v>
+        <v>753718</v>
       </c>
       <c r="R25" t="n">
-        <v>7218023</v>
+        <v>7218035</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3158,18 +3164,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125023342</v>
+        <v>125023323</v>
       </c>
       <c r="B26" t="n">
-        <v>78684</v>
+        <v>91166</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753722</v>
+        <v>753504</v>
       </c>
       <c r="R26" t="n">
-        <v>7217596</v>
+        <v>7217889</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3272,7 +3272,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3291,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125023323</v>
+        <v>125023446</v>
       </c>
       <c r="B27" t="n">
-        <v>91166</v>
+        <v>91375</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3303,25 +3302,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3331,10 +3330,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753504</v>
+        <v>753567</v>
       </c>
       <c r="R27" t="n">
-        <v>7217889</v>
+        <v>7217721</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,6 +3374,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3393,10 +3393,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125023446</v>
+        <v>125023354</v>
       </c>
       <c r="B28" t="n">
-        <v>91375</v>
+        <v>80028</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3405,25 +3405,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1106</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753567</v>
+        <v>753773</v>
       </c>
       <c r="R28" t="n">
-        <v>7217721</v>
+        <v>7217842</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3477,7 +3477,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3496,10 +3495,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125023354</v>
+        <v>125023430</v>
       </c>
       <c r="B29" t="n">
-        <v>80028</v>
+        <v>80063</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3508,25 +3507,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3536,10 +3535,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753773</v>
+        <v>753789</v>
       </c>
       <c r="R29" t="n">
-        <v>7217842</v>
+        <v>7217809</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3598,10 +3597,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125023430</v>
+        <v>125023366</v>
       </c>
       <c r="B30" t="n">
-        <v>80063</v>
+        <v>80028</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3610,25 +3609,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3638,10 +3637,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753789</v>
+        <v>753778</v>
       </c>
       <c r="R30" t="n">
-        <v>7217809</v>
+        <v>7217945</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3700,10 +3699,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125023366</v>
+        <v>125023444</v>
       </c>
       <c r="B31" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3716,21 +3715,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3740,10 +3739,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753778</v>
+        <v>753746</v>
       </c>
       <c r="R31" t="n">
-        <v>7217945</v>
+        <v>7217930</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3776,6 +3775,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3802,7 +3806,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125023444</v>
+        <v>125023443</v>
       </c>
       <c r="B32" t="n">
         <v>57635</v>
@@ -3842,10 +3846,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753746</v>
+        <v>753575</v>
       </c>
       <c r="R32" t="n">
-        <v>7217930</v>
+        <v>7217751</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3882,7 +3886,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Avskalad gran</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3909,10 +3913,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125023443</v>
+        <v>125023342</v>
       </c>
       <c r="B33" t="n">
-        <v>57635</v>
+        <v>78684</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3925,21 +3929,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3949,10 +3953,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753575</v>
+        <v>753722</v>
       </c>
       <c r="R33" t="n">
-        <v>7217751</v>
+        <v>7217596</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3987,17 +3991,13 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125023391</v>
+        <v>125023373</v>
       </c>
       <c r="B60" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6727,25 +6727,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753706</v>
+        <v>753768</v>
       </c>
       <c r="R60" t="n">
-        <v>7218039</v>
+        <v>7218016</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6817,10 +6817,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125023434</v>
+        <v>125023368</v>
       </c>
       <c r="B61" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6833,42 +6833,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753797</v>
+        <v>753808</v>
       </c>
       <c r="R61" t="n">
-        <v>7217988</v>
+        <v>7217964</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6901,11 +6893,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6932,10 +6919,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125023373</v>
+        <v>125023404</v>
       </c>
       <c r="B62" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6948,21 +6935,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6972,10 +6959,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753768</v>
+        <v>753743</v>
       </c>
       <c r="R62" t="n">
-        <v>7218016</v>
+        <v>7218044</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7034,10 +7021,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125023368</v>
+        <v>125023434</v>
       </c>
       <c r="B63" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7050,34 +7037,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753808</v>
+        <v>753797</v>
       </c>
       <c r="R63" t="n">
-        <v>7217964</v>
+        <v>7217988</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7110,6 +7105,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7136,10 +7136,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125023404</v>
+        <v>125023391</v>
       </c>
       <c r="B64" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7148,25 +7148,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753743</v>
+        <v>753706</v>
       </c>
       <c r="R64" t="n">
-        <v>7218044</v>
+        <v>7218039</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -907,16 +907,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125023417</v>
+        <v>125023403</v>
       </c>
       <c r="B4" t="n">
         <v>78947</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>NT</t>
@@ -947,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753474</v>
+        <v>753762</v>
       </c>
       <c r="R4" t="n">
-        <v>7218026</v>
+        <v>7218015</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,16 +1004,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125023378</v>
+        <v>125023365</v>
       </c>
       <c r="B5" t="n">
         <v>80028</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1049,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753722</v>
+        <v>753784</v>
       </c>
       <c r="R5" t="n">
-        <v>7218033</v>
+        <v>7217948</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,15 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125023362</v>
+        <v>125023324</v>
       </c>
       <c r="B6" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753752</v>
+        <v>753480</v>
       </c>
       <c r="R6" t="n">
-        <v>7217944</v>
+        <v>7218033</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,15 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125023326</v>
+        <v>125023402</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,42 +1209,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>753598</v>
+        <v>753752</v>
       </c>
       <c r="R7" t="n">
-        <v>7217744</v>
+        <v>7217878</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,11 +1269,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,15 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125023363</v>
+        <v>125023426</v>
       </c>
       <c r="B8" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1344,21 +1306,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1368,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>753782</v>
+        <v>753597</v>
       </c>
       <c r="R8" t="n">
-        <v>7217946</v>
+        <v>7217728</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,16 +1392,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125023413</v>
+        <v>125023401</v>
       </c>
       <c r="B9" t="n">
         <v>78947</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1470,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>753517</v>
+        <v>753780</v>
       </c>
       <c r="R9" t="n">
-        <v>7217918</v>
+        <v>7217865</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,15 +1489,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125023396</v>
+        <v>125023321</v>
       </c>
       <c r="B10" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,41 +1500,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>753626</v>
+        <v>753679</v>
       </c>
       <c r="R10" t="n">
-        <v>7218004</v>
+        <v>7218005</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,18 +1562,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1647,15 +1586,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125023441</v>
+        <v>125023327</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57793</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,21 +1597,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,10 +1621,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>753798</v>
+        <v>753740</v>
       </c>
       <c r="R11" t="n">
-        <v>7217948</v>
+        <v>7217891</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,11 +1657,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1754,15 +1683,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023320</v>
+        <v>125023368</v>
       </c>
       <c r="B12" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,21 +1694,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1794,10 +1718,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>753687</v>
+        <v>753808</v>
       </c>
       <c r="R12" t="n">
-        <v>7217999</v>
+        <v>7217964</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1856,15 +1780,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125023403</v>
+        <v>125023326</v>
       </c>
       <c r="B13" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,34 +1791,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753762</v>
+        <v>753598</v>
       </c>
       <c r="R13" t="n">
-        <v>7218015</v>
+        <v>7217744</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,6 +1859,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1958,37 +1890,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125023372</v>
+        <v>125023389</v>
       </c>
       <c r="B14" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1998,10 +1925,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753790</v>
+        <v>753729</v>
       </c>
       <c r="R14" t="n">
-        <v>7217992</v>
+        <v>7218042</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,37 +1987,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125023335</v>
+        <v>125023388</v>
       </c>
       <c r="B15" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2100,10 +2022,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>753790</v>
+        <v>753742</v>
       </c>
       <c r="R15" t="n">
-        <v>7217992</v>
+        <v>7217924</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,15 +2084,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125023345</v>
+        <v>125023328</v>
       </c>
       <c r="B16" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57793</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,21 +2095,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2202,10 +2119,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753790</v>
+        <v>753742</v>
       </c>
       <c r="R16" t="n">
-        <v>7217981</v>
+        <v>7217926</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2264,37 +2181,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125023389</v>
+        <v>125023330</v>
       </c>
       <c r="B17" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57793</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2304,10 +2216,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753729</v>
+        <v>753730</v>
       </c>
       <c r="R17" t="n">
-        <v>7218042</v>
+        <v>7217943</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2366,15 +2278,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125023429</v>
+        <v>125023318</v>
       </c>
       <c r="B18" t="n">
-        <v>80063</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91131</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,21 +2289,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,10 +2313,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753792</v>
+        <v>753680</v>
       </c>
       <c r="R18" t="n">
-        <v>7217798</v>
+        <v>7218004</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2468,37 +2375,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125023390</v>
+        <v>125023351</v>
       </c>
       <c r="B19" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2508,10 +2410,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753701</v>
+        <v>753758</v>
       </c>
       <c r="R19" t="n">
-        <v>7218031</v>
+        <v>7217819</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2570,37 +2472,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125023341</v>
+        <v>125023345</v>
       </c>
       <c r="B20" t="n">
-        <v>80056</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2610,10 +2507,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753654</v>
+        <v>753790</v>
       </c>
       <c r="R20" t="n">
-        <v>7218008</v>
+        <v>7217981</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2672,15 +2569,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125023349</v>
+        <v>125023435</v>
       </c>
       <c r="B21" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,34 +2580,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753795</v>
+        <v>753562</v>
       </c>
       <c r="R21" t="n">
-        <v>7217800</v>
+        <v>7217727</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2748,6 +2648,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2774,16 +2679,11 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125023374</v>
+        <v>125023355</v>
       </c>
       <c r="B22" t="n">
         <v>80028</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2814,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753763</v>
+        <v>753792</v>
       </c>
       <c r="R22" t="n">
-        <v>7218015</v>
+        <v>7217850</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,37 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125023380</v>
+        <v>125023357</v>
       </c>
       <c r="B23" t="n">
-        <v>80064</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2916,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753769</v>
+        <v>753793</v>
       </c>
       <c r="R23" t="n">
-        <v>7218019</v>
+        <v>7217856</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2978,15 +2873,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125023343</v>
+        <v>125023342</v>
       </c>
       <c r="B24" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78684</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2994,21 +2884,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3018,10 +2908,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753760</v>
+        <v>753722</v>
       </c>
       <c r="R24" t="n">
-        <v>7218023</v>
+        <v>7217596</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3054,11 +2944,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3086,37 +2971,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125023392</v>
+        <v>125023416</v>
       </c>
       <c r="B25" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3126,10 +3006,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753718</v>
+        <v>753470</v>
       </c>
       <c r="R25" t="n">
-        <v>7218035</v>
+        <v>7218024</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,37 +3068,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125023323</v>
+        <v>125023429</v>
       </c>
       <c r="B26" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80063</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3228,10 +3103,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753504</v>
+        <v>753792</v>
       </c>
       <c r="R26" t="n">
-        <v>7217889</v>
+        <v>7217798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3290,37 +3165,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125023446</v>
+        <v>125023336</v>
       </c>
       <c r="B27" t="n">
-        <v>91375</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1106</v>
+        <v>112</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3330,10 +3200,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753567</v>
+        <v>753566</v>
       </c>
       <c r="R27" t="n">
-        <v>7217721</v>
+        <v>7217862</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3374,7 +3244,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3393,15 +3262,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125023354</v>
+        <v>125023438</v>
       </c>
       <c r="B28" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3409,21 +3273,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3433,10 +3297,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753773</v>
+        <v>753612</v>
       </c>
       <c r="R28" t="n">
-        <v>7217842</v>
+        <v>7217703</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3469,6 +3333,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3495,37 +3364,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125023430</v>
+        <v>125023315</v>
       </c>
       <c r="B29" t="n">
-        <v>80063</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3535,10 +3399,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753789</v>
+        <v>753491</v>
       </c>
       <c r="R29" t="n">
-        <v>7217809</v>
+        <v>7217766</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3571,6 +3435,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3597,15 +3466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125023366</v>
+        <v>125023444</v>
       </c>
       <c r="B30" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3613,21 +3477,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3637,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753778</v>
+        <v>753746</v>
       </c>
       <c r="R30" t="n">
-        <v>7217945</v>
+        <v>7217930</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3673,6 +3537,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3699,37 +3568,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125023444</v>
+        <v>125023392</v>
       </c>
       <c r="B31" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3739,10 +3603,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753746</v>
+        <v>753718</v>
       </c>
       <c r="R31" t="n">
-        <v>7217930</v>
+        <v>7218035</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3775,11 +3639,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3806,15 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125023443</v>
+        <v>125023412</v>
       </c>
       <c r="B32" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3822,21 +3676,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3846,10 +3700,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753575</v>
+        <v>753568</v>
       </c>
       <c r="R32" t="n">
-        <v>7217751</v>
+        <v>7217875</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3882,11 +3736,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3913,15 +3762,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125023342</v>
+        <v>125023348</v>
       </c>
       <c r="B33" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3929,21 +3773,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3953,10 +3797,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753722</v>
+        <v>753817</v>
       </c>
       <c r="R33" t="n">
-        <v>7217596</v>
+        <v>7217853</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3997,7 +3841,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4016,15 +3859,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125023328</v>
+        <v>125023378</v>
       </c>
       <c r="B34" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4032,21 +3870,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4056,10 +3894,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753742</v>
+        <v>753722</v>
       </c>
       <c r="R34" t="n">
-        <v>7217926</v>
+        <v>7218033</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4118,15 +3956,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125023405</v>
+        <v>125023360</v>
       </c>
       <c r="B35" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4134,21 +3967,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4158,10 +3991,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753748</v>
+        <v>753752</v>
       </c>
       <c r="R35" t="n">
-        <v>7218047</v>
+        <v>7217944</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4220,15 +4053,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125023325</v>
+        <v>125023316</v>
       </c>
       <c r="B36" t="n">
         <v>57635</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4258,7 +4086,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4268,10 +4096,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753575</v>
+        <v>753568</v>
       </c>
       <c r="R36" t="n">
-        <v>7217959</v>
+        <v>7217733</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4308,7 +4136,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4335,15 +4163,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125023438</v>
+        <v>125023404</v>
       </c>
       <c r="B37" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4351,21 +4174,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4375,10 +4198,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753612</v>
+        <v>753743</v>
       </c>
       <c r="R37" t="n">
-        <v>7217703</v>
+        <v>7218044</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4411,11 +4234,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4442,15 +4260,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125023351</v>
+        <v>125023395</v>
       </c>
       <c r="B38" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91184</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4458,21 +4271,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4482,10 +4295,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753758</v>
+        <v>753472</v>
       </c>
       <c r="R38" t="n">
-        <v>7217819</v>
+        <v>7218031</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4544,37 +4357,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125023334</v>
+        <v>125023399</v>
       </c>
       <c r="B39" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4584,10 +4392,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753752</v>
+        <v>753751</v>
       </c>
       <c r="R39" t="n">
-        <v>7217919</v>
+        <v>7217806</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4651,11 +4459,6 @@
       <c r="B40" t="n">
         <v>80063</v>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>LC</t>
@@ -4748,37 +4551,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125023337</v>
+        <v>125023323</v>
       </c>
       <c r="B41" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4788,10 +4586,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753523</v>
+        <v>753504</v>
       </c>
       <c r="R41" t="n">
-        <v>7218086</v>
+        <v>7217889</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4850,37 +4648,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125023409</v>
+        <v>125023319</v>
       </c>
       <c r="B42" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91131</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4890,10 +4683,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753562</v>
+        <v>753506</v>
       </c>
       <c r="R42" t="n">
-        <v>7217917</v>
+        <v>7217904</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4952,15 +4745,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125023423</v>
+        <v>125023343</v>
       </c>
       <c r="B43" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4968,21 +4756,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4992,10 +4780,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753610</v>
+        <v>753760</v>
       </c>
       <c r="R43" t="n">
-        <v>7217727</v>
+        <v>7218023</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5030,12 +4818,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5054,16 +4848,11 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125023367</v>
+        <v>125023372</v>
       </c>
       <c r="B44" t="n">
         <v>80028</v>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D44" t="inlineStr">
         <is>
           <t>NT</t>
@@ -5094,10 +4883,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753786</v>
+        <v>753790</v>
       </c>
       <c r="R44" t="n">
-        <v>7217962</v>
+        <v>7217992</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5156,16 +4945,11 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125023358</v>
+        <v>125023349</v>
       </c>
       <c r="B45" t="n">
         <v>80028</v>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D45" t="inlineStr">
         <is>
           <t>NT</t>
@@ -5196,10 +4980,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753758</v>
+        <v>753795</v>
       </c>
       <c r="R45" t="n">
-        <v>7217900</v>
+        <v>7217800</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5258,15 +5042,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125023416</v>
+        <v>125023445</v>
       </c>
       <c r="B46" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5274,21 +5053,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5298,10 +5077,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753470</v>
+        <v>753715</v>
       </c>
       <c r="R46" t="n">
-        <v>7218024</v>
+        <v>7218026</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5334,6 +5113,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5360,37 +5144,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125023442</v>
+        <v>125023446</v>
       </c>
       <c r="B47" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1106</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5400,10 +5179,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753726</v>
+        <v>753567</v>
       </c>
       <c r="R47" t="n">
-        <v>7218039</v>
+        <v>7217721</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5438,17 +5217,13 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5467,15 +5242,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125023445</v>
+        <v>125023406</v>
       </c>
       <c r="B48" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5483,21 +5253,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5507,10 +5277,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753715</v>
+        <v>753718</v>
       </c>
       <c r="R48" t="n">
-        <v>7218026</v>
+        <v>7218042</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5543,11 +5313,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5574,37 +5339,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125023338</v>
+        <v>125023387</v>
       </c>
       <c r="B49" t="n">
-        <v>8720</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78683</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100798</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Smal trollknäppare</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Danosoma conspersum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5614,10 +5374,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753699</v>
+        <v>753816</v>
       </c>
       <c r="R49" t="n">
-        <v>7217618</v>
+        <v>7217838</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5658,7 +5418,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5677,15 +5436,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125023381</v>
+        <v>125023430</v>
       </c>
       <c r="B50" t="n">
-        <v>80064</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80063</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5693,21 +5447,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5717,10 +5471,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753722</v>
+        <v>753789</v>
       </c>
       <c r="R50" t="n">
-        <v>7218033</v>
+        <v>7217809</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5779,15 +5533,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125023401</v>
+        <v>125023325</v>
       </c>
       <c r="B51" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5795,34 +5544,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753780</v>
+        <v>753575</v>
       </c>
       <c r="R51" t="n">
-        <v>7217865</v>
+        <v>7217959</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5855,6 +5612,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5881,15 +5643,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125023420</v>
+        <v>125023443</v>
       </c>
       <c r="B52" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5897,21 +5654,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5921,10 +5678,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>753559</v>
+        <v>753575</v>
       </c>
       <c r="R52" t="n">
-        <v>7217734</v>
+        <v>7217751</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5957,6 +5714,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5983,15 +5745,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125023414</v>
+        <v>125023333</v>
       </c>
       <c r="B53" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57793</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5999,21 +5756,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6023,10 +5780,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>753630</v>
+        <v>753781</v>
       </c>
       <c r="R53" t="n">
-        <v>7218006</v>
+        <v>7217902</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6085,37 +5842,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125023315</v>
+        <v>125023341</v>
       </c>
       <c r="B54" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80056</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6125,10 +5877,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753491</v>
+        <v>753654</v>
       </c>
       <c r="R54" t="n">
-        <v>7217766</v>
+        <v>7218008</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6161,11 +5913,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6192,15 +5939,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125023398</v>
+        <v>125023439</v>
       </c>
       <c r="B55" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6208,41 +5950,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753778</v>
+        <v>753568</v>
       </c>
       <c r="R55" t="n">
-        <v>7217858</v>
+        <v>7217716</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6279,7 +6014,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6288,7 +6023,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6307,37 +6041,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125023321</v>
+        <v>125023390</v>
       </c>
       <c r="B56" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6347,10 +6076,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753679</v>
+        <v>753701</v>
       </c>
       <c r="R56" t="n">
-        <v>7218005</v>
+        <v>7218031</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6409,15 +6138,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125023324</v>
+        <v>125023398</v>
       </c>
       <c r="B57" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6425,34 +6149,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753480</v>
+        <v>753778</v>
       </c>
       <c r="R57" t="n">
-        <v>7218033</v>
+        <v>7217858</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6487,12 +6218,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6511,32 +6248,27 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125023431</v>
+        <v>125023418</v>
       </c>
       <c r="B58" t="n">
-        <v>80063</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6551,10 +6283,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753774</v>
+        <v>753406</v>
       </c>
       <c r="R58" t="n">
-        <v>7217939</v>
+        <v>7217999</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6613,16 +6345,11 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125023355</v>
+        <v>125023375</v>
       </c>
       <c r="B59" t="n">
         <v>80028</v>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>NT</t>
@@ -6653,10 +6380,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753792</v>
+        <v>753750</v>
       </c>
       <c r="R59" t="n">
-        <v>7217850</v>
+        <v>7218028</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6715,16 +6442,11 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125023373</v>
+        <v>125023354</v>
       </c>
       <c r="B60" t="n">
         <v>80028</v>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>NT</t>
@@ -6755,10 +6477,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753768</v>
+        <v>753773</v>
       </c>
       <c r="R60" t="n">
-        <v>7218016</v>
+        <v>7217842</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6817,16 +6539,11 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125023368</v>
+        <v>125023352</v>
       </c>
       <c r="B61" t="n">
         <v>80028</v>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>NT</t>
@@ -6857,10 +6574,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753808</v>
+        <v>753763</v>
       </c>
       <c r="R61" t="n">
-        <v>7217964</v>
+        <v>7217831</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6919,15 +6636,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125023404</v>
+        <v>125023434</v>
       </c>
       <c r="B62" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6935,34 +6647,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753743</v>
+        <v>753797</v>
       </c>
       <c r="R62" t="n">
-        <v>7218044</v>
+        <v>7217988</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6995,6 +6715,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7021,15 +6746,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125023434</v>
+        <v>125023414</v>
       </c>
       <c r="B63" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7037,42 +6757,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753797</v>
+        <v>753630</v>
       </c>
       <c r="R63" t="n">
-        <v>7217988</v>
+        <v>7218006</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7105,11 +6817,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Gjorde bohålet större, flög spån! Ville inte störa och uppehöll mig därför inte nära eller länge vid bohålet. Därav viss osäkerhet om art, svårt att se den ordentligt.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7136,37 +6843,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125023391</v>
+        <v>125023405</v>
       </c>
       <c r="B64" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7176,10 +6878,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753706</v>
+        <v>753748</v>
       </c>
       <c r="R64" t="n">
-        <v>7218039</v>
+        <v>7218047</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7238,15 +6940,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125023348</v>
+        <v>125023394</v>
       </c>
       <c r="B65" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91184</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7254,21 +6951,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7278,10 +6975,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753817</v>
+        <v>753596</v>
       </c>
       <c r="R65" t="n">
-        <v>7217853</v>
+        <v>7217939</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7340,37 +7037,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125023418</v>
+        <v>125023337</v>
       </c>
       <c r="B66" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79932</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7380,10 +7072,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753406</v>
+        <v>753523</v>
       </c>
       <c r="R66" t="n">
-        <v>7217999</v>
+        <v>7218086</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7442,16 +7134,11 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125023407</v>
+        <v>125023421</v>
       </c>
       <c r="B67" t="n">
         <v>78947</v>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>NT</t>
@@ -7482,10 +7169,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753671</v>
+        <v>753573</v>
       </c>
       <c r="R67" t="n">
-        <v>7218008</v>
+        <v>7217745</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7544,16 +7231,11 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125023419</v>
+        <v>125023407</v>
       </c>
       <c r="B68" t="n">
         <v>78947</v>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D68" t="inlineStr">
         <is>
           <t>NT</t>
@@ -7584,10 +7266,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753550</v>
+        <v>753671</v>
       </c>
       <c r="R68" t="n">
-        <v>7217725</v>
+        <v>7218008</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7646,15 +7328,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125023387</v>
+        <v>125023413</v>
       </c>
       <c r="B69" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7662,21 +7339,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7686,10 +7363,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753816</v>
+        <v>753517</v>
       </c>
       <c r="R69" t="n">
-        <v>7217838</v>
+        <v>7217918</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7748,15 +7425,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125023347</v>
+        <v>125023396</v>
       </c>
       <c r="B70" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7764,34 +7436,41 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753850</v>
+        <v>753626</v>
       </c>
       <c r="R70" t="n">
-        <v>7217843</v>
+        <v>7218004</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7826,12 +7505,18 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7850,15 +7535,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125023411</v>
+        <v>125023373</v>
       </c>
       <c r="B71" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7866,21 +7546,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7890,10 +7570,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753557</v>
+        <v>753768</v>
       </c>
       <c r="R71" t="n">
-        <v>7217895</v>
+        <v>7218016</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7952,15 +7632,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125023330</v>
+        <v>125023417</v>
       </c>
       <c r="B72" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7968,21 +7643,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7992,10 +7667,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753730</v>
+        <v>753474</v>
       </c>
       <c r="R72" t="n">
-        <v>7217943</v>
+        <v>7218026</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8054,15 +7729,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125023316</v>
+        <v>125023350</v>
       </c>
       <c r="B73" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8070,42 +7740,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>753568</v>
+        <v>753789</v>
       </c>
       <c r="R73" t="n">
-        <v>7217733</v>
+        <v>7217812</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8138,11 +7800,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8169,15 +7826,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125023336</v>
+        <v>125023358</v>
       </c>
       <c r="B74" t="n">
-        <v>91116</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8185,21 +7837,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8209,10 +7861,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>753566</v>
+        <v>753758</v>
       </c>
       <c r="R74" t="n">
-        <v>7217862</v>
+        <v>7217900</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8271,16 +7923,11 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125023357</v>
+        <v>125023374</v>
       </c>
       <c r="B75" t="n">
         <v>80028</v>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D75" t="inlineStr">
         <is>
           <t>NT</t>
@@ -8311,10 +7958,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>753793</v>
+        <v>753763</v>
       </c>
       <c r="R75" t="n">
-        <v>7217856</v>
+        <v>7218015</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8373,37 +8020,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125023365</v>
+        <v>125023334</v>
       </c>
       <c r="B76" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80057</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8413,10 +8055,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>753784</v>
+        <v>753752</v>
       </c>
       <c r="R76" t="n">
-        <v>7217948</v>
+        <v>7217919</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8475,16 +8117,11 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125023369</v>
+        <v>125023366</v>
       </c>
       <c r="B77" t="n">
         <v>80028</v>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D77" t="inlineStr">
         <is>
           <t>NT</t>
@@ -8515,10 +8152,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>753797</v>
+        <v>753778</v>
       </c>
       <c r="R77" t="n">
-        <v>7218005</v>
+        <v>7217945</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8577,15 +8214,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125023352</v>
+        <v>125023442</v>
       </c>
       <c r="B78" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8593,21 +8225,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8617,10 +8249,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>753763</v>
+        <v>753726</v>
       </c>
       <c r="R78" t="n">
-        <v>7217831</v>
+        <v>7218039</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8653,6 +8285,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8679,37 +8316,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125023318</v>
+        <v>125023411</v>
       </c>
       <c r="B79" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8719,10 +8351,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>753680</v>
+        <v>753557</v>
       </c>
       <c r="R79" t="n">
-        <v>7218004</v>
+        <v>7217895</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8781,15 +8413,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125023395</v>
+        <v>125023363</v>
       </c>
       <c r="B80" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8797,21 +8424,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8821,10 +8448,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>753472</v>
+        <v>753782</v>
       </c>
       <c r="R80" t="n">
-        <v>7218031</v>
+        <v>7217946</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8883,37 +8510,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125023319</v>
+        <v>125023347</v>
       </c>
       <c r="B81" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8923,10 +8545,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>753506</v>
+        <v>753850</v>
       </c>
       <c r="R81" t="n">
-        <v>7217904</v>
+        <v>7217843</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8985,15 +8607,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125023421</v>
+        <v>125023369</v>
       </c>
       <c r="B82" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9001,21 +8618,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9025,10 +8642,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>753573</v>
+        <v>753797</v>
       </c>
       <c r="R82" t="n">
-        <v>7217745</v>
+        <v>7218005</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9087,15 +8704,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125023333</v>
+        <v>125023419</v>
       </c>
       <c r="B83" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9103,21 +8715,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9127,10 +8739,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>753781</v>
+        <v>753550</v>
       </c>
       <c r="R83" t="n">
-        <v>7217902</v>
+        <v>7217725</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9189,15 +8801,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125023388</v>
+        <v>125023338</v>
       </c>
       <c r="B84" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8720</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9205,21 +8812,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>100798</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal trollknäppare</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Danosoma conspersum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyllenhal, 1808)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9229,10 +8836,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>753742</v>
+        <v>753699</v>
       </c>
       <c r="R84" t="n">
-        <v>7217924</v>
+        <v>7217618</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9273,6 +8880,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9291,15 +8899,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125023359</v>
+        <v>125023420</v>
       </c>
       <c r="B85" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9307,21 +8910,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9331,10 +8934,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>753753</v>
+        <v>753559</v>
       </c>
       <c r="R85" t="n">
-        <v>7217910</v>
+        <v>7217734</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9393,37 +8996,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125023402</v>
+        <v>125023335</v>
       </c>
       <c r="B86" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80057</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9433,10 +9031,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>753752</v>
+        <v>753790</v>
       </c>
       <c r="R86" t="n">
-        <v>7217878</v>
+        <v>7217992</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9495,15 +9093,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125023426</v>
+        <v>125023359</v>
       </c>
       <c r="B87" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9511,21 +9104,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9535,10 +9128,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>753597</v>
+        <v>753753</v>
       </c>
       <c r="R87" t="n">
-        <v>7217728</v>
+        <v>7217910</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9597,37 +9190,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125023412</v>
+        <v>125023381</v>
       </c>
       <c r="B88" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80064</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9637,10 +9225,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>753568</v>
+        <v>753722</v>
       </c>
       <c r="R88" t="n">
-        <v>7217875</v>
+        <v>7218033</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9699,15 +9287,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125023399</v>
+        <v>125023320</v>
       </c>
       <c r="B89" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9715,21 +9298,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9739,10 +9322,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>753751</v>
+        <v>753687</v>
       </c>
       <c r="R89" t="n">
-        <v>7217806</v>
+        <v>7217999</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9801,15 +9384,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125023435</v>
+        <v>125023423</v>
       </c>
       <c r="B90" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9817,39 +9395,31 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Fjällboslyet, Vb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>753562</v>
+        <v>753610</v>
       </c>
       <c r="R90" t="n">
         <v>7217727</v>
@@ -9885,11 +9455,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Färsk bohål</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9916,15 +9481,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125023327</v>
+        <v>125023367</v>
       </c>
       <c r="B91" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9932,21 +9492,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9956,10 +9516,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>753740</v>
+        <v>753786</v>
       </c>
       <c r="R91" t="n">
-        <v>7217891</v>
+        <v>7217962</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10018,37 +9578,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125023406</v>
+        <v>125023380</v>
       </c>
       <c r="B92" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80064</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10058,10 +9613,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>753718</v>
+        <v>753769</v>
       </c>
       <c r="R92" t="n">
-        <v>7218042</v>
+        <v>7218019</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10120,15 +9675,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125023350</v>
+        <v>125023409</v>
       </c>
       <c r="B93" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10136,21 +9686,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10160,10 +9710,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>753789</v>
+        <v>753562</v>
       </c>
       <c r="R93" t="n">
-        <v>7217812</v>
+        <v>7217917</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10222,37 +9772,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125023375</v>
+        <v>125023431</v>
       </c>
       <c r="B94" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80063</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10262,10 +9807,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>753750</v>
+        <v>753774</v>
       </c>
       <c r="R94" t="n">
-        <v>7218028</v>
+        <v>7217939</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10324,15 +9869,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125023394</v>
+        <v>125023441</v>
       </c>
       <c r="B95" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10340,21 +9880,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10364,10 +9904,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>753596</v>
+        <v>753798</v>
       </c>
       <c r="R95" t="n">
-        <v>7217939</v>
+        <v>7217948</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10400,6 +9940,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10426,37 +9971,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125023439</v>
+        <v>125023391</v>
       </c>
       <c r="B96" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10466,10 +10006,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>753568</v>
+        <v>753706</v>
       </c>
       <c r="R96" t="n">
-        <v>7217716</v>
+        <v>7218039</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10502,11 +10042,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10533,15 +10068,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125023317</v>
+        <v>125023383</v>
       </c>
       <c r="B97" t="n">
-        <v>78979</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91624</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10549,21 +10079,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10576,10 +10101,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>753719</v>
+        <v>753603</v>
       </c>
       <c r="R97" t="n">
-        <v>7217616</v>
+        <v>7217932</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10639,15 +10164,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125023383</v>
+        <v>125023317</v>
       </c>
       <c r="B98" t="n">
-        <v>91570</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78999</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10655,16 +10175,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6040186</v>
+        <v>185</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10677,10 +10202,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>753603</v>
+        <v>753719</v>
       </c>
       <c r="R98" t="n">
-        <v>7217932</v>
+        <v>7217616</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10743,12 +10268,7 @@
         <v>125023339</v>
       </c>
       <c r="B99" t="n">
-        <v>92440</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92494</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 16580-2025 artfynd.xlsx
+++ b/artfynd/A 16580-2025 artfynd.xlsx
@@ -10268,7 +10268,7 @@
         <v>125023339</v>
       </c>
       <c r="B99" t="n">
-        <v>92494</v>
+        <v>92501</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
